--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32296,6 +32296,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1389">
+      <c r="A1389" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1389" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1389" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="G1389" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32319,6 +32319,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1390">
+      <c r="A1390" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1390" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1390" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="G1390" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32342,6 +32342,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1391">
+      <c r="A1391" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1391" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C1391" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="G1391" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32365,6 +32365,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1392">
+      <c r="A1392" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1392" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1392" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G1392" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32206,22 +32206,22 @@
     </row>
     <row r="1385">
       <c r="A1385" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1385" t="n">
-        <v>3000</v>
+        <v>250</v>
       </c>
       <c r="C1385" t="n">
         <v>6.09999990463257</v>
       </c>
       <c r="D1385" t="n">
-        <v>6</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="E1385" t="n">
-        <v>6.05000019073486</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="F1385" t="n">
-        <v>6.05000019073486</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="G1385" t="s">
         <v>7</v>
@@ -32229,16 +32229,16 @@
     </row>
     <row r="1386">
       <c r="A1386" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1386" t="n">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="C1386" t="n">
-        <v>6.05000019073486</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="D1386" t="n">
-        <v>6.05000019073486</v>
+        <v>6</v>
       </c>
       <c r="E1386" t="n">
         <v>6.05000019073486</v>
@@ -32252,22 +32252,22 @@
     </row>
     <row r="1387">
       <c r="A1387" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1387" t="n">
-        <v>53750</v>
+        <v>250</v>
       </c>
       <c r="C1387" t="n">
-        <v>6.59999990463257</v>
+        <v>6.05000019073486</v>
       </c>
       <c r="D1387" t="n">
-        <v>6.15000009536743</v>
+        <v>6.05000019073486</v>
       </c>
       <c r="E1387" t="n">
-        <v>6.15000009536743</v>
+        <v>6.05000019073486</v>
       </c>
       <c r="F1387" t="n">
-        <v>6.55000019073486</v>
+        <v>6.05000019073486</v>
       </c>
       <c r="G1387" t="s">
         <v>7</v>
@@ -32275,22 +32275,22 @@
     </row>
     <row r="1388">
       <c r="A1388" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1388" t="n">
-        <v>12500</v>
+        <v>53750</v>
       </c>
       <c r="C1388" t="n">
         <v>6.59999990463257</v>
       </c>
       <c r="D1388" t="n">
-        <v>6.34999990463257</v>
+        <v>6.15000009536743</v>
       </c>
       <c r="E1388" t="n">
-        <v>6.59999990463257</v>
+        <v>6.15000009536743</v>
       </c>
       <c r="F1388" t="n">
-        <v>6.34999990463257</v>
+        <v>6.55000019073486</v>
       </c>
       <c r="G1388" t="s">
         <v>7</v>
@@ -32298,22 +32298,22 @@
     </row>
     <row r="1389">
       <c r="A1389" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1389" t="n">
-        <v>6000</v>
+        <v>12500</v>
       </c>
       <c r="C1389" t="n">
-        <v>6.40000009536743</v>
+        <v>6.59999990463257</v>
       </c>
       <c r="D1389" t="n">
-        <v>6.30000019073486</v>
+        <v>6.34999990463257</v>
       </c>
       <c r="E1389" t="n">
-        <v>6.40000009536743</v>
+        <v>6.59999990463257</v>
       </c>
       <c r="F1389" t="n">
-        <v>6.40000009536743</v>
+        <v>6.34999990463257</v>
       </c>
       <c r="G1389" t="s">
         <v>7</v>
@@ -32321,22 +32321,22 @@
     </row>
     <row r="1390">
       <c r="A1390" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1390" t="n">
-        <v>750</v>
+        <v>6000</v>
       </c>
       <c r="C1390" t="n">
-        <v>6.34999990463257</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="D1390" t="n">
         <v>6.30000019073486</v>
       </c>
       <c r="E1390" t="n">
-        <v>6.34999990463257</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="F1390" t="n">
-        <v>6.30000019073486</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="G1390" t="s">
         <v>7</v>
@@ -32344,22 +32344,22 @@
     </row>
     <row r="1391">
       <c r="A1391" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1391" t="n">
-        <v>6500</v>
+        <v>750</v>
       </c>
       <c r="C1391" t="n">
-        <v>6.40000009536743</v>
+        <v>6.34999990463257</v>
       </c>
       <c r="D1391" t="n">
         <v>6.30000019073486</v>
       </c>
       <c r="E1391" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="F1391" t="n">
         <v>6.30000019073486</v>
-      </c>
-      <c r="F1391" t="n">
-        <v>6.40000009536743</v>
       </c>
       <c r="G1391" t="s">
         <v>7</v>
@@ -32367,24 +32367,47 @@
     </row>
     <row r="1392">
       <c r="A1392" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1392" t="n">
-        <v>3000</v>
+        <v>6500</v>
       </c>
       <c r="C1392" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="D1392" t="n">
         <v>6.30000019073486</v>
-      </c>
-      <c r="D1392" t="n">
-        <v>6.25</v>
       </c>
       <c r="E1392" t="n">
         <v>6.30000019073486</v>
       </c>
       <c r="F1392" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="G1392" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1393" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C1393" t="n">
         <v>6.25</v>
       </c>
-      <c r="G1392" t="s">
+      <c r="D1393" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="G1393" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.04456090927124</v>
+        <v>3.04456067085266</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G5" t="n">
-        <v>3.19249391555786</v>
+        <v>3.19249367713928</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.29747843742371</v>
+        <v>3.29747867584229</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G23" t="n">
-        <v>3.34519910812378</v>
+        <v>3.34519934654236</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G29" t="n">
-        <v>3.40723562240601</v>
+        <v>3.40723538398743</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.5</v>
       </c>
       <c r="G32" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G36" t="n">
-        <v>3.33565497398376</v>
+        <v>3.33565473556519</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060949325562</v>
+        <v>3.65060973167419</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64583730697632</v>
+        <v>3.6458375453949</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.53608083724976</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.53608083724976</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G58" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G61" t="n">
-        <v>3.40723562240601</v>
+        <v>3.40723538398743</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.40723562240601</v>
+        <v>3.40723538398743</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G74" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.5</v>
       </c>
       <c r="G76" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G79" t="n">
-        <v>3.35474348068237</v>
+        <v>3.35474324226379</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G103" t="n">
-        <v>3.40723562240601</v>
+        <v>3.40723538398743</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G111" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.0037407875061</v>
+        <v>4.00374031066895</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>3.97988033294678</v>
+        <v>3.97988057136536</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G121" t="n">
-        <v>4.06577730178833</v>
+        <v>4.06577682495117</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G122" t="n">
-        <v>4.11349678039551</v>
+        <v>4.11349725723267</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G123" t="n">
-        <v>4.09918165206909</v>
+        <v>4.09918117523193</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G130" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079182624817</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.9655647277832</v>
+        <v>3.96556448936462</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079182624817</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.0037407875061</v>
+        <v>4.00374031066895</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95602035522461</v>
+        <v>3.95601987838745</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079182624817</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942422866821</v>
+        <v>3.98942375183105</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.88443970680237</v>
+        <v>3.88443994522095</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808711051941</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.89398336410522</v>
+        <v>3.89398312568665</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.82240319252014</v>
+        <v>3.82240295410156</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>3.82240319252014</v>
+        <v>3.82240295410156</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G169" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G180" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.5</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G193" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.53608083724976</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.5</v>
       </c>
       <c r="G202" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G204" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.50744819641113</v>
+        <v>3.50744843482971</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G215" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.5</v>
       </c>
       <c r="G231" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G239" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.5</v>
       </c>
       <c r="G244" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.5</v>
       </c>
       <c r="G249" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>3.29747843742371</v>
+        <v>3.29747867584229</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G256" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G258" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6028892993927</v>
+        <v>3.60288906097412</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>3.6028892993927</v>
+        <v>3.60288906097412</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.5</v>
       </c>
       <c r="G278" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.5</v>
       </c>
       <c r="G284" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>3.18772196769714</v>
+        <v>3.18772172927856</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535120010376</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535120010376</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535120010376</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G303" t="n">
-        <v>3.82717514038086</v>
+        <v>3.82717537879944</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>3.82717514038086</v>
+        <v>3.82717537879944</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.82717514038086</v>
+        <v>3.82717537879944</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808711051941</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>3.75082230567932</v>
+        <v>3.75082206726074</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G340" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>3.64583730697632</v>
+        <v>3.6458375453949</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G374" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G375" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G388" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.50267648696899</v>
+        <v>3.50267672538757</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G407" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>3.74092364311218</v>
+        <v>3.7409234046936</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.75</v>
       </c>
       <c r="G420" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.75</v>
       </c>
       <c r="G423" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G425" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G428" t="n">
-        <v>3.74092364311218</v>
+        <v>3.7409234046936</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G433" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.75</v>
       </c>
       <c r="G443" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.75</v>
       </c>
       <c r="G444" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.75</v>
       </c>
       <c r="G449" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G461" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.75</v>
       </c>
       <c r="G467" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G469" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.75</v>
       </c>
       <c r="G478" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G485" t="n">
-        <v>3.47026228904724</v>
+        <v>3.47026252746582</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G488" t="n">
-        <v>3.45092964172363</v>
+        <v>3.45092940330505</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.5</v>
       </c>
       <c r="G490" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.5</v>
       </c>
       <c r="G491" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31559896469116</v>
+        <v>3.31559920310974</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G501" t="n">
-        <v>3.45092964172363</v>
+        <v>3.45092940330505</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>3.52826142311096</v>
+        <v>3.52826166152954</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G505" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G507" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G515" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G519" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G521" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G522" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G523" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G530" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G537" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G538" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.75059032440186</v>
+        <v>3.75059056282043</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G570" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G571" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G573" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G577" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G581" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G582" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G583" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G592" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G593" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G595" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.5</v>
       </c>
       <c r="G604" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G611" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G639" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G643" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>3.76992297172546</v>
+        <v>3.76992321014404</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -36642,6 +36642,32 @@
         <v>6.15000009536743</v>
       </c>
       <c r="H1395" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1396" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C1396" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="H1396" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05410480499268</v>
+        <v>3.0541045665741</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246367454529</v>
+        <v>3.40246391296387</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>3.38337540626526</v>
+        <v>3.38337564468384</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611083984375</v>
+        <v>3.32611107826233</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G29" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723586082458</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.5</v>
       </c>
       <c r="G32" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G36" t="n">
-        <v>3.33565473556519</v>
+        <v>3.33565497398376</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G40" t="n">
-        <v>3.75559449195862</v>
+        <v>3.75559425354004</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197756767273</v>
+        <v>3.62197732925415</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G57" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G61" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723586082458</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>3.54562473297119</v>
+        <v>3.54562449455261</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836040496826</v>
+        <v>3.48836016654968</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.4120078086853</v>
+        <v>3.41200757026672</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723586082458</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G74" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.5</v>
       </c>
       <c r="G76" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839040756226</v>
+        <v>3.27839064598083</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839040756226</v>
+        <v>3.27839064598083</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495581626892</v>
+        <v>3.4549560546875</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G103" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723586082458</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.65538167953491</v>
+        <v>3.65538144111633</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492581367493</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.0848650932312</v>
+        <v>4.08486604690552</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G121" t="n">
-        <v>4.06577682495117</v>
+        <v>4.06577777862549</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G123" t="n">
-        <v>4.09918117523193</v>
+        <v>4.09918165206909</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.97033596038818</v>
+        <v>3.97033619880676</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896860122681</v>
+        <v>3.99896883964539</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.97033596038818</v>
+        <v>3.97033619880676</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.97033596038818</v>
+        <v>3.97033619880676</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.96556448936462</v>
+        <v>3.96556401252747</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.0085129737854</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.9417040348053</v>
+        <v>3.94170427322388</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95601987838745</v>
+        <v>3.95602035522461</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896860122681</v>
+        <v>3.99896883964539</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124793052673</v>
+        <v>3.95124816894531</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124793052673</v>
+        <v>3.95124816894531</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>4.0085129737854</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760028839111</v>
+        <v>4.02760076522827</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>4.01805639266968</v>
+        <v>4.01805686950684</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>4.0085129737854</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942375183105</v>
+        <v>3.98942446708679</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.9417040348053</v>
+        <v>3.94170427322388</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.87489533424377</v>
+        <v>3.87489557266235</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808663368225</v>
+        <v>3.80808687210083</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>3.87489533424377</v>
+        <v>3.87489557266235</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.89398312568665</v>
+        <v>3.8939836025238</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.82240295410156</v>
+        <v>3.82240319252014</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>3.82240295410156</v>
+        <v>3.82240319252014</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>3.65538167953491</v>
+        <v>3.65538144111633</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G175" t="n">
-        <v>3.61243343353271</v>
+        <v>3.61243319511414</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G180" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383127212524</v>
+        <v>3.37383151054382</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.5</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G197" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.5</v>
       </c>
       <c r="G202" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G207" t="n">
-        <v>3.4501838684082</v>
+        <v>3.45018410682678</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G215" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G216" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G222" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.5</v>
       </c>
       <c r="G231" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>3.46450018882751</v>
+        <v>3.46450042724609</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G239" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.5</v>
       </c>
       <c r="G244" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.5</v>
       </c>
       <c r="G249" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495581626892</v>
+        <v>3.4549560546875</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G258" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>3.60288906097412</v>
+        <v>3.6028892993927</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>3.60288906097412</v>
+        <v>3.6028892993927</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G269" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G270" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.5</v>
       </c>
       <c r="G278" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.5</v>
       </c>
       <c r="G284" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>3.18772172927856</v>
+        <v>3.18772149085999</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808663368225</v>
+        <v>3.80808687210083</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>3.75082206726074</v>
+        <v>3.75082230567932</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G340" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492581367493</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G370" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G371" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G377" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G388" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G394" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.50267672538757</v>
+        <v>3.50267648696899</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G407" t="n">
-        <v>3.65538167953491</v>
+        <v>3.65538144111633</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G409" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492581367493</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G411" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G414" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>3.65538167953491</v>
+        <v>3.65538144111633</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492581367493</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G425" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G433" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G469" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G488" t="n">
-        <v>3.45092940330505</v>
+        <v>3.45092964172363</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.5</v>
       </c>
       <c r="G490" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.5</v>
       </c>
       <c r="G491" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426473617554</v>
+        <v>3.35426497459412</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G501" t="n">
-        <v>3.45092940330505</v>
+        <v>3.45092964172363</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>3.52826166152954</v>
+        <v>3.52826142311096</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G507" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G524" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G526" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G530" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.75059056282043</v>
+        <v>3.75059032440186</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G570" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G571" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G573" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G592" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G593" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.5</v>
       </c>
       <c r="G604" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G611" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G639" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225507736206</v>
+        <v>4.13225555419922</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809734344482</v>
+        <v>4.32809686660767</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.6806116104126</v>
+        <v>4.68061208724976</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71977996826172</v>
+        <v>4.71978044509888</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770086288452</v>
+        <v>4.81770038604736</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875951766968</v>
+        <v>5.23875999450684</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356199264526</v>
+        <v>5.48356151580811</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -36668,6 +36668,32 @@
         <v>6.19999980926514</v>
       </c>
       <c r="H1396" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1397" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C1397" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1397" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -551,7 +551,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51699256896973</v>
+        <v>3.51699233055115</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G20" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>3.38337540626526</v>
+        <v>3.38337564468384</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.35951495170593</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611083984375</v>
+        <v>3.32611107826233</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G40" t="n">
-        <v>3.75559449195862</v>
+        <v>3.75559425354004</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G41" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060997009277</v>
+        <v>3.65060973167419</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.75</v>
       </c>
       <c r="G45" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902884483337</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380126953125</v>
+        <v>3.58380103111267</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.60766100883484</v>
+        <v>3.60766124725342</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G58" t="n">
-        <v>3.51699256896973</v>
+        <v>3.51699233055115</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>3.54562449455261</v>
+        <v>3.54562473297119</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.41200733184814</v>
+        <v>3.41200757026672</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G69" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G70" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>3.29270648956299</v>
+        <v>3.29270672798157</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495581626892</v>
+        <v>3.45495557785034</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380126953125</v>
+        <v>3.58380103111267</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.0037407875061</v>
+        <v>4.00374031066895</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>3.9798800945282</v>
+        <v>3.97988033294678</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307187080383</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033643722534</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896836280823</v>
+        <v>3.99896883964539</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G126" t="n">
-        <v>3.92738771438599</v>
+        <v>3.92738747596741</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033643722534</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G130" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033643722534</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.96556448936462</v>
+        <v>3.96556425094604</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307187080383</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307187080383</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.0037407875061</v>
+        <v>4.00374031066895</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.94170451164246</v>
+        <v>3.94170427322388</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95601987838745</v>
+        <v>3.95602011680603</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896836280823</v>
+        <v>3.99896883964539</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760028839111</v>
+        <v>4.02760076522827</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>4.01805639266968</v>
+        <v>4.01805686950684</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942399024963</v>
+        <v>3.98942446708679</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.94170451164246</v>
+        <v>3.94170427322388</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.8748950958252</v>
+        <v>3.87489533424377</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.88443994522095</v>
+        <v>3.88443970680237</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G158" t="n">
-        <v>3.84626317024231</v>
+        <v>3.84626340866089</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>3.8748950958252</v>
+        <v>3.87489533424377</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.82240295410156</v>
+        <v>3.82240319252014</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>3.82240295410156</v>
+        <v>3.82240319252014</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G171" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>3.64106559753418</v>
+        <v>3.64106583595276</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.60766100883484</v>
+        <v>3.60766124725342</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G175" t="n">
-        <v>3.61243319511414</v>
+        <v>3.61243343353271</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>3.55516862869263</v>
+        <v>3.55516886711121</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383127212524</v>
+        <v>3.3738317489624</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G193" t="n">
-        <v>3.51699256896973</v>
+        <v>3.51699233055115</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G195" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G207" t="n">
-        <v>3.45018410682678</v>
+        <v>3.4501838684082</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G212" t="n">
-        <v>3.55516862869263</v>
+        <v>3.55516886711121</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G215" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.75</v>
       </c>
       <c r="G224" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902884483337</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.75</v>
       </c>
       <c r="G225" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902884483337</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>3.35951495170593</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G239" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G243" t="n">
-        <v>3.23544239997864</v>
+        <v>3.23544216156006</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495581626892</v>
+        <v>3.45495557785034</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G263" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G267" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G271" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>3.35951495170593</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>3.23544239997864</v>
+        <v>3.23544216156006</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G286" t="n">
-        <v>3.23544239997864</v>
+        <v>3.23544216156006</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G287" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>3.18772172927856</v>
+        <v>3.18772149085999</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G293" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G303" t="n">
-        <v>3.82717537879944</v>
+        <v>3.82717514038086</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G305" t="n">
-        <v>3.84626317024231</v>
+        <v>3.84626340866089</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>3.82717537879944</v>
+        <v>3.82717514038086</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.82717537879944</v>
+        <v>3.82717514038086</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>3.7508225440979</v>
+        <v>3.75082230567932</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>3.84626317024231</v>
+        <v>3.84626340866089</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G334" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G335" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G336" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G337" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G362" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036620140076</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G372" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G373" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G388" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G391" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G395" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G400" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G407" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.75</v>
       </c>
       <c r="G408" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902884483337</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G417" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>3.7409234046936</v>
+        <v>3.74092364311218</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G425" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G428" t="n">
-        <v>3.7409234046936</v>
+        <v>3.74092364311218</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G433" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G461" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G469" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059608459473</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G488" t="n">
-        <v>3.45092940330505</v>
+        <v>3.45092964172363</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.5</v>
       </c>
       <c r="G490" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.5</v>
       </c>
       <c r="G491" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31559920310974</v>
+        <v>3.31559896469116</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G497" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G498" t="n">
-        <v>3.36393165588379</v>
+        <v>3.36393141746521</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426473617554</v>
+        <v>3.35426497459412</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G501" t="n">
-        <v>3.45092940330505</v>
+        <v>3.45092964172363</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059608459473</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>3.52826166152954</v>
+        <v>3.52826142311096</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G505" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G507" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G515" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>3.68292474746704</v>
+        <v>3.68292498588562</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G519" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>3.78925609588623</v>
+        <v>3.78925585746765</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G530" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.75059056282043</v>
+        <v>3.75059032440186</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059608459473</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G570" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G571" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G573" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G581" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G582" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G583" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G592" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G593" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.5</v>
       </c>
       <c r="G604" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G611" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>3.36393165588379</v>
+        <v>3.36393141746521</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G634" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G635" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G639" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G657" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225507736206</v>
+        <v>4.13225555419922</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809734344482</v>
+        <v>4.32809686660767</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.6806116104126</v>
+        <v>4.68061208724976</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71977996826172</v>
+        <v>4.71978044509888</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770086288452</v>
+        <v>4.81770038604736</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875951766968</v>
+        <v>5.23875999450684</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356199264526</v>
+        <v>5.48356151580811</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -36798,6 +36798,32 @@
         <v>6.09999990463257</v>
       </c>
       <c r="H1401" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1402" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C1402" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F1402" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1402" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32680,8 +32680,31 @@
       <c r="E1405" t="n">
         <v>5.84999990463257</v>
       </c>
-      <c r="F1405"/>
+      <c r="F1405" t="n">
+        <v>5.84999990463257</v>
+      </c>
       <c r="G1405" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1406" t="n">
+        <v>14750</v>
+      </c>
+      <c r="C1406" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="F1406"/>
+      <c r="G1406" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32703,8 +32703,31 @@
       <c r="E1406" t="n">
         <v>5.80000019073486</v>
       </c>
-      <c r="F1406"/>
+      <c r="F1406" t="n">
+        <v>6.09999990463257</v>
+      </c>
       <c r="G1406" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1407" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1407" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="F1407"/>
+      <c r="G1407" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32726,8 +32726,31 @@
       <c r="E1407" t="n">
         <v>6.15000009536743</v>
       </c>
-      <c r="F1407"/>
+      <c r="F1407" t="n">
+        <v>5.94999980926514</v>
+      </c>
       <c r="G1407" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1408" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C1408" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="F1408"/>
+      <c r="G1408" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32749,8 +32749,31 @@
       <c r="E1408" t="n">
         <v>5.90000009536743</v>
       </c>
-      <c r="F1408"/>
+      <c r="F1408" t="n">
+        <v>5.90000009536743</v>
+      </c>
       <c r="G1408" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1409" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1409" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="F1409"/>
+      <c r="G1409" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -32779,6 +32779,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1410">
+      <c r="A1410" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1410" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1410" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="G1410" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G5" t="n">
-        <v>3.19249367713928</v>
+        <v>3.19249391555786</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51699256896973</v>
+        <v>3.51699233055115</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246391296387</v>
+        <v>3.40246367454529</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G10" t="n">
-        <v>3.42632365226746</v>
+        <v>3.42632389068604</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109560012817</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611083984375</v>
+        <v>3.32611107826233</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109560012817</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G40" t="n">
-        <v>3.75559449195862</v>
+        <v>3.75559425354004</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060997009277</v>
+        <v>3.65060949325562</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.75</v>
       </c>
       <c r="G45" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902884483337</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G46" t="n">
-        <v>3.6458375453949</v>
+        <v>3.64583730697632</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380126953125</v>
+        <v>3.58380103111267</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197756767273</v>
+        <v>3.62197732925415</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.60766124725342</v>
+        <v>3.60766100883484</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G58" t="n">
-        <v>3.51699256896973</v>
+        <v>3.51699233055115</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>3.54562449455261</v>
+        <v>3.54562473297119</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836016654968</v>
+        <v>3.4883599281311</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G69" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G70" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109560012817</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G77" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677975654602</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677975654602</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>3.29270672798157</v>
+        <v>3.29270696640015</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G93" t="n">
-        <v>3.28793454170227</v>
+        <v>3.28793478012085</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677975654602</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G97" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G101" t="n">
-        <v>3.52653670310974</v>
+        <v>3.52653622627258</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495581626892</v>
+        <v>3.45495557785034</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380126953125</v>
+        <v>3.58380103111267</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G111" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.08486557006836</v>
+        <v>4.08486461639404</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>3.97988057136536</v>
+        <v>3.97988033294678</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G121" t="n">
-        <v>4.06577777862549</v>
+        <v>4.06577730178833</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896883964539</v>
+        <v>3.99896836280823</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>3.92261576652527</v>
+        <v>3.92261600494385</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.93215990066528</v>
+        <v>3.93215918540955</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G130" t="n">
-        <v>3.93215990066528</v>
+        <v>3.93215918540955</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.96556448936462</v>
+        <v>3.96556425094604</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.00851249694824</v>
+        <v>4.00851202011108</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92261576652527</v>
+        <v>3.92261600494385</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93215990066528</v>
+        <v>3.93215918540955</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.94170427322388</v>
+        <v>3.94170379638672</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95601987838745</v>
+        <v>3.95602011680603</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896883964539</v>
+        <v>3.99896836280823</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124816894531</v>
+        <v>3.95124769210815</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124816894531</v>
+        <v>3.95124769210815</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00851249694824</v>
+        <v>4.00851202011108</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760076522827</v>
+        <v>4.02760028839111</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>4.00851249694824</v>
+        <v>4.00851202011108</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942399024963</v>
+        <v>3.98942446708679</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.94170427322388</v>
+        <v>3.94170379638672</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.87489533424377</v>
+        <v>3.8748950958252</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.88443970680237</v>
+        <v>3.88443946838379</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G158" t="n">
-        <v>3.84626340866089</v>
+        <v>3.84626317024231</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>3.87489533424377</v>
+        <v>3.8748950958252</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.8939836025238</v>
+        <v>3.89398312568665</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G166" t="n">
-        <v>3.7889986038208</v>
+        <v>3.78899884223938</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G169" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G171" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>3.64106583595276</v>
+        <v>3.6410653591156</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.60766124725342</v>
+        <v>3.60766100883484</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G175" t="n">
-        <v>3.61243343353271</v>
+        <v>3.61243319511414</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.57425689697266</v>
+        <v>3.57425665855408</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>3.55516862869263</v>
+        <v>3.55516886711121</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G193" t="n">
-        <v>3.51699256896973</v>
+        <v>3.51699233055115</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G195" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G197" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677975654602</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G207" t="n">
-        <v>3.4501838684082</v>
+        <v>3.45018362998962</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G208" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G212" t="n">
-        <v>3.55516862869263</v>
+        <v>3.55516886711121</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G216" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G217" t="n">
-        <v>3.57425689697266</v>
+        <v>3.57425665855408</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G222" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.75</v>
       </c>
       <c r="G224" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902884483337</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.75</v>
       </c>
       <c r="G225" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902884483337</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28793454170227</v>
+        <v>3.28793478012085</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G239" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495581626892</v>
+        <v>3.45495557785034</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G267" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G269" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G270" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G271" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G287" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677975654602</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G305" t="n">
-        <v>3.84626340866089</v>
+        <v>3.84626317024231</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>3.75082230567932</v>
+        <v>3.7508225440979</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>3.84626340866089</v>
+        <v>3.84626317024231</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>3.7889986038208</v>
+        <v>3.78899884223938</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>3.7889986038208</v>
+        <v>3.78899884223938</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G357" t="n">
-        <v>3.7889986038208</v>
+        <v>3.78899884223938</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>3.6458375453949</v>
+        <v>3.64583730697632</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G370" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G371" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G372" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G373" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G374" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G375" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G388" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905956268311</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G390" t="n">
-        <v>3.25453042984009</v>
+        <v>3.25453066825867</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G391" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G394" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G395" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677975654602</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G400" t="n">
-        <v>3.49313235282898</v>
+        <v>3.4931321144104</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.75</v>
       </c>
       <c r="G408" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902884483337</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G409" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G411" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G414" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G417" t="n">
-        <v>3.63629341125488</v>
+        <v>3.63629364967346</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>3.7409234046936</v>
+        <v>3.74092364311218</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G428" t="n">
-        <v>3.7409234046936</v>
+        <v>3.74092364311218</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G485" t="n">
-        <v>3.47026252746582</v>
+        <v>3.4702627658844</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31559920310974</v>
+        <v>3.31559896469116</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G497" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G498" t="n">
-        <v>3.36393165588379</v>
+        <v>3.36393141746521</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G505" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G521" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G522" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G523" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G524" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G525" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G526" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G537" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G538" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G577" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G589" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G595" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>3.36393165588379</v>
+        <v>3.36393141746521</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G634" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G635" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G643" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G657" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G669" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -37084,6 +37084,32 @@
         <v>5.69999980926514</v>
       </c>
       <c r="H1412" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1413" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C1413" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="F1413" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="G1413" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="H1413" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -525,7 +525,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G10" t="n">
-        <v>3.42632389068604</v>
+        <v>3.42632365226746</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36905956268311</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G20" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>3.38337564468384</v>
+        <v>3.38337540626526</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951495170593</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611107826233</v>
+        <v>3.32611083984375</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G40" t="n">
-        <v>3.75559425354004</v>
+        <v>3.75559449195862</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G41" t="n">
-        <v>3.73173427581787</v>
+        <v>3.73173451423645</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060949325562</v>
+        <v>3.65060997009277</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.75</v>
       </c>
       <c r="G45" t="n">
-        <v>3.57902884483337</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64583730697632</v>
+        <v>3.6458375453949</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197732925415</v>
+        <v>3.62197756767273</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G58" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>3.54562473297119</v>
+        <v>3.54562449455261</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.4883599281311</v>
+        <v>3.48836016654968</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.41200757026672</v>
+        <v>3.41200733184814</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G69" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G70" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G74" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407480239868</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407480239868</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839040756226</v>
+        <v>3.27839064598083</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839040756226</v>
+        <v>3.27839064598083</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>3.29270696640015</v>
+        <v>3.29270648956299</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G93" t="n">
-        <v>3.28793478012085</v>
+        <v>3.28793454170227</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G101" t="n">
-        <v>3.52653622627258</v>
+        <v>3.52653646469116</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495557785034</v>
+        <v>3.45495581626892</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.00374031066895</v>
+        <v>4.0037407875061</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.08486461639404</v>
+        <v>4.08486557006836</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>3.97988033294678</v>
+        <v>3.9798800945282</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>3.91307139396667</v>
+        <v>3.91307163238525</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>3.90352773666382</v>
+        <v>3.9035279750824</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.97033596038818</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G126" t="n">
-        <v>3.92738747596741</v>
+        <v>3.92738771438599</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.93215918540955</v>
+        <v>3.9321596622467</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.97033596038818</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G130" t="n">
-        <v>3.93215918540955</v>
+        <v>3.9321596622467</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.97033596038818</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.96556425094604</v>
+        <v>3.96556448936462</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.00851202011108</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>3.91307139396667</v>
+        <v>3.91307163238525</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>3.91307139396667</v>
+        <v>3.91307163238525</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.00374031066895</v>
+        <v>4.0037407875061</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93215918540955</v>
+        <v>3.9321596622467</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.94170379638672</v>
+        <v>3.94170451164246</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95602011680603</v>
+        <v>3.95601987838745</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124769210815</v>
+        <v>3.95124816894531</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124769210815</v>
+        <v>3.95124816894531</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00851202011108</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>4.00851202011108</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942446708679</v>
+        <v>3.98942399024963</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.94170379638672</v>
+        <v>3.94170451164246</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.88443946838379</v>
+        <v>3.88443994522095</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808663368225</v>
+        <v>3.80808687210083</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.89398312568665</v>
+        <v>3.89398336410522</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.82240319252014</v>
+        <v>3.82240295410156</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>3.82240319252014</v>
+        <v>3.82240295410156</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G166" t="n">
-        <v>3.78899884223938</v>
+        <v>3.7889986038208</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G171" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>3.6410653591156</v>
+        <v>3.64106559753418</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.57425665855408</v>
+        <v>3.57425689697266</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>3.55516886711121</v>
+        <v>3.55516862869263</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G180" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383151054382</v>
+        <v>3.37383127212524</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G193" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G195" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G197" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>3.36905956268311</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G207" t="n">
-        <v>3.45018362998962</v>
+        <v>3.45018410682678</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G212" t="n">
-        <v>3.55516886711121</v>
+        <v>3.55516862869263</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G215" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G216" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G217" t="n">
-        <v>3.57425665855408</v>
+        <v>3.57425689697266</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G222" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.75</v>
       </c>
       <c r="G224" t="n">
-        <v>3.57902884483337</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.75</v>
       </c>
       <c r="G225" t="n">
-        <v>3.57902884483337</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28793478012085</v>
+        <v>3.28793454170227</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951495170593</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G239" t="n">
-        <v>3.36905956268311</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>3.36905956268311</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G243" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>3.36905956268311</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495557785034</v>
+        <v>3.45495581626892</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G258" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>3.60288906097412</v>
+        <v>3.6028892993927</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>3.60288906097412</v>
+        <v>3.6028892993927</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G263" t="n">
-        <v>3.73173427581787</v>
+        <v>3.73173451423645</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.59811735153198</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G267" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G269" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G270" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G271" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951495170593</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407480239868</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407480239868</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G286" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.59811735153198</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G293" t="n">
-        <v>3.73173427581787</v>
+        <v>3.73173451423645</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808663368225</v>
+        <v>3.80808687210083</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G334" t="n">
-        <v>3.73173427581787</v>
+        <v>3.73173451423645</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G335" t="n">
-        <v>3.73173427581787</v>
+        <v>3.73173451423645</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G336" t="n">
-        <v>3.73173427581787</v>
+        <v>3.73173451423645</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G337" t="n">
-        <v>3.73173427581787</v>
+        <v>3.73173451423645</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>3.78899884223938</v>
+        <v>3.7889986038208</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>3.78899884223938</v>
+        <v>3.7889986038208</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G357" t="n">
-        <v>3.78899884223938</v>
+        <v>3.7889986038208</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G362" t="n">
-        <v>3.73173427581787</v>
+        <v>3.73173451423645</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>3.64583730697632</v>
+        <v>3.6458375453949</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G370" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G371" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G372" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G373" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.59811735153198</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.59811735153198</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G388" t="n">
-        <v>3.36905956268311</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.20680999755859</v>
+        <v>3.20680975914001</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G390" t="n">
-        <v>3.25453066825867</v>
+        <v>3.25453042984009</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G391" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G394" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G395" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G400" t="n">
-        <v>3.4931321144104</v>
+        <v>3.49313235282898</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.75</v>
       </c>
       <c r="G408" t="n">
-        <v>3.57902884483337</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G409" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G411" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G414" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G417" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>3.74092364311218</v>
+        <v>3.7409234046936</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G425" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G428" t="n">
-        <v>3.74092364311218</v>
+        <v>3.7409234046936</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G433" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692719459534</v>
+        <v>3.56692743301392</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692719459534</v>
+        <v>3.56692743301392</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G469" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G485" t="n">
-        <v>3.4702627658844</v>
+        <v>3.47026252746582</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G488" t="n">
-        <v>3.45092964172363</v>
+        <v>3.45092940330505</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.5</v>
       </c>
       <c r="G490" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.5</v>
       </c>
       <c r="G491" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31559896469116</v>
+        <v>3.31559920310974</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G497" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G498" t="n">
-        <v>3.36393141746521</v>
+        <v>3.36393165588379</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426497459412</v>
+        <v>3.35426473617554</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G501" t="n">
-        <v>3.45092964172363</v>
+        <v>3.45092940330505</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>3.52826142311096</v>
+        <v>3.52826166152954</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G505" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G507" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G521" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G522" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G523" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G525" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G530" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G537" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G538" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.75059032440186</v>
+        <v>3.75059056282043</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G570" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G571" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G573" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G577" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G589" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G592" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G593" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G595" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.5</v>
       </c>
       <c r="G604" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G611" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>3.36393141746521</v>
+        <v>3.36393165588379</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G634" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G635" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G639" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G643" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G657" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G669" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932498931885</v>
+        <v>3.79932522773743</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932498931885</v>
+        <v>3.79932522773743</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225555419922</v>
+        <v>4.13225507736206</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183973312378</v>
+        <v>4.15183925628662</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809686660767</v>
+        <v>4.32809734344482</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.68061208724976</v>
+        <v>4.6806116104126</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71978044509888</v>
+        <v>4.71977996826172</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183973312378</v>
+        <v>4.15183925628662</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770038604736</v>
+        <v>4.81770086288452</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875999450684</v>
+        <v>5.23875951766968</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356151580811</v>
+        <v>5.48356199264526</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772068023682</v>
+        <v>5.28772020339966</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772068023682</v>
+        <v>5.28772020339966</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -37110,6 +37110,32 @@
         <v>5.84999990463257</v>
       </c>
       <c r="H1413" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1414" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1414" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="F1414" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="G1414" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="H1414" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.04456067085266</v>
+        <v>3.04456090927124</v>
       </c>
       <c r="H3" t="n">
         <v>230500</v>
@@ -543,7 +543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130888938904</v>
       </c>
       <c r="H6" t="n">
         <v>552500</v>
@@ -630,7 +630,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246343612671</v>
+        <v>3.40246367454529</v>
       </c>
       <c r="H9" t="n">
         <v>56500</v>
@@ -659,7 +659,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G10" t="n">
-        <v>3.42632389068604</v>
+        <v>3.42632365226746</v>
       </c>
       <c r="H10" t="n">
         <v>32500</v>
@@ -688,7 +688,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H11" t="n">
         <v>56500</v>
@@ -804,7 +804,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H15" t="n">
         <v>53000</v>
@@ -833,7 +833,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.31179451942444</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H16" t="n">
         <v>34500</v>
@@ -862,7 +862,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.29747867584229</v>
+        <v>3.29747843742371</v>
       </c>
       <c r="H17" t="n">
         <v>15000</v>
@@ -920,7 +920,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H19" t="n">
         <v>43500</v>
@@ -1007,7 +1007,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H22" t="n">
         <v>32500</v>
@@ -1036,7 +1036,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G23" t="n">
-        <v>3.34519934654236</v>
+        <v>3.34519910812378</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1094,7 +1094,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H25" t="n">
         <v>13500</v>
@@ -1123,7 +1123,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.35951495170593</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H26" t="n">
         <v>19500</v>
@@ -1152,7 +1152,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611107826233</v>
+        <v>3.32611083984375</v>
       </c>
       <c r="H27" t="n">
         <v>10000</v>
@@ -1181,7 +1181,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H28" t="n">
         <v>14000</v>
@@ -1210,7 +1210,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G29" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723562240601</v>
       </c>
       <c r="H29" t="n">
         <v>12000</v>
@@ -1268,7 +1268,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H31" t="n">
         <v>14000</v>
@@ -1326,7 +1326,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H33" t="n">
         <v>25000</v>
@@ -1355,7 +1355,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H34" t="n">
         <v>6000</v>
@@ -1384,7 +1384,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H35" t="n">
         <v>51000</v>
@@ -1471,7 +1471,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H38" t="n">
         <v>12500</v>
@@ -1500,7 +1500,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H39" t="n">
         <v>158500</v>
@@ -1558,7 +1558,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G41" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H41" t="n">
         <v>28000</v>
@@ -1587,7 +1587,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H42" t="n">
         <v>19500</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060973167419</v>
+        <v>3.65060949325562</v>
       </c>
       <c r="H43" t="n">
         <v>14500</v>
@@ -1645,7 +1645,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H44" t="n">
         <v>20000</v>
@@ -1761,7 +1761,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608083724976</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1819,7 +1819,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197732925415</v>
+        <v>3.62197756767273</v>
       </c>
       <c r="H50" t="n">
         <v>6500</v>
@@ -1848,7 +1848,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.60766100883484</v>
+        <v>3.60766124725342</v>
       </c>
       <c r="H51" t="n">
         <v>24500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1906,7 +1906,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H53" t="n">
         <v>14000</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130888938904</v>
       </c>
       <c r="H54" t="n">
         <v>19000</v>
@@ -1993,7 +1993,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608083724976</v>
       </c>
       <c r="H56" t="n">
         <v>9000</v>
@@ -2138,7 +2138,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G61" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723562240601</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2254,7 +2254,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836016654968</v>
+        <v>3.48836040496826</v>
       </c>
       <c r="H65" t="n">
         <v>22000</v>
@@ -2341,7 +2341,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.41200757026672</v>
+        <v>3.4120078086853</v>
       </c>
       <c r="H68" t="n">
         <v>16500</v>
@@ -2486,7 +2486,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723562240601</v>
       </c>
       <c r="H73" t="n">
         <v>5000</v>
@@ -2515,7 +2515,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G74" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H75" t="n">
         <v>6000</v>
@@ -2602,7 +2602,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G77" t="n">
-        <v>3.41677975654602</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H77" t="n">
         <v>67000</v>
@@ -2631,7 +2631,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.41677975654602</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H78" t="n">
         <v>32000</v>
@@ -2660,7 +2660,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G79" t="n">
-        <v>3.35474324226379</v>
+        <v>3.35474348068237</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2718,7 +2718,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H82" t="n">
         <v>16000</v>
@@ -2776,7 +2776,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H83" t="n">
         <v>4500</v>
@@ -2805,7 +2805,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H84" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.31179451942444</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H85" t="n">
         <v>43000</v>
@@ -2863,7 +2863,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407480239868</v>
       </c>
       <c r="H86" t="n">
         <v>43000</v>
@@ -2921,7 +2921,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407480239868</v>
       </c>
       <c r="H88" t="n">
         <v>27500</v>
@@ -2950,7 +2950,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839040756226</v>
+        <v>3.27839064598083</v>
       </c>
       <c r="H89" t="n">
         <v>4500</v>
@@ -2979,7 +2979,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839040756226</v>
+        <v>3.27839064598083</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3124,7 +3124,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>3.32133865356445</v>
+        <v>3.32133913040161</v>
       </c>
       <c r="H95" t="n">
         <v>12000</v>
@@ -3153,7 +3153,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>3.41677975654602</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H96" t="n">
         <v>51000</v>
@@ -3182,7 +3182,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G97" t="n">
-        <v>3.44541168212891</v>
+        <v>3.44541192054749</v>
       </c>
       <c r="H97" t="n">
         <v>43000</v>
@@ -3211,7 +3211,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H98" t="n">
         <v>31500</v>
@@ -3298,7 +3298,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G101" t="n">
-        <v>3.52653622627258</v>
+        <v>3.52653646469116</v>
       </c>
       <c r="H101" t="n">
         <v>11500</v>
@@ -3327,7 +3327,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495557785034</v>
+        <v>3.45495581626892</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3356,7 +3356,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G103" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723562240601</v>
       </c>
       <c r="H103" t="n">
         <v>17500</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3501,7 +3501,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H108" t="n">
         <v>18000</v>
@@ -3588,7 +3588,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G111" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H111" t="n">
         <v>28000</v>
@@ -3646,7 +3646,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H113" t="n">
         <v>30500</v>
@@ -3849,7 +3849,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>3.9035279750824</v>
+        <v>3.90352773666382</v>
       </c>
       <c r="H120" t="n">
         <v>8500</v>
@@ -3907,7 +3907,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G122" t="n">
-        <v>4.11349725723267</v>
+        <v>4.11349678039551</v>
       </c>
       <c r="H122" t="n">
         <v>20500</v>
@@ -3965,7 +3965,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.97033596038818</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H124" t="n">
         <v>38000</v>
@@ -3994,7 +3994,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896836280823</v>
+        <v>3.99896860122681</v>
       </c>
       <c r="H125" t="n">
         <v>57500</v>
@@ -4023,7 +4023,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G126" t="n">
-        <v>3.92738795280457</v>
+        <v>3.92738771438599</v>
       </c>
       <c r="H126" t="n">
         <v>26000</v>
@@ -4110,7 +4110,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.97033596038818</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H129" t="n">
         <v>213000</v>
@@ -4168,7 +4168,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.97033596038818</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H131" t="n">
         <v>31000</v>
@@ -4197,7 +4197,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079254150391</v>
+        <v>3.96079182624817</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.96556425094604</v>
+        <v>3.9655647277832</v>
       </c>
       <c r="H133" t="n">
         <v>15500</v>
@@ -4313,7 +4313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079254150391</v>
+        <v>3.96079182624817</v>
       </c>
       <c r="H136" t="n">
         <v>6500</v>
@@ -4458,7 +4458,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.94170427322388</v>
+        <v>3.9417040348053</v>
       </c>
       <c r="H141" t="n">
         <v>4000</v>
@@ -4487,7 +4487,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95602011680603</v>
+        <v>3.95602035522461</v>
       </c>
       <c r="H142" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896836280823</v>
+        <v>3.99896860122681</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124816894531</v>
+        <v>3.95124793052673</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4574,7 +4574,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124816894531</v>
+        <v>3.95124793052673</v>
       </c>
       <c r="H145" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079254150391</v>
+        <v>3.96079182624817</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4661,7 +4661,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760076522827</v>
+        <v>4.02760028839111</v>
       </c>
       <c r="H148" t="n">
         <v>15500</v>
@@ -4748,7 +4748,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942446708679</v>
+        <v>3.98942422866821</v>
       </c>
       <c r="H151" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.94170427322388</v>
+        <v>3.9417040348053</v>
       </c>
       <c r="H152" t="n">
         <v>9500</v>
@@ -4893,7 +4893,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808663368225</v>
+        <v>3.80808711051941</v>
       </c>
       <c r="H156" t="n">
         <v>29500</v>
@@ -4951,7 +4951,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G158" t="n">
-        <v>3.84626317024231</v>
+        <v>3.84626340866089</v>
       </c>
       <c r="H158" t="n">
         <v>6000</v>
@@ -5038,7 +5038,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.89398312568665</v>
+        <v>3.89398336410522</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.82240295410156</v>
+        <v>3.82240319252014</v>
       </c>
       <c r="H164" t="n">
         <v>3500</v>
@@ -5154,7 +5154,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>3.82240295410156</v>
+        <v>3.82240319252014</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5270,7 +5270,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G169" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H169" t="n">
         <v>22000</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G171" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H171" t="n">
         <v>5000</v>
@@ -5386,7 +5386,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.60766100883484</v>
+        <v>3.60766124725342</v>
       </c>
       <c r="H173" t="n">
         <v>6000</v>
@@ -5473,7 +5473,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H176" t="n">
         <v>3000</v>
@@ -5531,7 +5531,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.57425665855408</v>
+        <v>3.57425689697266</v>
       </c>
       <c r="H178" t="n">
         <v>19000</v>
@@ -5560,7 +5560,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>3.55516886711121</v>
+        <v>3.55516862869263</v>
       </c>
       <c r="H179" t="n">
         <v>12500</v>
@@ -5589,7 +5589,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G180" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130888938904</v>
       </c>
       <c r="H180" t="n">
         <v>8000</v>
@@ -5676,7 +5676,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H183" t="n">
         <v>11500</v>
@@ -5705,7 +5705,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H184" t="n">
         <v>17000</v>
@@ -5734,7 +5734,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383151054382</v>
+        <v>3.37383127212524</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5763,7 +5763,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.30225086212158</v>
+        <v>3.302250623703</v>
       </c>
       <c r="H186" t="n">
         <v>18000</v>
@@ -5821,7 +5821,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H188" t="n">
         <v>10500</v>
@@ -5850,7 +5850,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H189" t="n">
         <v>3000</v>
@@ -5937,7 +5937,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H192" t="n">
         <v>1500</v>
@@ -6140,7 +6140,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130888938904</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608083724976</v>
       </c>
       <c r="H200" t="n">
         <v>3500</v>
@@ -6256,7 +6256,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H203" t="n">
         <v>45000</v>
@@ -6285,7 +6285,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G204" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586754798889</v>
       </c>
       <c r="H204" t="n">
         <v>34000</v>
@@ -6314,7 +6314,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.41677975654602</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6401,7 +6401,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G208" t="n">
-        <v>3.44541168212891</v>
+        <v>3.44541192054749</v>
       </c>
       <c r="H208" t="n">
         <v>2000</v>
@@ -6430,7 +6430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H209" t="n">
         <v>5000</v>
@@ -6459,7 +6459,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.50744867324829</v>
+        <v>3.50744819641113</v>
       </c>
       <c r="H210" t="n">
         <v>18000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6517,7 +6517,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G212" t="n">
-        <v>3.55516886711121</v>
+        <v>3.55516862869263</v>
       </c>
       <c r="H212" t="n">
         <v>20000</v>
@@ -6546,7 +6546,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H213" t="n">
         <v>4000</v>
@@ -6662,7 +6662,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G217" t="n">
-        <v>3.57425665855408</v>
+        <v>3.57425689697266</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130888938904</v>
       </c>
       <c r="H223" t="n">
         <v>7500</v>
@@ -6923,7 +6923,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H226" t="n">
         <v>21000</v>
@@ -6952,7 +6952,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H227" t="n">
         <v>40000</v>
@@ -6981,7 +6981,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586754798889</v>
       </c>
       <c r="H228" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586754798889</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586754798889</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>3.35951495170593</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H233" t="n">
         <v>8500</v>
@@ -7155,7 +7155,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H234" t="n">
         <v>3000</v>
@@ -7213,7 +7213,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>3.44541168212891</v>
+        <v>3.44541192054749</v>
       </c>
       <c r="H236" t="n">
         <v>4000</v>
@@ -7242,7 +7242,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H237" t="n">
         <v>3500</v>
@@ -7271,7 +7271,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32133865356445</v>
+        <v>3.32133913040161</v>
       </c>
       <c r="H238" t="n">
         <v>5000</v>
@@ -7358,7 +7358,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H241" t="n">
         <v>17500</v>
@@ -7387,7 +7387,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>3.32133865356445</v>
+        <v>3.32133913040161</v>
       </c>
       <c r="H242" t="n">
         <v>36500</v>
@@ -7474,7 +7474,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H245" t="n">
         <v>9500</v>
@@ -7503,7 +7503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7619,7 +7619,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H250" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>3.29747867584229</v>
+        <v>3.29747843742371</v>
       </c>
       <c r="H251" t="n">
         <v>4500</v>
@@ -7677,7 +7677,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>3.32133865356445</v>
+        <v>3.32133913040161</v>
       </c>
       <c r="H252" t="n">
         <v>4000</v>
@@ -7764,7 +7764,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7793,7 +7793,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G256" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586754798889</v>
       </c>
       <c r="H256" t="n">
         <v>17500</v>
@@ -7822,7 +7822,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495557785034</v>
+        <v>3.45495581626892</v>
       </c>
       <c r="H257" t="n">
         <v>9000</v>
@@ -7851,7 +7851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G258" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130888938904</v>
       </c>
       <c r="H258" t="n">
         <v>11500</v>
@@ -7938,7 +7938,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H261" t="n">
         <v>3000</v>
@@ -7967,7 +7967,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H262" t="n">
         <v>18500</v>
@@ -7996,7 +7996,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G263" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H263" t="n">
         <v>2500</v>
@@ -8141,7 +8141,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44541168212891</v>
+        <v>3.44541192054749</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8228,7 +8228,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G271" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H271" t="n">
         <v>9000</v>
@@ -8257,7 +8257,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H272" t="n">
         <v>5000</v>
@@ -8286,7 +8286,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H273" t="n">
         <v>2000</v>
@@ -8315,7 +8315,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>3.35951495170593</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H274" t="n">
         <v>1500</v>
@@ -8460,7 +8460,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H279" t="n">
         <v>9500</v>
@@ -8489,7 +8489,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407480239868</v>
       </c>
       <c r="H281" t="n">
         <v>1000</v>
@@ -8547,7 +8547,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407480239868</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G287" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H287" t="n">
         <v>2000</v>
@@ -8721,7 +8721,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>3.18772172927856</v>
+        <v>3.18772196769714</v>
       </c>
       <c r="H288" t="n">
         <v>500</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.41677975654602</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8779,7 +8779,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H290" t="n">
         <v>10500</v>
@@ -8866,7 +8866,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G293" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H293" t="n">
         <v>11500</v>
@@ -8895,7 +8895,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H294" t="n">
         <v>2000</v>
@@ -8953,7 +8953,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H296" t="n">
         <v>14500</v>
@@ -8982,7 +8982,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535120010376</v>
       </c>
       <c r="H297" t="n">
         <v>30500</v>
@@ -9069,7 +9069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535120010376</v>
       </c>
       <c r="H300" t="n">
         <v>26000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535120010376</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9156,7 +9156,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G303" t="n">
-        <v>3.82717537879944</v>
+        <v>3.82717514038086</v>
       </c>
       <c r="H303" t="n">
         <v>1000</v>
@@ -9185,7 +9185,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H304" t="n">
         <v>27000</v>
@@ -9214,7 +9214,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G305" t="n">
-        <v>3.84626317024231</v>
+        <v>3.84626340866089</v>
       </c>
       <c r="H305" t="n">
         <v>10000</v>
@@ -9243,7 +9243,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>3.82717537879944</v>
+        <v>3.82717514038086</v>
       </c>
       <c r="H306" t="n">
         <v>500</v>
@@ -9272,7 +9272,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.82717537879944</v>
+        <v>3.82717514038086</v>
       </c>
       <c r="H307" t="n">
         <v>1500</v>
@@ -9301,7 +9301,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808663368225</v>
+        <v>3.80808711051941</v>
       </c>
       <c r="H308" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H309" t="n">
         <v>13500</v>
@@ -9359,7 +9359,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H310" t="n">
         <v>8000</v>
@@ -9475,7 +9475,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9678,7 +9678,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H321" t="n">
         <v>3500</v>
@@ -9707,7 +9707,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>3.84626317024231</v>
+        <v>3.84626340866089</v>
       </c>
       <c r="H322" t="n">
         <v>1000</v>
@@ -9823,7 +9823,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H326" t="n">
         <v>2000</v>
@@ -9881,7 +9881,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H328" t="n">
         <v>7000</v>
@@ -9910,7 +9910,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G334" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H334" t="n">
         <v>1000</v>
@@ -10084,7 +10084,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G335" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G336" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G337" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10577,7 +10577,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H352" t="n">
         <v>2500</v>
@@ -10780,7 +10780,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H359" t="n">
         <v>2500</v>
@@ -10867,7 +10867,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G362" t="n">
-        <v>3.73173451423645</v>
+        <v>3.73173427581787</v>
       </c>
       <c r="H362" t="n">
         <v>500</v>
@@ -10896,7 +10896,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G372" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H372" t="n">
         <v>1000</v>
@@ -11186,7 +11186,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G373" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G374" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H374" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G375" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H382" t="n">
         <v>2000</v>
@@ -11534,7 +11534,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130888938904</v>
       </c>
       <c r="H385" t="n">
         <v>7000</v>
@@ -11592,7 +11592,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H387" t="n">
         <v>43000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.20680999755859</v>
+        <v>3.20680975914001</v>
       </c>
       <c r="H389" t="n">
         <v>9500</v>
@@ -11679,7 +11679,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G390" t="n">
-        <v>3.25453066825867</v>
+        <v>3.25453042984009</v>
       </c>
       <c r="H390" t="n">
         <v>1000</v>
@@ -11708,7 +11708,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G391" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H391" t="n">
         <v>32000</v>
@@ -11737,7 +11737,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586754798889</v>
       </c>
       <c r="H392" t="n">
         <v>11500</v>
@@ -11824,7 +11824,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G395" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H395" t="n">
         <v>8500</v>
@@ -11853,7 +11853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H396" t="n">
         <v>8000</v>
@@ -11882,7 +11882,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>3.41677975654602</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11940,7 +11940,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586754798889</v>
       </c>
       <c r="H399" t="n">
         <v>4500</v>
@@ -11998,7 +11998,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12027,7 +12027,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G402" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H402" t="n">
         <v>15500</v>
@@ -12085,7 +12085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130888938904</v>
       </c>
       <c r="H404" t="n">
         <v>500</v>
@@ -12317,7 +12317,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H412" t="n">
         <v>13500</v>
@@ -12346,7 +12346,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H413" t="n">
         <v>500</v>
@@ -12462,7 +12462,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G417" t="n">
-        <v>3.63629364967346</v>
+        <v>3.63629341125488</v>
       </c>
       <c r="H417" t="n">
         <v>9000</v>
@@ -12549,7 +12549,7 @@
         <v>3.75</v>
       </c>
       <c r="G420" t="n">
-        <v>3.62492609024048</v>
+        <v>3.62492632865906</v>
       </c>
       <c r="H420" t="n">
         <v>3500</v>
@@ -12636,7 +12636,7 @@
         <v>3.75</v>
       </c>
       <c r="G423" t="n">
-        <v>3.62492609024048</v>
+        <v>3.62492632865906</v>
       </c>
       <c r="H423" t="n">
         <v>500</v>
@@ -12723,7 +12723,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H426" t="n">
         <v>1000</v>
@@ -12752,7 +12752,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H427" t="n">
         <v>2500</v>
@@ -12810,7 +12810,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.62492609024048</v>
+        <v>3.62492632865906</v>
       </c>
       <c r="H429" t="n">
         <v>5500</v>
@@ -12839,7 +12839,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H430" t="n">
         <v>4000</v>
@@ -12868,7 +12868,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H431" t="n">
         <v>500</v>
@@ -12955,7 +12955,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H434" t="n">
         <v>2000</v>
@@ -12984,7 +12984,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692719459534</v>
+        <v>3.56692743301392</v>
       </c>
       <c r="H435" t="n">
         <v>3500</v>
@@ -13216,7 +13216,7 @@
         <v>3.75</v>
       </c>
       <c r="G443" t="n">
-        <v>3.62492609024048</v>
+        <v>3.62492632865906</v>
       </c>
       <c r="H443" t="n">
         <v>2500</v>
@@ -13245,7 +13245,7 @@
         <v>3.75</v>
       </c>
       <c r="G444" t="n">
-        <v>3.62492609024048</v>
+        <v>3.62492632865906</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H447" t="n">
         <v>51500</v>
@@ -13361,7 +13361,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>3.75</v>
       </c>
       <c r="G449" t="n">
-        <v>3.62492609024048</v>
+        <v>3.62492632865906</v>
       </c>
       <c r="H449" t="n">
         <v>2500</v>
@@ -13419,7 +13419,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H454" t="n">
         <v>1000</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H455" t="n">
         <v>2500</v>
@@ -13680,7 +13680,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H459" t="n">
         <v>102000</v>
@@ -13709,7 +13709,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H460" t="n">
         <v>1000</v>
@@ -13738,7 +13738,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G461" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>3.75</v>
       </c>
       <c r="G467" t="n">
-        <v>3.62492609024048</v>
+        <v>3.62492632865906</v>
       </c>
       <c r="H467" t="n">
         <v>500</v>
@@ -13941,7 +13941,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692719459534</v>
+        <v>3.56692743301392</v>
       </c>
       <c r="H468" t="n">
         <v>2500</v>
@@ -14028,7 +14028,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H471" t="n">
         <v>8500</v>
@@ -14057,7 +14057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H472" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H474" t="n">
         <v>5500</v>
@@ -14144,7 +14144,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H475" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H476" t="n">
         <v>7500</v>
@@ -14202,7 +14202,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H477" t="n">
         <v>500</v>
@@ -14231,7 +14231,7 @@
         <v>3.75</v>
       </c>
       <c r="G478" t="n">
-        <v>3.62492609024048</v>
+        <v>3.62492632865906</v>
       </c>
       <c r="H478" t="n">
         <v>2500</v>
@@ -14260,7 +14260,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H479" t="n">
         <v>500</v>
@@ -14289,7 +14289,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H480" t="n">
         <v>10000</v>
@@ -14347,7 +14347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H482" t="n">
         <v>2500</v>
@@ -14434,7 +14434,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G485" t="n">
-        <v>3.4702627658844</v>
+        <v>3.47026228904724</v>
       </c>
       <c r="H485" t="n">
         <v>6500</v>
@@ -14463,7 +14463,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H486" t="n">
         <v>4000</v>
@@ -14492,7 +14492,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>3.42193031311035</v>
+        <v>3.42193007469177</v>
       </c>
       <c r="H487" t="n">
         <v>6000</v>
@@ -14550,7 +14550,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H489" t="n">
         <v>1000</v>
@@ -14666,7 +14666,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>3.42193031311035</v>
+        <v>3.42193007469177</v>
       </c>
       <c r="H493" t="n">
         <v>4000</v>
@@ -14695,7 +14695,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>3.42193031311035</v>
+        <v>3.42193007469177</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>3.42193031311035</v>
+        <v>3.42193007469177</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.42193031311035</v>
+        <v>3.42193007469177</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G497" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H497" t="n">
         <v>3000</v>
@@ -14811,7 +14811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G498" t="n">
-        <v>3.36393141746521</v>
+        <v>3.36393165588379</v>
       </c>
       <c r="H498" t="n">
         <v>1500</v>
@@ -14840,7 +14840,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426497459412</v>
+        <v>3.35426473617554</v>
       </c>
       <c r="H499" t="n">
         <v>6500</v>
@@ -14869,7 +14869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859521865845</v>
       </c>
       <c r="H500" t="n">
         <v>5500</v>
@@ -14927,7 +14927,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H502" t="n">
         <v>4000</v>
@@ -14956,7 +14956,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H503" t="n">
         <v>3000</v>
@@ -15304,7 +15304,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G515" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H515" t="n">
         <v>37500</v>
@@ -15362,7 +15362,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H517" t="n">
         <v>6500</v>
@@ -15391,7 +15391,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H518" t="n">
         <v>25000</v>
@@ -15420,7 +15420,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G519" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H519" t="n">
         <v>14500</v>
@@ -15449,7 +15449,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H520" t="n">
         <v>2500</v>
@@ -15594,7 +15594,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G525" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H525" t="n">
         <v>4000</v>
@@ -15710,7 +15710,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H529" t="n">
         <v>7500</v>
@@ -15768,7 +15768,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H531" t="n">
         <v>500</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H532" t="n">
         <v>6000</v>
@@ -15826,7 +15826,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H533" t="n">
         <v>5000</v>
@@ -15855,7 +15855,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H534" t="n">
         <v>2500</v>
@@ -15884,7 +15884,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H535" t="n">
         <v>1000</v>
@@ -15913,7 +15913,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H536" t="n">
         <v>500</v>
@@ -16058,7 +16058,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H541" t="n">
         <v>16500</v>
@@ -16261,7 +16261,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H548" t="n">
         <v>2500</v>
@@ -16290,7 +16290,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H549" t="n">
         <v>2500</v>
@@ -16319,7 +16319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16493,7 +16493,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H556" t="n">
         <v>4500</v>
@@ -16522,7 +16522,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H557" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H559" t="n">
         <v>2500</v>
@@ -16609,7 +16609,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H560" t="n">
         <v>2500</v>
@@ -16725,7 +16725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H565" t="n">
         <v>7000</v>
@@ -16783,7 +16783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H567" t="n">
         <v>17500</v>
@@ -16841,7 +16841,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -17044,7 +17044,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H575" t="n">
         <v>13000</v>
@@ -17131,7 +17131,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H578" t="n">
         <v>2500</v>
@@ -17160,7 +17160,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H579" t="n">
         <v>16500</v>
@@ -17189,7 +17189,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H580" t="n">
         <v>8500</v>
@@ -17218,7 +17218,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G581" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H581" t="n">
         <v>7000</v>
@@ -17247,7 +17247,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G582" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G583" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H583" t="n">
         <v>2000</v>
@@ -17305,7 +17305,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H585" t="n">
         <v>9500</v>
@@ -17363,7 +17363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H586" t="n">
         <v>5500</v>
@@ -17392,7 +17392,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H587" t="n">
         <v>2000</v>
@@ -17421,7 +17421,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H588" t="n">
         <v>5000</v>
@@ -17450,7 +17450,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G589" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859521865845</v>
       </c>
       <c r="H599" t="n">
         <v>500</v>
@@ -17769,7 +17769,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859521865845</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17798,7 +17798,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859521865845</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17856,7 +17856,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H603" t="n">
         <v>7000</v>
@@ -17943,7 +17943,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H606" t="n">
         <v>1000</v>
@@ -18001,7 +18001,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H608" t="n">
         <v>19500</v>
@@ -18117,7 +18117,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H612" t="n">
         <v>500</v>
@@ -18146,7 +18146,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H613" t="n">
         <v>500</v>
@@ -18233,7 +18233,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>3.67325830459595</v>
+        <v>3.67325854301453</v>
       </c>
       <c r="H616" t="n">
         <v>4000</v>
@@ -18262,7 +18262,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H622" t="n">
         <v>4500</v>
@@ -18494,7 +18494,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H625" t="n">
         <v>2000</v>
@@ -18697,7 +18697,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H632" t="n">
         <v>19000</v>
@@ -18726,7 +18726,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>3.36393141746521</v>
+        <v>3.36393165588379</v>
       </c>
       <c r="H633" t="n">
         <v>18000</v>
@@ -18755,7 +18755,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G634" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H634" t="n">
         <v>19000</v>
@@ -18784,7 +18784,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G635" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H635" t="n">
         <v>6000</v>
@@ -18813,7 +18813,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859521865845</v>
       </c>
       <c r="H636" t="n">
         <v>7000</v>
@@ -18871,7 +18871,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859521865845</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H646" t="n">
         <v>9000</v>
@@ -19132,7 +19132,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H647" t="n">
         <v>8500</v>
@@ -19161,7 +19161,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H650" t="n">
         <v>500</v>
@@ -19248,7 +19248,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H651" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859521865845</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G657" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H657" t="n">
         <v>500</v>
@@ -19567,7 +19567,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H662" t="n">
         <v>1000</v>
@@ -19770,7 +19770,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G669" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H669" t="n">
         <v>3500</v>
@@ -19799,7 +19799,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>3.76992321014404</v>
+        <v>3.76992297172546</v>
       </c>
       <c r="H670" t="n">
         <v>2500</v>
@@ -19944,7 +19944,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H675" t="n">
         <v>2500</v>
@@ -20060,7 +20060,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932498931885</v>
+        <v>3.79932522773743</v>
       </c>
       <c r="H679" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H681" t="n">
         <v>94000</v>
@@ -20147,7 +20147,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932498931885</v>
+        <v>3.79932522773743</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20234,7 +20234,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H687" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20524,7 +20524,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H695" t="n">
         <v>10500</v>
@@ -21104,7 +21104,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H715" t="n">
         <v>12500</v>
@@ -21133,7 +21133,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H723" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H730" t="n">
         <v>500</v>
@@ -21713,7 +21713,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H736" t="n">
         <v>2000</v>
@@ -21974,7 +21974,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22003,7 +22003,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H746" t="n">
         <v>500</v>
@@ -22061,7 +22061,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H748" t="n">
         <v>8000</v>
@@ -22090,7 +22090,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H749" t="n">
         <v>500</v>
@@ -22235,7 +22235,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H754" t="n">
         <v>7000</v>
@@ -22351,7 +22351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H758" t="n">
         <v>16000</v>
@@ -22438,7 +22438,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H761" t="n">
         <v>500</v>
@@ -22467,7 +22467,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H766" t="n">
         <v>1000</v>
@@ -22612,7 +22612,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H770" t="n">
         <v>4000</v>
@@ -22786,7 +22786,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225555419922</v>
+        <v>4.13225507736206</v>
       </c>
       <c r="H773" t="n">
         <v>41000</v>
@@ -23018,7 +23018,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H781" t="n">
         <v>8500</v>
@@ -23076,7 +23076,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H783" t="n">
         <v>16500</v>
@@ -23105,7 +23105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183973312378</v>
+        <v>4.15183925628662</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H785" t="n">
         <v>26000</v>
@@ -23163,7 +23163,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H786" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H787" t="n">
         <v>3500</v>
@@ -23221,7 +23221,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H788" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809686660767</v>
+        <v>4.32809734344482</v>
       </c>
       <c r="H790" t="n">
         <v>7500</v>
@@ -23395,7 +23395,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H794" t="n">
         <v>1000</v>
@@ -23743,7 +23743,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.68061208724976</v>
+        <v>4.6806116104126</v>
       </c>
       <c r="H808" t="n">
         <v>7500</v>
@@ -23946,7 +23946,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71978044509888</v>
+        <v>4.71977996826172</v>
       </c>
       <c r="H818" t="n">
         <v>3500</v>
@@ -24207,7 +24207,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H822" t="n">
         <v>6500</v>
@@ -24236,7 +24236,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H827" t="n">
         <v>2000</v>
@@ -24381,7 +24381,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H831" t="n">
         <v>500</v>
@@ -24497,7 +24497,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -24816,7 +24816,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H843" t="n">
         <v>500</v>
@@ -25164,7 +25164,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H855" t="n">
         <v>2000</v>
@@ -25686,7 +25686,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H873" t="n">
         <v>500</v>
@@ -25715,7 +25715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -25889,7 +25889,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183973312378</v>
+        <v>4.15183925628662</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H881" t="n">
         <v>1500</v>
@@ -25947,7 +25947,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -25976,7 +25976,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26063,7 +26063,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H886" t="n">
         <v>2000</v>
@@ -26092,7 +26092,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H887" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H889" t="n">
         <v>2500</v>
@@ -26179,7 +26179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H892" t="n">
         <v>55000</v>
@@ -26266,7 +26266,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H893" t="n">
         <v>3000</v>
@@ -26295,7 +26295,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H895" t="n">
         <v>11500</v>
@@ -26469,7 +26469,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770038604736</v>
+        <v>4.81770086288452</v>
       </c>
       <c r="H900" t="n">
         <v>6500</v>
@@ -26556,7 +26556,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26730,7 +26730,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H909" t="n">
         <v>11000</v>
@@ -27020,7 +27020,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H919" t="n">
         <v>6500</v>
@@ -27107,7 +27107,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875999450684</v>
+        <v>5.23875951766968</v>
       </c>
       <c r="H922" t="n">
         <v>19000</v>
@@ -27194,7 +27194,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356151580811</v>
+        <v>5.48356199264526</v>
       </c>
       <c r="H925" t="n">
         <v>22000</v>
@@ -27339,7 +27339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772068023682</v>
+        <v>5.28772020339966</v>
       </c>
       <c r="H930" t="n">
         <v>16000</v>
@@ -27368,7 +27368,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772068023682</v>
+        <v>5.28772020339966</v>
       </c>
       <c r="H931" t="n">
         <v>3000</v>
@@ -41410,6 +41410,35 @@
         <v>2500</v>
       </c>
       <c r="I1415" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1416" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1416" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="H1416" t="n">
+        <v>8750</v>
+      </c>
+      <c r="I1416" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.04456090927124</v>
+        <v>3.04456067085266</v>
       </c>
       <c r="H3" t="n">
         <v>230500</v>
@@ -543,7 +543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H6" t="n">
         <v>552500</v>
@@ -572,7 +572,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H7" t="n">
         <v>324500</v>
@@ -659,7 +659,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G10" t="n">
-        <v>3.42632365226746</v>
+        <v>3.42632389068604</v>
       </c>
       <c r="H10" t="n">
         <v>32500</v>
@@ -775,7 +775,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H14" t="n">
         <v>78500</v>
@@ -862,7 +862,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.29747843742371</v>
+        <v>3.29747867584229</v>
       </c>
       <c r="H17" t="n">
         <v>15000</v>
@@ -920,7 +920,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H19" t="n">
         <v>43500</v>
@@ -1007,7 +1007,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H22" t="n">
         <v>32500</v>
@@ -1036,7 +1036,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G23" t="n">
-        <v>3.34519910812378</v>
+        <v>3.34519934654236</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1094,7 +1094,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H25" t="n">
         <v>13500</v>
@@ -1268,7 +1268,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H31" t="n">
         <v>14000</v>
@@ -1326,7 +1326,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H33" t="n">
         <v>25000</v>
@@ -1355,7 +1355,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H34" t="n">
         <v>6000</v>
@@ -1384,7 +1384,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H35" t="n">
         <v>51000</v>
@@ -1500,7 +1500,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H39" t="n">
         <v>158500</v>
@@ -1587,7 +1587,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H42" t="n">
         <v>19500</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060949325562</v>
+        <v>3.65060997009277</v>
       </c>
       <c r="H43" t="n">
         <v>14500</v>
@@ -1645,7 +1645,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H44" t="n">
         <v>20000</v>
@@ -1674,7 +1674,7 @@
         <v>3.75</v>
       </c>
       <c r="G45" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902932167053</v>
       </c>
       <c r="H45" t="n">
         <v>29500</v>
@@ -1703,7 +1703,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64583730697632</v>
+        <v>3.6458375453949</v>
       </c>
       <c r="H46" t="n">
         <v>12500</v>
@@ -1732,7 +1732,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H47" t="n">
         <v>18000</v>
@@ -1761,7 +1761,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.53608083724976</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1848,7 +1848,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.60766124725342</v>
+        <v>3.60766100883484</v>
       </c>
       <c r="H51" t="n">
         <v>24500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1906,7 +1906,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H53" t="n">
         <v>14000</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H54" t="n">
         <v>19000</v>
@@ -1993,7 +1993,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.53608083724976</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H56" t="n">
         <v>9000</v>
@@ -2051,7 +2051,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G58" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H58" t="n">
         <v>18000</v>
@@ -2109,7 +2109,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H60" t="n">
         <v>16000</v>
@@ -2167,7 +2167,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H62" t="n">
         <v>9000</v>
@@ -2196,7 +2196,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>3.54562473297119</v>
+        <v>3.54562449455261</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2225,7 +2225,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H64" t="n">
         <v>1000</v>
@@ -2341,7 +2341,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.4120078086853</v>
+        <v>3.41200757026672</v>
       </c>
       <c r="H68" t="n">
         <v>16500</v>
@@ -2515,7 +2515,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G74" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2660,7 +2660,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G79" t="n">
-        <v>3.35474348068237</v>
+        <v>3.35474324226379</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2863,7 +2863,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H86" t="n">
         <v>43000</v>
@@ -2921,7 +2921,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H88" t="n">
         <v>27500</v>
@@ -3124,7 +3124,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H95" t="n">
         <v>12000</v>
@@ -3211,7 +3211,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H98" t="n">
         <v>31500</v>
@@ -3269,7 +3269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H100" t="n">
         <v>29000</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3501,7 +3501,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H108" t="n">
         <v>18000</v>
@@ -3530,7 +3530,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H109" t="n">
         <v>8500</v>
@@ -3588,7 +3588,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G111" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H111" t="n">
         <v>28000</v>
@@ -3646,7 +3646,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H113" t="n">
         <v>30500</v>
@@ -3675,7 +3675,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H114" t="n">
         <v>28000</v>
@@ -3704,7 +3704,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492533683777</v>
       </c>
       <c r="H115" t="n">
         <v>19500</v>
@@ -3762,7 +3762,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.0848650932312</v>
+        <v>4.08486557006836</v>
       </c>
       <c r="H117" t="n">
         <v>47000</v>
@@ -3791,7 +3791,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>3.97988033294678</v>
+        <v>3.9798800945282</v>
       </c>
       <c r="H118" t="n">
         <v>63000</v>
@@ -3820,7 +3820,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>3.91307163238525</v>
+        <v>3.9130711555481</v>
       </c>
       <c r="H119" t="n">
         <v>38500</v>
@@ -3907,7 +3907,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G122" t="n">
-        <v>4.11349678039551</v>
+        <v>4.11349725723267</v>
       </c>
       <c r="H122" t="n">
         <v>20500</v>
@@ -3936,7 +3936,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G123" t="n">
-        <v>4.09918165206909</v>
+        <v>4.09918117523193</v>
       </c>
       <c r="H123" t="n">
         <v>15000</v>
@@ -3994,7 +3994,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896860122681</v>
+        <v>3.99896836280823</v>
       </c>
       <c r="H125" t="n">
         <v>57500</v>
@@ -4023,7 +4023,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G126" t="n">
-        <v>3.92738771438599</v>
+        <v>3.92738747596741</v>
       </c>
       <c r="H126" t="n">
         <v>26000</v>
@@ -4052,7 +4052,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>3.92261600494385</v>
+        <v>3.92261576652527</v>
       </c>
       <c r="H127" t="n">
         <v>7500</v>
@@ -4197,7 +4197,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079182624817</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.9655647277832</v>
+        <v>3.96556448936462</v>
       </c>
       <c r="H133" t="n">
         <v>15500</v>
@@ -4284,7 +4284,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92261600494385</v>
+        <v>3.92261576652527</v>
       </c>
       <c r="H135" t="n">
         <v>14500</v>
@@ -4313,7 +4313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079182624817</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H136" t="n">
         <v>6500</v>
@@ -4342,7 +4342,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>3.91307163238525</v>
+        <v>3.9130711555481</v>
       </c>
       <c r="H137" t="n">
         <v>12000</v>
@@ -4371,7 +4371,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>3.91307163238525</v>
+        <v>3.9130711555481</v>
       </c>
       <c r="H138" t="n">
         <v>5500</v>
@@ -4458,7 +4458,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.9417040348053</v>
+        <v>3.94170427322388</v>
       </c>
       <c r="H141" t="n">
         <v>4000</v>
@@ -4487,7 +4487,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95602035522461</v>
+        <v>3.95601987838745</v>
       </c>
       <c r="H142" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896860122681</v>
+        <v>3.99896836280823</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124793052673</v>
+        <v>3.95124769210815</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4574,7 +4574,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124793052673</v>
+        <v>3.95124769210815</v>
       </c>
       <c r="H145" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079182624817</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4661,7 +4661,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760028839111</v>
+        <v>4.02760076522827</v>
       </c>
       <c r="H148" t="n">
         <v>15500</v>
@@ -4748,7 +4748,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942422866821</v>
+        <v>3.98942399024963</v>
       </c>
       <c r="H151" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.9417040348053</v>
+        <v>3.94170427322388</v>
       </c>
       <c r="H152" t="n">
         <v>9500</v>
@@ -4835,7 +4835,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.87489533424377</v>
+        <v>3.8748950958252</v>
       </c>
       <c r="H154" t="n">
         <v>3000</v>
@@ -4893,7 +4893,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808711051941</v>
+        <v>3.80808687210083</v>
       </c>
       <c r="H156" t="n">
         <v>29500</v>
@@ -4980,7 +4980,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>3.87489533424377</v>
+        <v>3.8748950958252</v>
       </c>
       <c r="H159" t="n">
         <v>6000</v>
@@ -5125,7 +5125,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.82240319252014</v>
+        <v>3.82240295410156</v>
       </c>
       <c r="H164" t="n">
         <v>3500</v>
@@ -5154,7 +5154,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>3.82240319252014</v>
+        <v>3.82240295410156</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5270,7 +5270,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G169" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H169" t="n">
         <v>22000</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5357,7 +5357,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>3.64106559753418</v>
+        <v>3.64106583595276</v>
       </c>
       <c r="H172" t="n">
         <v>500</v>
@@ -5386,7 +5386,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.60766124725342</v>
+        <v>3.60766100883484</v>
       </c>
       <c r="H173" t="n">
         <v>6000</v>
@@ -5473,7 +5473,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H176" t="n">
         <v>3000</v>
@@ -5502,7 +5502,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H177" t="n">
         <v>500</v>
@@ -5589,7 +5589,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G180" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H180" t="n">
         <v>8000</v>
@@ -5647,7 +5647,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H182" t="n">
         <v>12500</v>
@@ -5705,7 +5705,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H184" t="n">
         <v>17000</v>
@@ -5734,7 +5734,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383127212524</v>
+        <v>3.37383151054382</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5763,7 +5763,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.302250623703</v>
+        <v>3.30225086212158</v>
       </c>
       <c r="H186" t="n">
         <v>18000</v>
@@ -5850,7 +5850,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H189" t="n">
         <v>3000</v>
@@ -5879,7 +5879,7 @@
         <v>3.625</v>
       </c>
       <c r="G190" t="n">
-        <v>3.4597282409668</v>
+        <v>3.45972800254822</v>
       </c>
       <c r="H190" t="n">
         <v>15000</v>
@@ -5937,7 +5937,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H192" t="n">
         <v>1500</v>
@@ -5966,7 +5966,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G193" t="n">
-        <v>3.51699233055115</v>
+        <v>3.51699256896973</v>
       </c>
       <c r="H193" t="n">
         <v>3500</v>
@@ -6053,7 +6053,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6082,7 +6082,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G197" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H198" t="n">
         <v>41000</v>
@@ -6140,7 +6140,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.53608083724976</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H200" t="n">
         <v>3500</v>
@@ -6198,7 +6198,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H201" t="n">
         <v>500</v>
@@ -6285,7 +6285,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G204" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H204" t="n">
         <v>34000</v>
@@ -6459,7 +6459,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.50744819641113</v>
+        <v>3.50744867324829</v>
       </c>
       <c r="H210" t="n">
         <v>18000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6546,7 +6546,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H213" t="n">
         <v>4000</v>
@@ -6633,7 +6633,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G216" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H216" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G222" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H222" t="n">
         <v>1000</v>
@@ -6836,7 +6836,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H223" t="n">
         <v>7500</v>
@@ -6865,7 +6865,7 @@
         <v>3.75</v>
       </c>
       <c r="G224" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902932167053</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>3.75</v>
       </c>
       <c r="G225" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902932167053</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H228" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H237" t="n">
         <v>3500</v>
@@ -7271,7 +7271,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H238" t="n">
         <v>5000</v>
@@ -7387,7 +7387,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H242" t="n">
         <v>36500</v>
@@ -7532,7 +7532,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>3.29747843742371</v>
+        <v>3.29747867584229</v>
       </c>
       <c r="H251" t="n">
         <v>4500</v>
@@ -7677,7 +7677,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H252" t="n">
         <v>4000</v>
@@ -7793,7 +7793,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G256" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H256" t="n">
         <v>17500</v>
@@ -7851,7 +7851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G258" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H258" t="n">
         <v>11500</v>
@@ -7880,7 +7880,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6028892993927</v>
+        <v>3.60288906097412</v>
       </c>
       <c r="H259" t="n">
         <v>2500</v>
@@ -7909,7 +7909,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>3.6028892993927</v>
+        <v>3.60288906097412</v>
       </c>
       <c r="H260" t="n">
         <v>10500</v>
@@ -7938,7 +7938,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H261" t="n">
         <v>3000</v>
@@ -7967,7 +7967,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H262" t="n">
         <v>18500</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H265" t="n">
         <v>6000</v>
@@ -8083,7 +8083,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H266" t="n">
         <v>7000</v>
@@ -8170,7 +8170,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G269" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H269" t="n">
         <v>8000</v>
@@ -8199,7 +8199,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G270" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8257,7 +8257,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H272" t="n">
         <v>5000</v>
@@ -8518,7 +8518,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H281" t="n">
         <v>1000</v>
@@ -8547,7 +8547,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.26407480239868</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>3.18772196769714</v>
+        <v>3.18772172927856</v>
       </c>
       <c r="H288" t="n">
         <v>500</v>
@@ -8779,7 +8779,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H290" t="n">
         <v>10500</v>
@@ -8808,7 +8808,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H292" t="n">
         <v>46500</v>
@@ -8895,7 +8895,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H294" t="n">
         <v>2000</v>
@@ -8953,7 +8953,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H296" t="n">
         <v>14500</v>
@@ -8982,7 +8982,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535120010376</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H297" t="n">
         <v>30500</v>
@@ -9069,7 +9069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535120010376</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H300" t="n">
         <v>26000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535120010376</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9156,7 +9156,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G303" t="n">
-        <v>3.82717514038086</v>
+        <v>3.82717537879944</v>
       </c>
       <c r="H303" t="n">
         <v>1000</v>
@@ -9185,7 +9185,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H304" t="n">
         <v>27000</v>
@@ -9243,7 +9243,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G306" t="n">
-        <v>3.82717514038086</v>
+        <v>3.82717537879944</v>
       </c>
       <c r="H306" t="n">
         <v>500</v>
@@ -9272,7 +9272,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G307" t="n">
-        <v>3.82717514038086</v>
+        <v>3.82717537879944</v>
       </c>
       <c r="H307" t="n">
         <v>1500</v>
@@ -9301,7 +9301,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808711051941</v>
+        <v>3.80808687210083</v>
       </c>
       <c r="H308" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H309" t="n">
         <v>13500</v>
@@ -9359,7 +9359,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H310" t="n">
         <v>8000</v>
@@ -9446,7 +9446,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H313" t="n">
         <v>6000</v>
@@ -9475,7 +9475,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9533,7 +9533,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H316" t="n">
         <v>7000</v>
@@ -9591,7 +9591,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H318" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H319" t="n">
         <v>3500</v>
@@ -9649,7 +9649,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H321" t="n">
         <v>3500</v>
@@ -9736,7 +9736,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G324" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H324" t="n">
         <v>1000</v>
@@ -9794,7 +9794,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H325" t="n">
         <v>1500</v>
@@ -9823,7 +9823,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H326" t="n">
         <v>2000</v>
@@ -9881,7 +9881,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H328" t="n">
         <v>7000</v>
@@ -9910,7 +9910,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>3.71264624595642</v>
+        <v>3.712646484375</v>
       </c>
       <c r="H333" t="n">
         <v>4500</v>
@@ -10171,7 +10171,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H338" t="n">
         <v>500</v>
@@ -10229,7 +10229,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G340" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H340" t="n">
         <v>2500</v>
@@ -10374,7 +10374,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10403,7 +10403,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492533683777</v>
       </c>
       <c r="H347" t="n">
         <v>1500</v>
@@ -10461,7 +10461,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H348" t="n">
         <v>3000</v>
@@ -10490,7 +10490,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>3.71264624595642</v>
+        <v>3.712646484375</v>
       </c>
       <c r="H349" t="n">
         <v>500</v>
@@ -10519,7 +10519,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G350" t="n">
-        <v>3.71264624595642</v>
+        <v>3.712646484375</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G351" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H351" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G353" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H353" t="n">
         <v>4000</v>
@@ -10635,7 +10635,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G354" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H355" t="n">
         <v>2500</v>
@@ -10693,7 +10693,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G356" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H356" t="n">
         <v>1000</v>
@@ -10751,7 +10751,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G358" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H358" t="n">
         <v>2500</v>
@@ -10780,7 +10780,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H359" t="n">
         <v>2500</v>
@@ -10809,7 +10809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H360" t="n">
         <v>9500</v>
@@ -10838,7 +10838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G365" t="n">
-        <v>3.71264624595642</v>
+        <v>3.712646484375</v>
       </c>
       <c r="H365" t="n">
         <v>1000</v>
@@ -10983,7 +10983,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>3.64583730697632</v>
+        <v>3.6458375453949</v>
       </c>
       <c r="H369" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G374" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H374" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G375" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H379" t="n">
         <v>500</v>
@@ -11389,7 +11389,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H380" t="n">
         <v>4000</v>
@@ -11418,7 +11418,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H382" t="n">
         <v>2000</v>
@@ -11476,7 +11476,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H383" t="n">
         <v>6500</v>
@@ -11505,7 +11505,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H385" t="n">
         <v>7000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.20680975914001</v>
+        <v>3.20680999755859</v>
       </c>
       <c r="H389" t="n">
         <v>9500</v>
@@ -11737,7 +11737,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H392" t="n">
         <v>11500</v>
@@ -11766,7 +11766,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H393" t="n">
         <v>6500</v>
@@ -11795,7 +11795,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G394" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>3.43586754798889</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H399" t="n">
         <v>4500</v>
@@ -11998,7 +11998,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12056,7 +12056,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H403" t="n">
         <v>2000</v>
@@ -12085,7 +12085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>3.53130888938904</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H404" t="n">
         <v>500</v>
@@ -12114,7 +12114,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H405" t="n">
         <v>5500</v>
@@ -12143,7 +12143,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12201,7 +12201,7 @@
         <v>3.75</v>
       </c>
       <c r="G408" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902932167053</v>
       </c>
       <c r="H408" t="n">
         <v>3500</v>
@@ -12259,7 +12259,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492533683777</v>
       </c>
       <c r="H410" t="n">
         <v>1500</v>
@@ -12346,7 +12346,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H413" t="n">
         <v>500</v>
@@ -12433,7 +12433,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492533683777</v>
       </c>
       <c r="H416" t="n">
         <v>2500</v>
@@ -12491,7 +12491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G418" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H418" t="n">
         <v>5000</v>
@@ -12520,7 +12520,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>3.74092364311218</v>
+        <v>3.7409234046936</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>3.75</v>
       </c>
       <c r="G420" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H420" t="n">
         <v>3500</v>
@@ -12636,7 +12636,7 @@
         <v>3.75</v>
       </c>
       <c r="G423" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H423" t="n">
         <v>500</v>
@@ -12752,7 +12752,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H427" t="n">
         <v>2500</v>
@@ -12781,7 +12781,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G428" t="n">
-        <v>3.74092364311218</v>
+        <v>3.7409234046936</v>
       </c>
       <c r="H428" t="n">
         <v>1500</v>
@@ -12810,7 +12810,7 @@
         <v>3.75</v>
       </c>
       <c r="G429" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H429" t="n">
         <v>5500</v>
@@ -12839,7 +12839,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H430" t="n">
         <v>4000</v>
@@ -12868,7 +12868,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H431" t="n">
         <v>500</v>
@@ -12955,7 +12955,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H434" t="n">
         <v>2000</v>
@@ -12984,7 +12984,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H435" t="n">
         <v>3500</v>
@@ -13216,7 +13216,7 @@
         <v>3.75</v>
       </c>
       <c r="G443" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H443" t="n">
         <v>2500</v>
@@ -13245,7 +13245,7 @@
         <v>3.75</v>
       </c>
       <c r="G444" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H447" t="n">
         <v>51500</v>
@@ -13361,7 +13361,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>3.75</v>
       </c>
       <c r="G449" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H449" t="n">
         <v>2500</v>
@@ -13419,7 +13419,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H455" t="n">
         <v>2500</v>
@@ -13680,7 +13680,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H459" t="n">
         <v>102000</v>
@@ -13709,7 +13709,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H460" t="n">
         <v>1000</v>
@@ -13738,7 +13738,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G461" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>3.75</v>
       </c>
       <c r="G467" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H467" t="n">
         <v>500</v>
@@ -13941,7 +13941,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H468" t="n">
         <v>2500</v>
@@ -14028,7 +14028,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H471" t="n">
         <v>8500</v>
@@ -14057,7 +14057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H472" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H474" t="n">
         <v>5500</v>
@@ -14144,7 +14144,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H475" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H476" t="n">
         <v>7500</v>
@@ -14202,7 +14202,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H477" t="n">
         <v>500</v>
@@ -14231,7 +14231,7 @@
         <v>3.75</v>
       </c>
       <c r="G478" t="n">
-        <v>3.62492632865906</v>
+        <v>3.62492609024048</v>
       </c>
       <c r="H478" t="n">
         <v>2500</v>
@@ -14347,7 +14347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H482" t="n">
         <v>2500</v>
@@ -14405,7 +14405,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H484" t="n">
         <v>14500</v>
@@ -14434,7 +14434,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G485" t="n">
-        <v>3.47026228904724</v>
+        <v>3.47026252746582</v>
       </c>
       <c r="H485" t="n">
         <v>6500</v>
@@ -14492,7 +14492,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H487" t="n">
         <v>6000</v>
@@ -14637,7 +14637,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31559896469116</v>
+        <v>3.31559920310974</v>
       </c>
       <c r="H492" t="n">
         <v>8500</v>
@@ -14666,7 +14666,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H493" t="n">
         <v>4000</v>
@@ -14695,7 +14695,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>3.42193007469177</v>
+        <v>3.42193031311035</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426473617554</v>
+        <v>3.35426497459412</v>
       </c>
       <c r="H499" t="n">
         <v>6500</v>
@@ -14869,7 +14869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H500" t="n">
         <v>5500</v>
@@ -15014,7 +15014,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G505" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H505" t="n">
         <v>1500</v>
@@ -15130,7 +15130,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H509" t="n">
         <v>1000</v>
@@ -15304,7 +15304,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G515" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H515" t="n">
         <v>37500</v>
@@ -15420,7 +15420,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G519" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H519" t="n">
         <v>14500</v>
@@ -15449,7 +15449,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H520" t="n">
         <v>2500</v>
@@ -15478,7 +15478,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G521" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H521" t="n">
         <v>5500</v>
@@ -15507,7 +15507,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G522" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H522" t="n">
         <v>6000</v>
@@ -15536,7 +15536,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G523" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H523" t="n">
         <v>8500</v>
@@ -15565,7 +15565,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G524" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H524" t="n">
         <v>13000</v>
@@ -15623,7 +15623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G526" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H526" t="n">
         <v>6000</v>
@@ -15681,7 +15681,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H528" t="n">
         <v>7500</v>
@@ -15710,7 +15710,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H529" t="n">
         <v>7500</v>
@@ -15768,7 +15768,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H531" t="n">
         <v>500</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H532" t="n">
         <v>6000</v>
@@ -15884,7 +15884,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G535" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H535" t="n">
         <v>1000</v>
@@ -15913,7 +15913,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H536" t="n">
         <v>500</v>
@@ -15942,7 +15942,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G537" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H537" t="n">
         <v>6500</v>
@@ -15971,7 +15971,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G538" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H548" t="n">
         <v>2500</v>
@@ -16290,7 +16290,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H549" t="n">
         <v>2500</v>
@@ -16319,7 +16319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16493,7 +16493,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H556" t="n">
         <v>4500</v>
@@ -16522,7 +16522,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H557" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H559" t="n">
         <v>2500</v>
@@ -16609,7 +16609,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H560" t="n">
         <v>2500</v>
@@ -16725,7 +16725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H565" t="n">
         <v>7000</v>
@@ -16783,7 +16783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H567" t="n">
         <v>17500</v>
@@ -16841,7 +16841,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -17044,7 +17044,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H575" t="n">
         <v>13000</v>
@@ -17102,7 +17102,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G577" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H577" t="n">
         <v>19000</v>
@@ -17131,7 +17131,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H578" t="n">
         <v>2500</v>
@@ -17160,7 +17160,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H579" t="n">
         <v>16500</v>
@@ -17189,7 +17189,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H580" t="n">
         <v>8500</v>
@@ -17218,7 +17218,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G581" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H581" t="n">
         <v>7000</v>
@@ -17247,7 +17247,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G582" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G583" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H583" t="n">
         <v>2000</v>
@@ -17305,7 +17305,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H586" t="n">
         <v>5500</v>
@@ -17392,7 +17392,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H587" t="n">
         <v>2000</v>
@@ -17624,7 +17624,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G595" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H595" t="n">
         <v>7000</v>
@@ -17740,7 +17740,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H599" t="n">
         <v>500</v>
@@ -17769,7 +17769,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17798,7 +17798,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -18001,7 +18001,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H608" t="n">
         <v>19500</v>
@@ -18117,7 +18117,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H612" t="n">
         <v>500</v>
@@ -18146,7 +18146,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H613" t="n">
         <v>500</v>
@@ -18233,7 +18233,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>3.67325854301453</v>
+        <v>3.67325830459595</v>
       </c>
       <c r="H616" t="n">
         <v>4000</v>
@@ -18262,7 +18262,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H622" t="n">
         <v>4500</v>
@@ -18494,7 +18494,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H625" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H636" t="n">
         <v>7000</v>
@@ -18871,7 +18871,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -19016,7 +19016,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G643" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H643" t="n">
         <v>7500</v>
@@ -19074,7 +19074,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H645" t="n">
         <v>7500</v>
@@ -19132,7 +19132,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H647" t="n">
         <v>8500</v>
@@ -19161,7 +19161,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H650" t="n">
         <v>500</v>
@@ -19248,7 +19248,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H651" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859521865845</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19567,7 +19567,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H662" t="n">
         <v>1000</v>
@@ -19799,7 +19799,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>3.76992297172546</v>
+        <v>3.76992321014404</v>
       </c>
       <c r="H670" t="n">
         <v>2500</v>
@@ -19828,7 +19828,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H671" t="n">
         <v>500</v>
@@ -19857,7 +19857,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H673" t="n">
         <v>1500</v>
@@ -19944,7 +19944,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H675" t="n">
         <v>2500</v>
@@ -20060,7 +20060,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H679" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H681" t="n">
         <v>94000</v>
@@ -20147,7 +20147,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20234,7 +20234,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H687" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20524,7 +20524,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H695" t="n">
         <v>10500</v>
@@ -21104,7 +21104,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H715" t="n">
         <v>12500</v>
@@ -21133,7 +21133,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H723" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H730" t="n">
         <v>500</v>
@@ -21713,7 +21713,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H736" t="n">
         <v>2000</v>
@@ -21974,7 +21974,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22003,7 +22003,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H746" t="n">
         <v>500</v>
@@ -22061,7 +22061,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H748" t="n">
         <v>8000</v>
@@ -22090,7 +22090,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H749" t="n">
         <v>500</v>
@@ -22235,7 +22235,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H754" t="n">
         <v>7000</v>
@@ -22351,7 +22351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H758" t="n">
         <v>16000</v>
@@ -22438,7 +22438,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H761" t="n">
         <v>500</v>
@@ -22467,7 +22467,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H766" t="n">
         <v>1000</v>
@@ -22612,7 +22612,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H770" t="n">
         <v>4000</v>
@@ -22786,7 +22786,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225507736206</v>
+        <v>4.13225555419922</v>
       </c>
       <c r="H773" t="n">
         <v>41000</v>
@@ -23018,7 +23018,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H781" t="n">
         <v>8500</v>
@@ -23076,7 +23076,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H783" t="n">
         <v>16500</v>
@@ -23105,7 +23105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H785" t="n">
         <v>26000</v>
@@ -23163,7 +23163,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H786" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H787" t="n">
         <v>3500</v>
@@ -23221,7 +23221,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H788" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809734344482</v>
+        <v>4.32809686660767</v>
       </c>
       <c r="H790" t="n">
         <v>7500</v>
@@ -23395,7 +23395,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H794" t="n">
         <v>1000</v>
@@ -23743,7 +23743,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.6806116104126</v>
+        <v>4.68061208724976</v>
       </c>
       <c r="H808" t="n">
         <v>7500</v>
@@ -23946,7 +23946,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71977996826172</v>
+        <v>4.71978044509888</v>
       </c>
       <c r="H818" t="n">
         <v>3500</v>
@@ -24207,7 +24207,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H822" t="n">
         <v>6500</v>
@@ -24236,7 +24236,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H827" t="n">
         <v>2000</v>
@@ -24381,7 +24381,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H831" t="n">
         <v>500</v>
@@ -24497,7 +24497,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -24816,7 +24816,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H843" t="n">
         <v>500</v>
@@ -25164,7 +25164,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H855" t="n">
         <v>2000</v>
@@ -25686,7 +25686,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H873" t="n">
         <v>500</v>
@@ -25715,7 +25715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -25889,7 +25889,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H881" t="n">
         <v>1500</v>
@@ -25947,7 +25947,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -25976,7 +25976,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26063,7 +26063,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H886" t="n">
         <v>2000</v>
@@ -26092,7 +26092,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H887" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H889" t="n">
         <v>2500</v>
@@ -26179,7 +26179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H892" t="n">
         <v>55000</v>
@@ -26266,7 +26266,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H893" t="n">
         <v>3000</v>
@@ -26295,7 +26295,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H895" t="n">
         <v>11500</v>
@@ -26469,7 +26469,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770086288452</v>
+        <v>4.81770038604736</v>
       </c>
       <c r="H900" t="n">
         <v>6500</v>
@@ -26556,7 +26556,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26730,7 +26730,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H909" t="n">
         <v>11000</v>
@@ -27020,7 +27020,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H919" t="n">
         <v>6500</v>
@@ -27107,7 +27107,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875951766968</v>
+        <v>5.23875999450684</v>
       </c>
       <c r="H922" t="n">
         <v>19000</v>
@@ -27194,7 +27194,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356199264526</v>
+        <v>5.48356151580811</v>
       </c>
       <c r="H925" t="n">
         <v>22000</v>
@@ -27339,7 +27339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H930" t="n">
         <v>16000</v>
@@ -27368,7 +27368,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H931" t="n">
         <v>3000</v>
@@ -41439,6 +41439,35 @@
         <v>8750</v>
       </c>
       <c r="I1416" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1417" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1417" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="H1417" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I1417" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -543,7 +543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H6" t="n">
         <v>552500</v>
@@ -630,7 +630,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246367454529</v>
+        <v>3.40246391296387</v>
       </c>
       <c r="H9" t="n">
         <v>56500</v>
@@ -688,7 +688,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H11" t="n">
         <v>56500</v>
@@ -804,7 +804,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H15" t="n">
         <v>53000</v>
@@ -833,7 +833,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H16" t="n">
         <v>34500</v>
@@ -891,7 +891,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.25930237770081</v>
+        <v>3.25930261611938</v>
       </c>
       <c r="H18" t="n">
         <v>31000</v>
@@ -978,7 +978,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>3.38337540626526</v>
+        <v>3.38337564468384</v>
       </c>
       <c r="H21" t="n">
         <v>32000</v>
@@ -1123,7 +1123,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951542854309</v>
       </c>
       <c r="H26" t="n">
         <v>19500</v>
@@ -1152,7 +1152,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611083984375</v>
+        <v>3.32611107826233</v>
       </c>
       <c r="H27" t="n">
         <v>10000</v>
@@ -1181,7 +1181,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H28" t="n">
         <v>14000</v>
@@ -1471,7 +1471,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H38" t="n">
         <v>12500</v>
@@ -1500,7 +1500,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H39" t="n">
         <v>158500</v>
@@ -1587,7 +1587,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H42" t="n">
         <v>19500</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060997009277</v>
+        <v>3.65060973167419</v>
       </c>
       <c r="H43" t="n">
         <v>14500</v>
@@ -1674,7 +1674,7 @@
         <v>3.75</v>
       </c>
       <c r="G45" t="n">
-        <v>3.57902932167053</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H45" t="n">
         <v>29500</v>
@@ -1703,7 +1703,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G46" t="n">
-        <v>3.6458375453949</v>
+        <v>3.64583730697632</v>
       </c>
       <c r="H46" t="n">
         <v>12500</v>
@@ -1761,7 +1761,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1819,7 +1819,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197756767273</v>
+        <v>3.62197732925415</v>
       </c>
       <c r="H50" t="n">
         <v>6500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1906,7 +1906,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H53" t="n">
         <v>14000</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H54" t="n">
         <v>19000</v>
@@ -1993,7 +1993,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H56" t="n">
         <v>9000</v>
@@ -2196,7 +2196,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>3.54562449455261</v>
+        <v>3.54562473297119</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2225,7 +2225,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H64" t="n">
         <v>1000</v>
@@ -2254,7 +2254,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836040496826</v>
+        <v>3.48836016654968</v>
       </c>
       <c r="H65" t="n">
         <v>22000</v>
@@ -2341,7 +2341,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.41200757026672</v>
+        <v>3.4120078086853</v>
       </c>
       <c r="H68" t="n">
         <v>16500</v>
@@ -2457,7 +2457,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H72" t="n">
         <v>22500</v>
@@ -2544,7 +2544,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H75" t="n">
         <v>6000</v>
@@ -2602,7 +2602,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G77" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H77" t="n">
         <v>67000</v>
@@ -2631,7 +2631,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H78" t="n">
         <v>32000</v>
@@ -2689,7 +2689,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H80" t="n">
         <v>4000</v>
@@ -2718,7 +2718,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H82" t="n">
         <v>16000</v>
@@ -2776,7 +2776,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H83" t="n">
         <v>4500</v>
@@ -2805,7 +2805,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H84" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H85" t="n">
         <v>43000</v>
@@ -2863,7 +2863,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407432556152</v>
       </c>
       <c r="H86" t="n">
         <v>43000</v>
@@ -2892,7 +2892,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H87" t="n">
         <v>8000</v>
@@ -2921,7 +2921,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407432556152</v>
       </c>
       <c r="H88" t="n">
         <v>27500</v>
@@ -2950,7 +2950,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H89" t="n">
         <v>4500</v>
@@ -2979,7 +2979,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3008,7 +3008,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H91" t="n">
         <v>9000</v>
@@ -3153,7 +3153,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H96" t="n">
         <v>51000</v>
@@ -3182,7 +3182,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G97" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H97" t="n">
         <v>43000</v>
@@ -3211,7 +3211,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H98" t="n">
         <v>31500</v>
@@ -3269,7 +3269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063997268677</v>
+        <v>3.44063949584961</v>
       </c>
       <c r="H100" t="n">
         <v>29000</v>
@@ -3327,7 +3327,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495581626892</v>
+        <v>3.45495557785034</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3501,7 +3501,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H108" t="n">
         <v>18000</v>
@@ -3704,7 +3704,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492533683777</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H115" t="n">
         <v>19500</v>
@@ -3762,7 +3762,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.08486557006836</v>
+        <v>4.0848650932312</v>
       </c>
       <c r="H117" t="n">
         <v>47000</v>
@@ -3820,7 +3820,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>3.9130711555481</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H119" t="n">
         <v>38500</v>
@@ -3878,7 +3878,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G121" t="n">
-        <v>4.06577730178833</v>
+        <v>4.06577682495117</v>
       </c>
       <c r="H121" t="n">
         <v>29500</v>
@@ -3936,7 +3936,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G123" t="n">
-        <v>4.09918117523193</v>
+        <v>4.09918165206909</v>
       </c>
       <c r="H123" t="n">
         <v>15000</v>
@@ -3965,7 +3965,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033548355103</v>
       </c>
       <c r="H124" t="n">
         <v>38000</v>
@@ -3994,7 +3994,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896836280823</v>
+        <v>3.99896812438965</v>
       </c>
       <c r="H125" t="n">
         <v>57500</v>
@@ -4023,7 +4023,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G126" t="n">
-        <v>3.92738747596741</v>
+        <v>3.92738771438599</v>
       </c>
       <c r="H126" t="n">
         <v>26000</v>
@@ -4052,7 +4052,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>3.92261576652527</v>
+        <v>3.92261552810669</v>
       </c>
       <c r="H127" t="n">
         <v>7500</v>
@@ -4081,7 +4081,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215942382812</v>
       </c>
       <c r="H128" t="n">
         <v>15500</v>
@@ -4110,7 +4110,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033548355103</v>
       </c>
       <c r="H129" t="n">
         <v>213000</v>
@@ -4139,7 +4139,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G130" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215942382812</v>
       </c>
       <c r="H130" t="n">
         <v>15000</v>
@@ -4168,7 +4168,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033548355103</v>
       </c>
       <c r="H131" t="n">
         <v>31000</v>
@@ -4197,7 +4197,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4284,7 +4284,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92261576652527</v>
+        <v>3.92261552810669</v>
       </c>
       <c r="H135" t="n">
         <v>14500</v>
@@ -4313,7 +4313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H136" t="n">
         <v>6500</v>
@@ -4342,7 +4342,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>3.9130711555481</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H137" t="n">
         <v>12000</v>
@@ -4371,7 +4371,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>3.9130711555481</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H138" t="n">
         <v>5500</v>
@@ -4429,7 +4429,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215942382812</v>
       </c>
       <c r="H140" t="n">
         <v>2500</v>
@@ -4458,7 +4458,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.94170427322388</v>
+        <v>3.94170355796814</v>
       </c>
       <c r="H141" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896836280823</v>
+        <v>3.99896812438965</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124769210815</v>
+        <v>3.95124745368958</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4574,7 +4574,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124769210815</v>
+        <v>3.95124745368958</v>
       </c>
       <c r="H145" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4661,7 +4661,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760076522827</v>
+        <v>4.02760028839111</v>
       </c>
       <c r="H148" t="n">
         <v>15500</v>
@@ -4748,7 +4748,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942399024963</v>
+        <v>3.98942422866821</v>
       </c>
       <c r="H151" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.94170427322388</v>
+        <v>3.94170355796814</v>
       </c>
       <c r="H152" t="n">
         <v>9500</v>
@@ -4893,7 +4893,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H156" t="n">
         <v>29500</v>
@@ -5241,7 +5241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5357,7 +5357,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>3.64106583595276</v>
+        <v>3.6410653591156</v>
       </c>
       <c r="H172" t="n">
         <v>500</v>
@@ -5444,7 +5444,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G175" t="n">
-        <v>3.61243343353271</v>
+        <v>3.61243319511414</v>
       </c>
       <c r="H175" t="n">
         <v>9000</v>
@@ -5531,7 +5531,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.57425689697266</v>
+        <v>3.57425665855408</v>
       </c>
       <c r="H178" t="n">
         <v>19000</v>
@@ -5589,7 +5589,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G180" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H180" t="n">
         <v>8000</v>
@@ -5647,7 +5647,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063997268677</v>
+        <v>3.44063949584961</v>
       </c>
       <c r="H182" t="n">
         <v>12500</v>
@@ -5676,7 +5676,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H183" t="n">
         <v>11500</v>
@@ -5821,7 +5821,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H188" t="n">
         <v>10500</v>
@@ -5937,7 +5937,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H192" t="n">
         <v>1500</v>
@@ -6140,7 +6140,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H200" t="n">
         <v>3500</v>
@@ -6256,7 +6256,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H203" t="n">
         <v>45000</v>
@@ -6285,7 +6285,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G204" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H204" t="n">
         <v>34000</v>
@@ -6314,7 +6314,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6401,7 +6401,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G208" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H208" t="n">
         <v>2000</v>
@@ -6430,7 +6430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H209" t="n">
         <v>5000</v>
@@ -6459,7 +6459,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.50744867324829</v>
+        <v>3.50744819641113</v>
       </c>
       <c r="H210" t="n">
         <v>18000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6546,7 +6546,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H213" t="n">
         <v>4000</v>
@@ -6662,7 +6662,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G217" t="n">
-        <v>3.57425689697266</v>
+        <v>3.57425665855408</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H223" t="n">
         <v>7500</v>
@@ -6865,7 +6865,7 @@
         <v>3.75</v>
       </c>
       <c r="G224" t="n">
-        <v>3.57902932167053</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>3.75</v>
       </c>
       <c r="G225" t="n">
-        <v>3.57902932167053</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H226" t="n">
         <v>21000</v>
@@ -6952,7 +6952,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H227" t="n">
         <v>40000</v>
@@ -6981,7 +6981,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H228" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951542854309</v>
       </c>
       <c r="H233" t="n">
         <v>8500</v>
@@ -7155,7 +7155,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H234" t="n">
         <v>3000</v>
@@ -7184,7 +7184,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>3.46450018882751</v>
+        <v>3.46449995040894</v>
       </c>
       <c r="H235" t="n">
         <v>46000</v>
@@ -7213,7 +7213,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H236" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H241" t="n">
         <v>17500</v>
@@ -7416,7 +7416,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G243" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H243" t="n">
         <v>2500</v>
@@ -7474,7 +7474,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H245" t="n">
         <v>9500</v>
@@ -7503,7 +7503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7619,7 +7619,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H250" t="n">
         <v>2500</v>
@@ -7706,7 +7706,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H253" t="n">
         <v>2500</v>
@@ -7764,7 +7764,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7793,7 +7793,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G256" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H256" t="n">
         <v>17500</v>
@@ -7822,7 +7822,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495581626892</v>
+        <v>3.45495557785034</v>
       </c>
       <c r="H257" t="n">
         <v>9000</v>
@@ -7851,7 +7851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G258" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H258" t="n">
         <v>11500</v>
@@ -7938,7 +7938,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H261" t="n">
         <v>3000</v>
@@ -8083,7 +8083,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H266" t="n">
         <v>7000</v>
@@ -8141,7 +8141,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8228,7 +8228,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G271" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H271" t="n">
         <v>9000</v>
@@ -8286,7 +8286,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H273" t="n">
         <v>2000</v>
@@ -8315,7 +8315,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951542854309</v>
       </c>
       <c r="H274" t="n">
         <v>1500</v>
@@ -8460,7 +8460,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H279" t="n">
         <v>9500</v>
@@ -8489,7 +8489,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407432556152</v>
       </c>
       <c r="H281" t="n">
         <v>1000</v>
@@ -8547,7 +8547,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407432556152</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8634,7 +8634,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H285" t="n">
         <v>1000</v>
@@ -8663,7 +8663,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G286" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G287" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H287" t="n">
         <v>2000</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8779,7 +8779,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H290" t="n">
         <v>10500</v>
@@ -8982,7 +8982,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H297" t="n">
         <v>30500</v>
@@ -9069,7 +9069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H300" t="n">
         <v>26000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9185,7 +9185,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H304" t="n">
         <v>27000</v>
@@ -9301,7 +9301,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H308" t="n">
         <v>1000</v>
@@ -9359,7 +9359,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H310" t="n">
         <v>8000</v>
@@ -9446,7 +9446,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H313" t="n">
         <v>6000</v>
@@ -9475,7 +9475,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9504,7 +9504,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>3.75082230567932</v>
+        <v>3.7508225440979</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9678,7 +9678,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H321" t="n">
         <v>3500</v>
@@ -9881,7 +9881,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H328" t="n">
         <v>7000</v>
@@ -9910,7 +9910,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>3.712646484375</v>
+        <v>3.71264624595642</v>
       </c>
       <c r="H333" t="n">
         <v>4500</v>
@@ -10432,7 +10432,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492533683777</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H347" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>3.712646484375</v>
+        <v>3.71264624595642</v>
       </c>
       <c r="H349" t="n">
         <v>500</v>
@@ -10519,7 +10519,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G350" t="n">
-        <v>3.712646484375</v>
+        <v>3.71264624595642</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H360" t="n">
         <v>9500</v>
@@ -10838,7 +10838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G365" t="n">
-        <v>3.712646484375</v>
+        <v>3.71264624595642</v>
       </c>
       <c r="H365" t="n">
         <v>1000</v>
@@ -10983,7 +10983,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>3.6458375453949</v>
+        <v>3.64583730697632</v>
       </c>
       <c r="H369" t="n">
         <v>1000</v>
@@ -11360,7 +11360,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H379" t="n">
         <v>500</v>
@@ -11476,7 +11476,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H383" t="n">
         <v>6500</v>
@@ -11505,7 +11505,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H385" t="n">
         <v>7000</v>
@@ -11592,7 +11592,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H387" t="n">
         <v>43000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.20680999755859</v>
+        <v>3.20680975914001</v>
       </c>
       <c r="H389" t="n">
         <v>9500</v>
@@ -11679,7 +11679,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G390" t="n">
-        <v>3.25453042984009</v>
+        <v>3.25453066825867</v>
       </c>
       <c r="H390" t="n">
         <v>1000</v>
@@ -11708,7 +11708,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G391" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H391" t="n">
         <v>32000</v>
@@ -11737,7 +11737,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H392" t="n">
         <v>11500</v>
@@ -11824,7 +11824,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G395" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H395" t="n">
         <v>8500</v>
@@ -11853,7 +11853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H396" t="n">
         <v>8000</v>
@@ -11882,7 +11882,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11940,7 +11940,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H399" t="n">
         <v>4500</v>
@@ -11998,7 +11998,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12085,7 +12085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H404" t="n">
         <v>500</v>
@@ -12114,7 +12114,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H405" t="n">
         <v>5500</v>
@@ -12201,7 +12201,7 @@
         <v>3.75</v>
       </c>
       <c r="G408" t="n">
-        <v>3.57902932167053</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H408" t="n">
         <v>3500</v>
@@ -12259,7 +12259,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492533683777</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H410" t="n">
         <v>1500</v>
@@ -12433,7 +12433,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492533683777</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H416" t="n">
         <v>2500</v>
@@ -12520,7 +12520,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>3.7409234046936</v>
+        <v>3.74092364311218</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H426" t="n">
         <v>1000</v>
@@ -12781,7 +12781,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G428" t="n">
-        <v>3.7409234046936</v>
+        <v>3.74092364311218</v>
       </c>
       <c r="H428" t="n">
         <v>1500</v>
@@ -12955,7 +12955,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H434" t="n">
         <v>2000</v>
@@ -13332,7 +13332,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H447" t="n">
         <v>51500</v>
@@ -13361,7 +13361,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H454" t="n">
         <v>1000</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H455" t="n">
         <v>2500</v>
@@ -14057,7 +14057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H472" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H474" t="n">
         <v>5500</v>
@@ -14144,7 +14144,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H475" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H476" t="n">
         <v>7500</v>
@@ -14202,7 +14202,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H477" t="n">
         <v>500</v>
@@ -14260,7 +14260,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H479" t="n">
         <v>500</v>
@@ -14289,7 +14289,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H480" t="n">
         <v>10000</v>
@@ -14405,7 +14405,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H484" t="n">
         <v>14500</v>
@@ -14434,7 +14434,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G485" t="n">
-        <v>3.47026252746582</v>
+        <v>3.4702627658844</v>
       </c>
       <c r="H485" t="n">
         <v>6500</v>
@@ -14463,7 +14463,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H486" t="n">
         <v>4000</v>
@@ -14550,7 +14550,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H489" t="n">
         <v>1000</v>
@@ -14637,7 +14637,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31559920310974</v>
+        <v>3.31559896469116</v>
       </c>
       <c r="H492" t="n">
         <v>8500</v>
@@ -14782,7 +14782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G497" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H497" t="n">
         <v>3000</v>
@@ -14811,7 +14811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G498" t="n">
-        <v>3.36393165588379</v>
+        <v>3.36393141746521</v>
       </c>
       <c r="H498" t="n">
         <v>1500</v>
@@ -14927,7 +14927,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H502" t="n">
         <v>4000</v>
@@ -14956,7 +14956,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H503" t="n">
         <v>3000</v>
@@ -15014,7 +15014,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G505" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H505" t="n">
         <v>1500</v>
@@ -15130,7 +15130,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H509" t="n">
         <v>1000</v>
@@ -15362,7 +15362,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H517" t="n">
         <v>6500</v>
@@ -15391,7 +15391,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H518" t="n">
         <v>25000</v>
@@ -15478,7 +15478,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G521" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H521" t="n">
         <v>5500</v>
@@ -15507,7 +15507,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G522" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H522" t="n">
         <v>6000</v>
@@ -15536,7 +15536,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G523" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H523" t="n">
         <v>8500</v>
@@ -15565,7 +15565,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G524" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H524" t="n">
         <v>13000</v>
@@ -15594,7 +15594,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G525" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H525" t="n">
         <v>4000</v>
@@ -15623,7 +15623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G526" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H526" t="n">
         <v>6000</v>
@@ -15681,7 +15681,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H528" t="n">
         <v>7500</v>
@@ -15710,7 +15710,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H529" t="n">
         <v>7500</v>
@@ -15826,7 +15826,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H533" t="n">
         <v>5000</v>
@@ -15855,7 +15855,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H534" t="n">
         <v>2500</v>
@@ -15942,7 +15942,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G537" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H537" t="n">
         <v>6500</v>
@@ -15971,7 +15971,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G538" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H541" t="n">
         <v>16500</v>
@@ -16725,7 +16725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H565" t="n">
         <v>7000</v>
@@ -16783,7 +16783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -17102,7 +17102,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G577" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H577" t="n">
         <v>19000</v>
@@ -17189,7 +17189,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H580" t="n">
         <v>8500</v>
@@ -17334,7 +17334,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H585" t="n">
         <v>9500</v>
@@ -17421,7 +17421,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H588" t="n">
         <v>5000</v>
@@ -17450,7 +17450,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G589" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G595" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H595" t="n">
         <v>7000</v>
@@ -17856,7 +17856,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H603" t="n">
         <v>7000</v>
@@ -17943,7 +17943,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H606" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H632" t="n">
         <v>19000</v>
@@ -18726,7 +18726,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>3.36393165588379</v>
+        <v>3.36393141746521</v>
       </c>
       <c r="H633" t="n">
         <v>18000</v>
@@ -18755,7 +18755,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G634" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H634" t="n">
         <v>19000</v>
@@ -18784,7 +18784,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G635" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H635" t="n">
         <v>6000</v>
@@ -19016,7 +19016,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G643" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H643" t="n">
         <v>7500</v>
@@ -19074,7 +19074,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H645" t="n">
         <v>7500</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H646" t="n">
         <v>9000</v>
@@ -19422,7 +19422,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G657" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H657" t="n">
         <v>500</v>
@@ -19567,7 +19567,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H662" t="n">
         <v>1000</v>
@@ -19770,7 +19770,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G669" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H669" t="n">
         <v>3500</v>
@@ -19828,7 +19828,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H671" t="n">
         <v>500</v>
@@ -19857,7 +19857,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H673" t="n">
         <v>1500</v>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -543,7 +543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H6" t="n">
         <v>552500</v>
@@ -630,7 +630,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246391296387</v>
+        <v>3.40246367454529</v>
       </c>
       <c r="H9" t="n">
         <v>56500</v>
@@ -688,7 +688,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H11" t="n">
         <v>56500</v>
@@ -804,7 +804,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H15" t="n">
         <v>53000</v>
@@ -833,7 +833,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H16" t="n">
         <v>34500</v>
@@ -891,7 +891,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.25930261611938</v>
+        <v>3.25930237770081</v>
       </c>
       <c r="H18" t="n">
         <v>31000</v>
@@ -978,7 +978,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>3.38337564468384</v>
+        <v>3.38337540626526</v>
       </c>
       <c r="H21" t="n">
         <v>32000</v>
@@ -1123,7 +1123,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.35951542854309</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H26" t="n">
         <v>19500</v>
@@ -1152,7 +1152,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611107826233</v>
+        <v>3.32611083984375</v>
       </c>
       <c r="H27" t="n">
         <v>10000</v>
@@ -1181,7 +1181,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H28" t="n">
         <v>14000</v>
@@ -1471,7 +1471,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H38" t="n">
         <v>12500</v>
@@ -1500,7 +1500,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H39" t="n">
         <v>158500</v>
@@ -1587,7 +1587,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H42" t="n">
         <v>19500</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060973167419</v>
+        <v>3.65060997009277</v>
       </c>
       <c r="H43" t="n">
         <v>14500</v>
@@ -1674,7 +1674,7 @@
         <v>3.75</v>
       </c>
       <c r="G45" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902932167053</v>
       </c>
       <c r="H45" t="n">
         <v>29500</v>
@@ -1703,7 +1703,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64583730697632</v>
+        <v>3.6458375453949</v>
       </c>
       <c r="H46" t="n">
         <v>12500</v>
@@ -1761,7 +1761,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1819,7 +1819,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197732925415</v>
+        <v>3.62197756767273</v>
       </c>
       <c r="H50" t="n">
         <v>6500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1906,7 +1906,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H53" t="n">
         <v>14000</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H54" t="n">
         <v>19000</v>
@@ -1993,7 +1993,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H56" t="n">
         <v>9000</v>
@@ -2196,7 +2196,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>3.54562473297119</v>
+        <v>3.54562449455261</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2225,7 +2225,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H64" t="n">
         <v>1000</v>
@@ -2254,7 +2254,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836016654968</v>
+        <v>3.48836040496826</v>
       </c>
       <c r="H65" t="n">
         <v>22000</v>
@@ -2341,7 +2341,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.4120078086853</v>
+        <v>3.41200757026672</v>
       </c>
       <c r="H68" t="n">
         <v>16500</v>
@@ -2457,7 +2457,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H72" t="n">
         <v>22500</v>
@@ -2544,7 +2544,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H75" t="n">
         <v>6000</v>
@@ -2602,7 +2602,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G77" t="n">
-        <v>3.4167799949646</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H77" t="n">
         <v>67000</v>
@@ -2631,7 +2631,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.4167799949646</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H78" t="n">
         <v>32000</v>
@@ -2689,7 +2689,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H80" t="n">
         <v>4000</v>
@@ -2718,7 +2718,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H82" t="n">
         <v>16000</v>
@@ -2776,7 +2776,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H83" t="n">
         <v>4500</v>
@@ -2805,7 +2805,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H84" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H85" t="n">
         <v>43000</v>
@@ -2863,7 +2863,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>3.26407432556152</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H86" t="n">
         <v>43000</v>
@@ -2892,7 +2892,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H87" t="n">
         <v>8000</v>
@@ -2921,7 +2921,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.26407432556152</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H88" t="n">
         <v>27500</v>
@@ -2950,7 +2950,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839040756226</v>
+        <v>3.27839064598083</v>
       </c>
       <c r="H89" t="n">
         <v>4500</v>
@@ -2979,7 +2979,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839040756226</v>
+        <v>3.27839064598083</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3008,7 +3008,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H91" t="n">
         <v>9000</v>
@@ -3153,7 +3153,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>3.4167799949646</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H96" t="n">
         <v>51000</v>
@@ -3182,7 +3182,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G97" t="n">
-        <v>3.44541168212891</v>
+        <v>3.44541192054749</v>
       </c>
       <c r="H97" t="n">
         <v>43000</v>
@@ -3211,7 +3211,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H98" t="n">
         <v>31500</v>
@@ -3269,7 +3269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063949584961</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H100" t="n">
         <v>29000</v>
@@ -3327,7 +3327,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495557785034</v>
+        <v>3.45495581626892</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3501,7 +3501,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H108" t="n">
         <v>18000</v>
@@ -3704,7 +3704,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492533683777</v>
       </c>
       <c r="H115" t="n">
         <v>19500</v>
@@ -3762,7 +3762,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.0848650932312</v>
+        <v>4.08486557006836</v>
       </c>
       <c r="H117" t="n">
         <v>47000</v>
@@ -3820,7 +3820,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>3.91307139396667</v>
+        <v>3.9130711555481</v>
       </c>
       <c r="H119" t="n">
         <v>38500</v>
@@ -3878,7 +3878,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G121" t="n">
-        <v>4.06577682495117</v>
+        <v>4.06577730178833</v>
       </c>
       <c r="H121" t="n">
         <v>29500</v>
@@ -3936,7 +3936,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G123" t="n">
-        <v>4.09918165206909</v>
+        <v>4.09918117523193</v>
       </c>
       <c r="H123" t="n">
         <v>15000</v>
@@ -3965,7 +3965,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.97033548355103</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H124" t="n">
         <v>38000</v>
@@ -3994,7 +3994,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896812438965</v>
+        <v>3.99896836280823</v>
       </c>
       <c r="H125" t="n">
         <v>57500</v>
@@ -4023,7 +4023,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G126" t="n">
-        <v>3.92738771438599</v>
+        <v>3.92738747596741</v>
       </c>
       <c r="H126" t="n">
         <v>26000</v>
@@ -4052,7 +4052,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>3.92261552810669</v>
+        <v>3.92261576652527</v>
       </c>
       <c r="H127" t="n">
         <v>7500</v>
@@ -4081,7 +4081,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.93215942382812</v>
+        <v>3.9321596622467</v>
       </c>
       <c r="H128" t="n">
         <v>15500</v>
@@ -4110,7 +4110,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.97033548355103</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H129" t="n">
         <v>213000</v>
@@ -4139,7 +4139,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G130" t="n">
-        <v>3.93215942382812</v>
+        <v>3.9321596622467</v>
       </c>
       <c r="H130" t="n">
         <v>15000</v>
@@ -4168,7 +4168,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.97033548355103</v>
+        <v>3.9703357219696</v>
       </c>
       <c r="H131" t="n">
         <v>31000</v>
@@ -4197,7 +4197,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4284,7 +4284,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92261552810669</v>
+        <v>3.92261576652527</v>
       </c>
       <c r="H135" t="n">
         <v>14500</v>
@@ -4313,7 +4313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H136" t="n">
         <v>6500</v>
@@ -4342,7 +4342,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>3.91307139396667</v>
+        <v>3.9130711555481</v>
       </c>
       <c r="H137" t="n">
         <v>12000</v>
@@ -4371,7 +4371,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>3.91307139396667</v>
+        <v>3.9130711555481</v>
       </c>
       <c r="H138" t="n">
         <v>5500</v>
@@ -4429,7 +4429,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93215942382812</v>
+        <v>3.9321596622467</v>
       </c>
       <c r="H140" t="n">
         <v>2500</v>
@@ -4458,7 +4458,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.94170355796814</v>
+        <v>3.94170427322388</v>
       </c>
       <c r="H141" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896812438965</v>
+        <v>3.99896836280823</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124745368958</v>
+        <v>3.95124769210815</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4574,7 +4574,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124745368958</v>
+        <v>3.95124769210815</v>
       </c>
       <c r="H145" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079230308533</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4661,7 +4661,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760028839111</v>
+        <v>4.02760076522827</v>
       </c>
       <c r="H148" t="n">
         <v>15500</v>
@@ -4748,7 +4748,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942422866821</v>
+        <v>3.98942399024963</v>
       </c>
       <c r="H151" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.94170355796814</v>
+        <v>3.94170427322388</v>
       </c>
       <c r="H152" t="n">
         <v>9500</v>
@@ -4893,7 +4893,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808663368225</v>
+        <v>3.80808687210083</v>
       </c>
       <c r="H156" t="n">
         <v>29500</v>
@@ -5241,7 +5241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5357,7 +5357,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>3.6410653591156</v>
+        <v>3.64106583595276</v>
       </c>
       <c r="H172" t="n">
         <v>500</v>
@@ -5444,7 +5444,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G175" t="n">
-        <v>3.61243319511414</v>
+        <v>3.61243343353271</v>
       </c>
       <c r="H175" t="n">
         <v>9000</v>
@@ -5531,7 +5531,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.57425665855408</v>
+        <v>3.57425689697266</v>
       </c>
       <c r="H178" t="n">
         <v>19000</v>
@@ -5589,7 +5589,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G180" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H180" t="n">
         <v>8000</v>
@@ -5647,7 +5647,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063949584961</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H182" t="n">
         <v>12500</v>
@@ -5676,7 +5676,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H183" t="n">
         <v>11500</v>
@@ -5821,7 +5821,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H188" t="n">
         <v>10500</v>
@@ -5937,7 +5937,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H192" t="n">
         <v>1500</v>
@@ -6140,7 +6140,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H200" t="n">
         <v>3500</v>
@@ -6256,7 +6256,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H203" t="n">
         <v>45000</v>
@@ -6285,7 +6285,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G204" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H204" t="n">
         <v>34000</v>
@@ -6314,7 +6314,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.4167799949646</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6401,7 +6401,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G208" t="n">
-        <v>3.44541168212891</v>
+        <v>3.44541192054749</v>
       </c>
       <c r="H208" t="n">
         <v>2000</v>
@@ -6430,7 +6430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H209" t="n">
         <v>5000</v>
@@ -6459,7 +6459,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.50744819641113</v>
+        <v>3.50744867324829</v>
       </c>
       <c r="H210" t="n">
         <v>18000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6546,7 +6546,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H213" t="n">
         <v>4000</v>
@@ -6662,7 +6662,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G217" t="n">
-        <v>3.57425665855408</v>
+        <v>3.57425689697266</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948518753052</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H223" t="n">
         <v>7500</v>
@@ -6865,7 +6865,7 @@
         <v>3.75</v>
       </c>
       <c r="G224" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902932167053</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>3.75</v>
       </c>
       <c r="G225" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902932167053</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>3.42155194282532</v>
+        <v>3.42155170440674</v>
       </c>
       <c r="H226" t="n">
         <v>21000</v>
@@ -6952,7 +6952,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H227" t="n">
         <v>40000</v>
@@ -6981,7 +6981,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H228" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>3.35951542854309</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H233" t="n">
         <v>8500</v>
@@ -7155,7 +7155,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H234" t="n">
         <v>3000</v>
@@ -7184,7 +7184,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>3.46449995040894</v>
+        <v>3.46450018882751</v>
       </c>
       <c r="H235" t="n">
         <v>46000</v>
@@ -7213,7 +7213,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>3.44541168212891</v>
+        <v>3.44541192054749</v>
       </c>
       <c r="H236" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H241" t="n">
         <v>17500</v>
@@ -7416,7 +7416,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G243" t="n">
-        <v>3.23544239997864</v>
+        <v>3.23544216156006</v>
       </c>
       <c r="H243" t="n">
         <v>2500</v>
@@ -7474,7 +7474,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H245" t="n">
         <v>9500</v>
@@ -7503,7 +7503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7619,7 +7619,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H250" t="n">
         <v>2500</v>
@@ -7706,7 +7706,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H253" t="n">
         <v>2500</v>
@@ -7764,7 +7764,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7793,7 +7793,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G256" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H256" t="n">
         <v>17500</v>
@@ -7822,7 +7822,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495557785034</v>
+        <v>3.45495581626892</v>
       </c>
       <c r="H257" t="n">
         <v>9000</v>
@@ -7851,7 +7851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G258" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H258" t="n">
         <v>11500</v>
@@ -7938,7 +7938,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H261" t="n">
         <v>3000</v>
@@ -8083,7 +8083,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H266" t="n">
         <v>7000</v>
@@ -8141,7 +8141,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44541168212891</v>
+        <v>3.44541192054749</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8228,7 +8228,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G271" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H271" t="n">
         <v>9000</v>
@@ -8286,7 +8286,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>3.37860345840454</v>
+        <v>3.37860321998596</v>
       </c>
       <c r="H273" t="n">
         <v>2000</v>
@@ -8315,7 +8315,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>3.35951542854309</v>
+        <v>3.35951519012451</v>
       </c>
       <c r="H274" t="n">
         <v>1500</v>
@@ -8460,7 +8460,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H279" t="n">
         <v>9500</v>
@@ -8489,7 +8489,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>3.26407432556152</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H281" t="n">
         <v>1000</v>
@@ -8547,7 +8547,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.26407432556152</v>
+        <v>3.2640745639801</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8634,7 +8634,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>3.23544239997864</v>
+        <v>3.23544216156006</v>
       </c>
       <c r="H285" t="n">
         <v>1000</v>
@@ -8663,7 +8663,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G286" t="n">
-        <v>3.23544239997864</v>
+        <v>3.23544216156006</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G287" t="n">
-        <v>3.24498653411865</v>
+        <v>3.24498629570007</v>
       </c>
       <c r="H287" t="n">
         <v>2000</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.4167799949646</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8779,7 +8779,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H290" t="n">
         <v>10500</v>
@@ -8982,7 +8982,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H297" t="n">
         <v>30500</v>
@@ -9069,7 +9069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H300" t="n">
         <v>26000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9185,7 +9185,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H304" t="n">
         <v>27000</v>
@@ -9301,7 +9301,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808663368225</v>
+        <v>3.80808687210083</v>
       </c>
       <c r="H308" t="n">
         <v>1000</v>
@@ -9359,7 +9359,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H310" t="n">
         <v>8000</v>
@@ -9446,7 +9446,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H313" t="n">
         <v>6000</v>
@@ -9475,7 +9475,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9504,7 +9504,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>3.7508225440979</v>
+        <v>3.75082230567932</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9678,7 +9678,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H321" t="n">
         <v>3500</v>
@@ -9881,7 +9881,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H328" t="n">
         <v>7000</v>
@@ -9910,7 +9910,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>3.71264624595642</v>
+        <v>3.712646484375</v>
       </c>
       <c r="H333" t="n">
         <v>4500</v>
@@ -10432,7 +10432,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492533683777</v>
       </c>
       <c r="H347" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>3.71264624595642</v>
+        <v>3.712646484375</v>
       </c>
       <c r="H349" t="n">
         <v>500</v>
@@ -10519,7 +10519,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G350" t="n">
-        <v>3.71264624595642</v>
+        <v>3.712646484375</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H360" t="n">
         <v>9500</v>
@@ -10838,7 +10838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>3.74127840995789</v>
+        <v>3.74127817153931</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G365" t="n">
-        <v>3.71264624595642</v>
+        <v>3.712646484375</v>
       </c>
       <c r="H365" t="n">
         <v>1000</v>
@@ -10983,7 +10983,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>3.64583730697632</v>
+        <v>3.6458375453949</v>
       </c>
       <c r="H369" t="n">
         <v>1000</v>
@@ -11360,7 +11360,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H379" t="n">
         <v>500</v>
@@ -11476,7 +11476,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H383" t="n">
         <v>6500</v>
@@ -11505,7 +11505,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>3.55994081497192</v>
+        <v>3.5599410533905</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H385" t="n">
         <v>7000</v>
@@ -11592,7 +11592,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H387" t="n">
         <v>43000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.20680975914001</v>
+        <v>3.20680999755859</v>
       </c>
       <c r="H389" t="n">
         <v>9500</v>
@@ -11679,7 +11679,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G390" t="n">
-        <v>3.25453066825867</v>
+        <v>3.25453042984009</v>
       </c>
       <c r="H390" t="n">
         <v>1000</v>
@@ -11708,7 +11708,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G391" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H391" t="n">
         <v>32000</v>
@@ -11737,7 +11737,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H392" t="n">
         <v>11500</v>
@@ -11824,7 +11824,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G395" t="n">
-        <v>3.34997129440308</v>
+        <v>3.3499710559845</v>
       </c>
       <c r="H395" t="n">
         <v>8500</v>
@@ -11853,7 +11853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H396" t="n">
         <v>8000</v>
@@ -11882,7 +11882,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>3.4167799949646</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11940,7 +11940,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>3.43586778640747</v>
+        <v>3.43586802482605</v>
       </c>
       <c r="H399" t="n">
         <v>4500</v>
@@ -11998,7 +11998,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857345581055</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12085,7 +12085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>3.53130865097046</v>
+        <v>3.53130841255188</v>
       </c>
       <c r="H404" t="n">
         <v>500</v>
@@ -12114,7 +12114,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H405" t="n">
         <v>5500</v>
@@ -12201,7 +12201,7 @@
         <v>3.75</v>
       </c>
       <c r="G408" t="n">
-        <v>3.57902908325195</v>
+        <v>3.57902932167053</v>
       </c>
       <c r="H408" t="n">
         <v>3500</v>
@@ -12259,7 +12259,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492533683777</v>
       </c>
       <c r="H410" t="n">
         <v>1500</v>
@@ -12433,7 +12433,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492533683777</v>
       </c>
       <c r="H416" t="n">
         <v>2500</v>
@@ -12520,7 +12520,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>3.74092364311218</v>
+        <v>3.7409234046936</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H426" t="n">
         <v>1000</v>
@@ -12781,7 +12781,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G428" t="n">
-        <v>3.74092364311218</v>
+        <v>3.7409234046936</v>
       </c>
       <c r="H428" t="n">
         <v>1500</v>
@@ -12955,7 +12955,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H434" t="n">
         <v>2000</v>
@@ -13332,7 +13332,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H447" t="n">
         <v>51500</v>
@@ -13361,7 +13361,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H454" t="n">
         <v>1000</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H455" t="n">
         <v>2500</v>
@@ -14057,7 +14057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H472" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H474" t="n">
         <v>5500</v>
@@ -14144,7 +14144,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425873756409</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H475" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H476" t="n">
         <v>7500</v>
@@ -14202,7 +14202,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H477" t="n">
         <v>500</v>
@@ -14260,7 +14260,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H479" t="n">
         <v>500</v>
@@ -14289,7 +14289,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.58626008033752</v>
+        <v>3.5862603187561</v>
       </c>
       <c r="H480" t="n">
         <v>10000</v>
@@ -14405,7 +14405,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H484" t="n">
         <v>14500</v>
@@ -14434,7 +14434,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G485" t="n">
-        <v>3.4702627658844</v>
+        <v>3.47026252746582</v>
       </c>
       <c r="H485" t="n">
         <v>6500</v>
@@ -14463,7 +14463,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H486" t="n">
         <v>4000</v>
@@ -14550,7 +14550,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H489" t="n">
         <v>1000</v>
@@ -14637,7 +14637,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31559896469116</v>
+        <v>3.31559920310974</v>
       </c>
       <c r="H492" t="n">
         <v>8500</v>
@@ -14782,7 +14782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G497" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H497" t="n">
         <v>3000</v>
@@ -14811,7 +14811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G498" t="n">
-        <v>3.36393141746521</v>
+        <v>3.36393165588379</v>
       </c>
       <c r="H498" t="n">
         <v>1500</v>
@@ -14927,7 +14927,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H502" t="n">
         <v>4000</v>
@@ -14956,7 +14956,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H503" t="n">
         <v>3000</v>
@@ -15014,7 +15014,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G505" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H505" t="n">
         <v>1500</v>
@@ -15130,7 +15130,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>3.5089282989502</v>
+        <v>3.50892853736877</v>
       </c>
       <c r="H509" t="n">
         <v>1000</v>
@@ -15362,7 +15362,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H517" t="n">
         <v>6500</v>
@@ -15391,7 +15391,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H518" t="n">
         <v>25000</v>
@@ -15478,7 +15478,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G521" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H521" t="n">
         <v>5500</v>
@@ -15507,7 +15507,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G522" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H522" t="n">
         <v>6000</v>
@@ -15536,7 +15536,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G523" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H523" t="n">
         <v>8500</v>
@@ -15565,7 +15565,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G524" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H524" t="n">
         <v>13000</v>
@@ -15594,7 +15594,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G525" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H525" t="n">
         <v>4000</v>
@@ -15623,7 +15623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G526" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H526" t="n">
         <v>6000</v>
@@ -15681,7 +15681,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H528" t="n">
         <v>7500</v>
@@ -15710,7 +15710,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H529" t="n">
         <v>7500</v>
@@ -15826,7 +15826,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H533" t="n">
         <v>5000</v>
@@ -15855,7 +15855,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H534" t="n">
         <v>2500</v>
@@ -15942,7 +15942,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G537" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H537" t="n">
         <v>6500</v>
@@ -15971,7 +15971,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G538" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>3.46059632301331</v>
+        <v>3.46059584617615</v>
       </c>
       <c r="H541" t="n">
         <v>16500</v>
@@ -16725,7 +16725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H565" t="n">
         <v>7000</v>
@@ -16783,7 +16783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -17102,7 +17102,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G577" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H577" t="n">
         <v>19000</v>
@@ -17189,7 +17189,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H580" t="n">
         <v>8500</v>
@@ -17334,7 +17334,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H585" t="n">
         <v>9500</v>
@@ -17421,7 +17421,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H588" t="n">
         <v>5000</v>
@@ -17450,7 +17450,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G589" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G595" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H595" t="n">
         <v>7000</v>
@@ -17856,7 +17856,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H603" t="n">
         <v>7000</v>
@@ -17943,7 +17943,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H606" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>3.40259742736816</v>
+        <v>3.40259718894958</v>
       </c>
       <c r="H632" t="n">
         <v>19000</v>
@@ -18726,7 +18726,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>3.36393141746521</v>
+        <v>3.36393165588379</v>
       </c>
       <c r="H633" t="n">
         <v>18000</v>
@@ -18755,7 +18755,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G634" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H634" t="n">
         <v>19000</v>
@@ -18784,7 +18784,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G635" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H635" t="n">
         <v>6000</v>
@@ -19016,7 +19016,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G643" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H643" t="n">
         <v>7500</v>
@@ -19074,7 +19074,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H645" t="n">
         <v>7500</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H646" t="n">
         <v>9000</v>
@@ -19422,7 +19422,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G657" t="n">
-        <v>3.49926161766052</v>
+        <v>3.4992618560791</v>
       </c>
       <c r="H657" t="n">
         <v>500</v>
@@ -19567,7 +19567,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392518043518</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H662" t="n">
         <v>1000</v>
@@ -19770,7 +19770,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G669" t="n">
-        <v>3.71192407608032</v>
+        <v>3.7119243144989</v>
       </c>
       <c r="H669" t="n">
         <v>3500</v>
@@ -19828,7 +19828,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H671" t="n">
         <v>500</v>
@@ -19857,7 +19857,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>3.69259119033813</v>
+        <v>3.69259142875671</v>
       </c>
       <c r="H673" t="n">
         <v>1500</v>
@@ -41468,6 +41468,64 @@
         <v>2500</v>
       </c>
       <c r="I1417" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1418" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1418" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="H1418" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1418" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1419" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1419" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="H1419" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1419" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G5" t="n">
-        <v>3.19249391555786</v>
+        <v>3.19249367713928</v>
       </c>
       <c r="H5" t="n">
         <v>244500</v>
@@ -630,7 +630,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246367454529</v>
+        <v>3.40246391296387</v>
       </c>
       <c r="H9" t="n">
         <v>56500</v>
@@ -659,7 +659,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G10" t="n">
-        <v>3.42632389068604</v>
+        <v>3.42632365226746</v>
       </c>
       <c r="H10" t="n">
         <v>32500</v>
@@ -775,7 +775,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H14" t="n">
         <v>78500</v>
@@ -833,7 +833,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H16" t="n">
         <v>34500</v>
@@ -949,7 +949,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G20" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H20" t="n">
         <v>83000</v>
@@ -978,7 +978,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>3.38337540626526</v>
+        <v>3.38337564468384</v>
       </c>
       <c r="H21" t="n">
         <v>32000</v>
@@ -1065,7 +1065,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109560012817</v>
       </c>
       <c r="H24" t="n">
         <v>48500</v>
@@ -1181,7 +1181,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H28" t="n">
         <v>14000</v>
@@ -1239,7 +1239,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1442,7 +1442,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109560012817</v>
       </c>
       <c r="H37" t="n">
         <v>59500</v>
@@ -1500,7 +1500,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G39" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H39" t="n">
         <v>158500</v>
@@ -1587,7 +1587,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H42" t="n">
         <v>19500</v>
@@ -1645,7 +1645,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H44" t="n">
         <v>20000</v>
@@ -1674,7 +1674,7 @@
         <v>3.75</v>
       </c>
       <c r="G45" t="n">
-        <v>3.57902932167053</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H45" t="n">
         <v>29500</v>
@@ -1761,7 +1761,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1848,7 +1848,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.60766100883484</v>
+        <v>3.60766124725342</v>
       </c>
       <c r="H51" t="n">
         <v>24500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1906,7 +1906,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H53" t="n">
         <v>14000</v>
@@ -1993,7 +1993,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H56" t="n">
         <v>9000</v>
@@ -2254,7 +2254,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836040496826</v>
+        <v>3.48836016654968</v>
       </c>
       <c r="H65" t="n">
         <v>22000</v>
@@ -2428,7 +2428,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109560012817</v>
       </c>
       <c r="H71" t="n">
         <v>28500</v>
@@ -2457,7 +2457,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H72" t="n">
         <v>22500</v>
@@ -2544,7 +2544,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H75" t="n">
         <v>6000</v>
@@ -2602,7 +2602,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G77" t="n">
-        <v>3.41677951812744</v>
+        <v>3.41677927970886</v>
       </c>
       <c r="H77" t="n">
         <v>67000</v>
@@ -2631,7 +2631,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.41677951812744</v>
+        <v>3.41677927970886</v>
       </c>
       <c r="H78" t="n">
         <v>32000</v>
@@ -2689,7 +2689,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H80" t="n">
         <v>4000</v>
@@ -2718,7 +2718,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H82" t="n">
         <v>16000</v>
@@ -2776,7 +2776,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H83" t="n">
         <v>4500</v>
@@ -2834,7 +2834,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H85" t="n">
         <v>43000</v>
@@ -3095,7 +3095,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H94" t="n">
         <v>25000</v>
@@ -3124,7 +3124,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>3.32133889198303</v>
+        <v>3.32133913040161</v>
       </c>
       <c r="H95" t="n">
         <v>12000</v>
@@ -3153,7 +3153,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>3.41677951812744</v>
+        <v>3.41677927970886</v>
       </c>
       <c r="H96" t="n">
         <v>51000</v>
@@ -3211,7 +3211,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H98" t="n">
         <v>31500</v>
@@ -3269,7 +3269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063997268677</v>
+        <v>3.44063973426819</v>
       </c>
       <c r="H100" t="n">
         <v>29000</v>
@@ -3298,7 +3298,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G101" t="n">
-        <v>3.52653646469116</v>
+        <v>3.52653670310974</v>
       </c>
       <c r="H101" t="n">
         <v>11500</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3501,7 +3501,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H108" t="n">
         <v>18000</v>
@@ -3559,7 +3559,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H110" t="n">
         <v>11500</v>
@@ -3588,7 +3588,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G111" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H111" t="n">
         <v>28000</v>
@@ -3646,7 +3646,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H113" t="n">
         <v>30500</v>
@@ -3675,7 +3675,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H114" t="n">
         <v>28000</v>
@@ -3704,7 +3704,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492533683777</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H115" t="n">
         <v>19500</v>
@@ -3733,7 +3733,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.0037407875061</v>
+        <v>4.00374031066895</v>
       </c>
       <c r="H116" t="n">
         <v>224500</v>
@@ -3791,7 +3791,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>3.9798800945282</v>
+        <v>3.97988057136536</v>
       </c>
       <c r="H118" t="n">
         <v>63000</v>
@@ -3820,7 +3820,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>3.9130711555481</v>
+        <v>3.91307163238525</v>
       </c>
       <c r="H119" t="n">
         <v>38500</v>
@@ -3878,7 +3878,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G121" t="n">
-        <v>4.06577730178833</v>
+        <v>4.06577777862549</v>
       </c>
       <c r="H121" t="n">
         <v>29500</v>
@@ -3936,7 +3936,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G123" t="n">
-        <v>4.09918117523193</v>
+        <v>4.09918165206909</v>
       </c>
       <c r="H123" t="n">
         <v>15000</v>
@@ -3994,7 +3994,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896836280823</v>
+        <v>3.99896883964539</v>
       </c>
       <c r="H125" t="n">
         <v>57500</v>
@@ -4081,7 +4081,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H128" t="n">
         <v>15500</v>
@@ -4139,7 +4139,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G130" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H130" t="n">
         <v>15000</v>
@@ -4342,7 +4342,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>3.9130711555481</v>
+        <v>3.91307163238525</v>
       </c>
       <c r="H137" t="n">
         <v>12000</v>
@@ -4371,7 +4371,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>3.9130711555481</v>
+        <v>3.91307163238525</v>
       </c>
       <c r="H138" t="n">
         <v>5500</v>
@@ -4400,7 +4400,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.0037407875061</v>
+        <v>4.00374031066895</v>
       </c>
       <c r="H139" t="n">
         <v>14000</v>
@@ -4429,7 +4429,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.9321596622467</v>
+        <v>3.93215990066528</v>
       </c>
       <c r="H140" t="n">
         <v>2500</v>
@@ -4516,7 +4516,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896836280823</v>
+        <v>3.99896883964539</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124769210815</v>
+        <v>3.95124816894531</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4574,7 +4574,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124769210815</v>
+        <v>3.95124816894531</v>
       </c>
       <c r="H145" t="n">
         <v>2000</v>
@@ -4835,7 +4835,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.8748950958252</v>
+        <v>3.87489533424377</v>
       </c>
       <c r="H154" t="n">
         <v>3000</v>
@@ -4980,7 +4980,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>3.8748950958252</v>
+        <v>3.87489533424377</v>
       </c>
       <c r="H159" t="n">
         <v>6000</v>
@@ -5038,7 +5038,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.89398336410522</v>
+        <v>3.8939836025238</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.82240295410156</v>
+        <v>3.82240319252014</v>
       </c>
       <c r="H164" t="n">
         <v>3500</v>
@@ -5154,7 +5154,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>3.82240295410156</v>
+        <v>3.82240319252014</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G169" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H169" t="n">
         <v>22000</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5386,7 +5386,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.60766100883484</v>
+        <v>3.60766124725342</v>
       </c>
       <c r="H173" t="n">
         <v>6000</v>
@@ -5473,7 +5473,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H176" t="n">
         <v>3000</v>
@@ -5502,7 +5502,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H177" t="n">
         <v>500</v>
@@ -5647,7 +5647,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063997268677</v>
+        <v>3.44063973426819</v>
       </c>
       <c r="H182" t="n">
         <v>12500</v>
@@ -5676,7 +5676,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H183" t="n">
         <v>11500</v>
@@ -5821,7 +5821,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H188" t="n">
         <v>10500</v>
@@ -5937,7 +5937,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H192" t="n">
         <v>1500</v>
@@ -6169,7 +6169,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H200" t="n">
         <v>3500</v>
@@ -6256,7 +6256,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H203" t="n">
         <v>45000</v>
@@ -6285,7 +6285,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G204" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H204" t="n">
         <v>34000</v>
@@ -6314,7 +6314,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.41677951812744</v>
+        <v>3.41677927970886</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6430,7 +6430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H209" t="n">
         <v>5000</v>
@@ -6459,7 +6459,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.50744867324829</v>
+        <v>3.50744843482971</v>
       </c>
       <c r="H210" t="n">
         <v>18000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6546,7 +6546,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H213" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948518753052</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>3.75</v>
       </c>
       <c r="G224" t="n">
-        <v>3.57902932167053</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>3.75</v>
       </c>
       <c r="G225" t="n">
-        <v>3.57902932167053</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H227" t="n">
         <v>40000</v>
@@ -6981,7 +6981,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H228" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H234" t="n">
         <v>3000</v>
@@ -7271,7 +7271,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32133889198303</v>
+        <v>3.32133913040161</v>
       </c>
       <c r="H238" t="n">
         <v>5000</v>
@@ -7387,7 +7387,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>3.32133889198303</v>
+        <v>3.32133913040161</v>
       </c>
       <c r="H242" t="n">
         <v>36500</v>
@@ -7532,7 +7532,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>3.32133889198303</v>
+        <v>3.32133913040161</v>
       </c>
       <c r="H252" t="n">
         <v>4000</v>
@@ -7706,7 +7706,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H253" t="n">
         <v>2500</v>
@@ -7764,7 +7764,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7793,7 +7793,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G256" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H256" t="n">
         <v>17500</v>
@@ -7938,7 +7938,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H261" t="n">
         <v>3000</v>
@@ -7967,7 +7967,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H262" t="n">
         <v>18500</v>
@@ -8025,7 +8025,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H264" t="n">
         <v>2500</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.59811687469482</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H265" t="n">
         <v>6000</v>
@@ -8286,7 +8286,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>3.37860321998596</v>
+        <v>3.37860345840454</v>
       </c>
       <c r="H273" t="n">
         <v>2000</v>
@@ -8344,7 +8344,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H275" t="n">
         <v>1000</v>
@@ -8373,7 +8373,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>3.33088302612305</v>
+        <v>3.33088326454163</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.41677951812744</v>
+        <v>3.41677927970886</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8779,7 +8779,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H290" t="n">
         <v>10500</v>
@@ -8808,7 +8808,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.59811687469482</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H292" t="n">
         <v>46500</v>
@@ -8895,7 +8895,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H294" t="n">
         <v>2000</v>
@@ -8953,7 +8953,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H296" t="n">
         <v>14500</v>
@@ -8982,7 +8982,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H297" t="n">
         <v>30500</v>
@@ -9069,7 +9069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H300" t="n">
         <v>26000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9185,7 +9185,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H304" t="n">
         <v>27000</v>
@@ -9330,7 +9330,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H309" t="n">
         <v>13500</v>
@@ -9359,7 +9359,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H310" t="n">
         <v>8000</v>
@@ -9388,7 +9388,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H311" t="n">
         <v>5000</v>
@@ -9446,7 +9446,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H313" t="n">
         <v>6000</v>
@@ -9475,7 +9475,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H314" t="n">
         <v>1000</v>
@@ -9678,7 +9678,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H321" t="n">
         <v>3500</v>
@@ -9765,7 +9765,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G324" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H324" t="n">
         <v>1000</v>
@@ -9794,7 +9794,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H325" t="n">
         <v>1500</v>
@@ -9823,7 +9823,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H326" t="n">
         <v>2000</v>
@@ -9852,7 +9852,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -10026,7 +10026,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>3.712646484375</v>
+        <v>3.71264624595642</v>
       </c>
       <c r="H333" t="n">
         <v>4500</v>
@@ -10171,7 +10171,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H338" t="n">
         <v>500</v>
@@ -10229,7 +10229,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G340" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H340" t="n">
         <v>2500</v>
@@ -10316,7 +10316,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H343" t="n">
         <v>10000</v>
@@ -10345,7 +10345,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.61720514297485</v>
+        <v>3.61720538139343</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10403,7 +10403,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492533683777</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H347" t="n">
         <v>1500</v>
@@ -10461,7 +10461,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H348" t="n">
         <v>3000</v>
@@ -10490,7 +10490,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G349" t="n">
-        <v>3.712646484375</v>
+        <v>3.71264624595642</v>
       </c>
       <c r="H349" t="n">
         <v>500</v>
@@ -10519,7 +10519,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G350" t="n">
-        <v>3.712646484375</v>
+        <v>3.71264624595642</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G351" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H351" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G353" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H353" t="n">
         <v>4000</v>
@@ -10635,7 +10635,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G354" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H355" t="n">
         <v>2500</v>
@@ -10693,7 +10693,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G356" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H356" t="n">
         <v>1000</v>
@@ -10751,7 +10751,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G358" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H358" t="n">
         <v>2500</v>
@@ -10780,7 +10780,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219038009644</v>
+        <v>3.72219014167786</v>
       </c>
       <c r="H359" t="n">
         <v>2500</v>
@@ -10809,7 +10809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H360" t="n">
         <v>9500</v>
@@ -10838,7 +10838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H363" t="n">
         <v>1000</v>
@@ -10925,7 +10925,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>3.74127817153931</v>
+        <v>3.74127840995789</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G365" t="n">
-        <v>3.712646484375</v>
+        <v>3.71264624595642</v>
       </c>
       <c r="H365" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G374" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H374" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G375" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.59811687469482</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H380" t="n">
         <v>4000</v>
@@ -11418,7 +11418,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.59811687469482</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H382" t="n">
         <v>2000</v>
@@ -11592,7 +11592,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H387" t="n">
         <v>43000</v>
@@ -11737,7 +11737,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H392" t="n">
         <v>11500</v>
@@ -11853,7 +11853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H396" t="n">
         <v>8000</v>
@@ -11882,7 +11882,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>3.41677951812744</v>
+        <v>3.41677927970886</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11940,7 +11940,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G399" t="n">
-        <v>3.43586802482605</v>
+        <v>3.43586778640747</v>
       </c>
       <c r="H399" t="n">
         <v>4500</v>
@@ -11998,7 +11998,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857345581055</v>
+        <v>3.58857321739197</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H405" t="n">
         <v>5500</v>
@@ -12143,7 +12143,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12201,7 +12201,7 @@
         <v>3.75</v>
       </c>
       <c r="G408" t="n">
-        <v>3.57902932167053</v>
+        <v>3.57902908325195</v>
       </c>
       <c r="H408" t="n">
         <v>3500</v>
@@ -12259,7 +12259,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492533683777</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H410" t="n">
         <v>1500</v>
@@ -12346,7 +12346,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62674927711487</v>
+        <v>3.62674951553345</v>
       </c>
       <c r="H413" t="n">
         <v>500</v>
@@ -12433,7 +12433,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492533683777</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H416" t="n">
         <v>2500</v>
@@ -12491,7 +12491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G418" t="n">
-        <v>3.69355797767639</v>
+        <v>3.69355773925781</v>
       </c>
       <c r="H418" t="n">
         <v>5000</v>
@@ -41526,6 +41526,35 @@
         <v>5000</v>
       </c>
       <c r="I1419" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1420" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1420" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="H1420" t="n">
+        <v>750</v>
+      </c>
+      <c r="I1420" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05410480499268</v>
+        <v>3.0541045665741</v>
       </c>
       <c r="H4" t="n">
         <v>47000</v>
@@ -630,7 +630,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246391296387</v>
+        <v>3.40246367454529</v>
       </c>
       <c r="H9" t="n">
         <v>56500</v>
@@ -746,7 +746,7 @@
         <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H13" t="n">
         <v>26500</v>
@@ -775,7 +775,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H14" t="n">
         <v>78500</v>
@@ -833,7 +833,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H16" t="n">
         <v>34500</v>
@@ -862,7 +862,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.29747867584229</v>
+        <v>3.29747843742371</v>
       </c>
       <c r="H17" t="n">
         <v>15000</v>
@@ -949,7 +949,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G20" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H20" t="n">
         <v>83000</v>
@@ -1007,7 +1007,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H22" t="n">
         <v>32500</v>
@@ -1065,7 +1065,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109560012817</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H24" t="n">
         <v>48500</v>
@@ -1094,7 +1094,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H25" t="n">
         <v>13500</v>
@@ -1181,7 +1181,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H28" t="n">
         <v>14000</v>
@@ -1239,7 +1239,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1297,7 +1297,7 @@
         <v>3.5</v>
       </c>
       <c r="G32" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H32" t="n">
         <v>20500</v>
@@ -1442,7 +1442,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109560012817</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H37" t="n">
         <v>59500</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65060997009277</v>
+        <v>3.65060973167419</v>
       </c>
       <c r="H43" t="n">
         <v>14500</v>
@@ -1645,7 +1645,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H44" t="n">
         <v>20000</v>
@@ -1732,7 +1732,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380126953125</v>
+        <v>3.58380103111267</v>
       </c>
       <c r="H47" t="n">
         <v>18000</v>
@@ -1761,7 +1761,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1790,7 +1790,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H49" t="n">
         <v>26000</v>
@@ -1819,7 +1819,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197756767273</v>
+        <v>3.62197732925415</v>
       </c>
       <c r="H50" t="n">
         <v>6500</v>
@@ -1848,7 +1848,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.60766124725342</v>
+        <v>3.60766100883484</v>
       </c>
       <c r="H51" t="n">
         <v>24500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1906,7 +1906,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H53" t="n">
         <v>14000</v>
@@ -1964,7 +1964,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H55" t="n">
         <v>8000</v>
@@ -1993,7 +1993,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H56" t="n">
         <v>9000</v>
@@ -2022,7 +2022,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G57" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H57" t="n">
         <v>7000</v>
@@ -2109,7 +2109,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H60" t="n">
         <v>16000</v>
@@ -2225,7 +2225,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H64" t="n">
         <v>1000</v>
@@ -2254,7 +2254,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836016654968</v>
+        <v>3.48836040496826</v>
       </c>
       <c r="H65" t="n">
         <v>22000</v>
@@ -2283,7 +2283,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H66" t="n">
         <v>9500</v>
@@ -2312,7 +2312,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H67" t="n">
         <v>6000</v>
@@ -2341,7 +2341,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.41200757026672</v>
+        <v>3.4120078086853</v>
       </c>
       <c r="H68" t="n">
         <v>16500</v>
@@ -2428,7 +2428,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109560012817</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H71" t="n">
         <v>28500</v>
@@ -2515,7 +2515,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G74" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H75" t="n">
         <v>6000</v>
@@ -2573,7 +2573,7 @@
         <v>3.5</v>
       </c>
       <c r="G76" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H76" t="n">
         <v>118500</v>
@@ -2602,7 +2602,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G77" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H77" t="n">
         <v>67000</v>
@@ -2631,7 +2631,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H78" t="n">
         <v>32000</v>
@@ -2718,7 +2718,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H83" t="n">
         <v>4500</v>
@@ -2834,7 +2834,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H85" t="n">
         <v>43000</v>
@@ -3095,7 +3095,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H94" t="n">
         <v>25000</v>
@@ -3153,7 +3153,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H96" t="n">
         <v>51000</v>
@@ -3211,7 +3211,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H98" t="n">
         <v>31500</v>
@@ -3269,7 +3269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H100" t="n">
         <v>29000</v>
@@ -3298,7 +3298,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G101" t="n">
-        <v>3.52653670310974</v>
+        <v>3.52653646469116</v>
       </c>
       <c r="H101" t="n">
         <v>11500</v>
@@ -3327,7 +3327,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495581626892</v>
+        <v>3.4549560546875</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3501,7 +3501,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H108" t="n">
         <v>18000</v>
@@ -3530,7 +3530,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380126953125</v>
+        <v>3.58380103111267</v>
       </c>
       <c r="H109" t="n">
         <v>8500</v>
@@ -3559,7 +3559,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H110" t="n">
         <v>11500</v>
@@ -3588,7 +3588,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G111" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H111" t="n">
         <v>28000</v>
@@ -3675,7 +3675,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H114" t="n">
         <v>28000</v>
@@ -3878,7 +3878,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G121" t="n">
-        <v>4.06577777862549</v>
+        <v>4.06577730178833</v>
       </c>
       <c r="H121" t="n">
         <v>29500</v>
@@ -3965,7 +3965,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033619880676</v>
       </c>
       <c r="H124" t="n">
         <v>38000</v>
@@ -4023,7 +4023,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G126" t="n">
-        <v>3.92738747596741</v>
+        <v>3.92738771438599</v>
       </c>
       <c r="H126" t="n">
         <v>26000</v>
@@ -4052,7 +4052,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>3.92261576652527</v>
+        <v>3.92261600494385</v>
       </c>
       <c r="H127" t="n">
         <v>7500</v>
@@ -4110,7 +4110,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033619880676</v>
       </c>
       <c r="H129" t="n">
         <v>213000</v>
@@ -4168,7 +4168,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.9703357219696</v>
+        <v>3.97033619880676</v>
       </c>
       <c r="H131" t="n">
         <v>31000</v>
@@ -4197,7 +4197,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4284,7 +4284,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92261576652527</v>
+        <v>3.92261600494385</v>
       </c>
       <c r="H135" t="n">
         <v>14500</v>
@@ -4313,7 +4313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H136" t="n">
         <v>6500</v>
@@ -4487,7 +4487,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95601987838745</v>
+        <v>3.95602035522461</v>
       </c>
       <c r="H142" t="n">
         <v>4000</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079230308533</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4661,7 +4661,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760076522827</v>
+        <v>4.02760028839111</v>
       </c>
       <c r="H148" t="n">
         <v>15500</v>
@@ -4864,7 +4864,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.88443970680237</v>
+        <v>3.88443994522095</v>
       </c>
       <c r="H155" t="n">
         <v>50000</v>
@@ -5038,7 +5038,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.8939836025238</v>
+        <v>3.89398336410522</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5241,7 +5241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5270,7 +5270,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G169" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H169" t="n">
         <v>22000</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5357,7 +5357,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>3.64106583595276</v>
+        <v>3.64106559753418</v>
       </c>
       <c r="H172" t="n">
         <v>500</v>
@@ -5386,7 +5386,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.60766124725342</v>
+        <v>3.60766100883484</v>
       </c>
       <c r="H173" t="n">
         <v>6000</v>
@@ -5473,7 +5473,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H176" t="n">
         <v>3000</v>
@@ -5647,7 +5647,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063997268677</v>
       </c>
       <c r="H182" t="n">
         <v>12500</v>
@@ -5705,7 +5705,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H184" t="n">
         <v>17000</v>
@@ -5734,7 +5734,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383151054382</v>
+        <v>3.37383127212524</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5792,7 +5792,7 @@
         <v>3.5</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H187" t="n">
         <v>125000</v>
@@ -5821,7 +5821,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H188" t="n">
         <v>10500</v>
@@ -5850,7 +5850,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H189" t="n">
         <v>3000</v>
@@ -5879,7 +5879,7 @@
         <v>3.625</v>
       </c>
       <c r="G190" t="n">
-        <v>3.45972800254822</v>
+        <v>3.4597282409668</v>
       </c>
       <c r="H190" t="n">
         <v>15000</v>
@@ -5908,7 +5908,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H191" t="n">
         <v>6000</v>
@@ -5937,7 +5937,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H192" t="n">
         <v>1500</v>
@@ -5995,7 +5995,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H194" t="n">
         <v>1500</v>
@@ -6053,7 +6053,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6082,7 +6082,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G197" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H198" t="n">
         <v>41000</v>
@@ -6169,7 +6169,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.53608059883118</v>
+        <v>3.5360803604126</v>
       </c>
       <c r="H200" t="n">
         <v>3500</v>
@@ -6227,7 +6227,7 @@
         <v>3.5</v>
       </c>
       <c r="G202" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H202" t="n">
         <v>20500</v>
@@ -6256,7 +6256,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H203" t="n">
         <v>45000</v>
@@ -6314,7 +6314,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6372,7 +6372,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G207" t="n">
-        <v>3.4501838684082</v>
+        <v>3.45018410682678</v>
       </c>
       <c r="H207" t="n">
         <v>5000</v>
@@ -6430,7 +6430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H209" t="n">
         <v>5000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6546,7 +6546,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H213" t="n">
         <v>4000</v>
@@ -6575,7 +6575,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G215" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G216" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H216" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G222" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H222" t="n">
         <v>1000</v>
@@ -6952,7 +6952,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H227" t="n">
         <v>40000</v>
@@ -7068,7 +7068,7 @@
         <v>3.5</v>
       </c>
       <c r="G231" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H231" t="n">
         <v>6500</v>
@@ -7155,7 +7155,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H234" t="n">
         <v>3000</v>
@@ -7184,7 +7184,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>3.46450018882751</v>
+        <v>3.46450042724609</v>
       </c>
       <c r="H235" t="n">
         <v>46000</v>
@@ -7242,7 +7242,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H237" t="n">
         <v>3500</v>
@@ -7445,7 +7445,7 @@
         <v>3.5</v>
       </c>
       <c r="G244" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H244" t="n">
         <v>5000</v>
@@ -7532,7 +7532,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>3.5</v>
       </c>
       <c r="G249" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H249" t="n">
         <v>5000</v>
@@ -7648,7 +7648,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>3.29747867584229</v>
+        <v>3.29747843742371</v>
       </c>
       <c r="H251" t="n">
         <v>4500</v>
@@ -7764,7 +7764,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7822,7 +7822,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495581626892</v>
+        <v>3.4549560546875</v>
       </c>
       <c r="H257" t="n">
         <v>9000</v>
@@ -7938,7 +7938,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H261" t="n">
         <v>3000</v>
@@ -8025,7 +8025,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H264" t="n">
         <v>2500</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H265" t="n">
         <v>6000</v>
@@ -8083,7 +8083,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H266" t="n">
         <v>7000</v>
@@ -8170,7 +8170,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G269" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H269" t="n">
         <v>8000</v>
@@ -8199,7 +8199,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G270" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8257,7 +8257,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>3.39769148826599</v>
+        <v>3.39769172668457</v>
       </c>
       <c r="H272" t="n">
         <v>5000</v>
@@ -8344,7 +8344,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H275" t="n">
         <v>1000</v>
@@ -8373,7 +8373,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>3.33088326454163</v>
+        <v>3.33088302612305</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.5</v>
       </c>
       <c r="G278" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8605,7 +8605,7 @@
         <v>3.5</v>
       </c>
       <c r="G284" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8779,7 +8779,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222038269043</v>
+        <v>3.51222062110901</v>
       </c>
       <c r="H290" t="n">
         <v>10500</v>
@@ -8808,7 +8808,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H292" t="n">
         <v>46500</v>
@@ -9359,7 +9359,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H310" t="n">
         <v>8000</v>
@@ -9388,7 +9388,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H311" t="n">
         <v>5000</v>
@@ -9446,7 +9446,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H313" t="n">
         <v>6000</v>
@@ -9533,7 +9533,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H316" t="n">
         <v>7000</v>
@@ -9591,7 +9591,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H318" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H319" t="n">
         <v>3500</v>
@@ -9649,7 +9649,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9852,7 +9852,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H328" t="n">
         <v>7000</v>
@@ -9910,7 +9910,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H338" t="n">
         <v>500</v>
@@ -10200,7 +10200,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H339" t="n">
         <v>500</v>
@@ -10229,7 +10229,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G340" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H340" t="n">
         <v>2500</v>
@@ -10316,7 +10316,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G343" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H343" t="n">
         <v>10000</v>
@@ -10345,7 +10345,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>3.61720538139343</v>
+        <v>3.61720514297485</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H348" t="n">
         <v>3000</v>
@@ -10809,7 +10809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H360" t="n">
         <v>9500</v>
@@ -10838,7 +10838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G374" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H374" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G375" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G377" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H377" t="n">
         <v>3500</v>
@@ -11331,7 +11331,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55039691925049</v>
+        <v>3.55039668083191</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H379" t="n">
         <v>500</v>
@@ -11389,7 +11389,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H380" t="n">
         <v>4000</v>
@@ -11418,7 +11418,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H382" t="n">
         <v>2000</v>
@@ -11476,7 +11476,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G383" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H383" t="n">
         <v>6500</v>
@@ -11505,7 +11505,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>3.5599410533905</v>
+        <v>3.55994081497192</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H387" t="n">
         <v>43000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.20680999755859</v>
+        <v>3.20680975914001</v>
       </c>
       <c r="H389" t="n">
         <v>9500</v>
@@ -11766,7 +11766,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H393" t="n">
         <v>6500</v>
@@ -11795,7 +11795,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G394" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H396" t="n">
         <v>8000</v>
@@ -11882,7 +11882,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>3.41677927970886</v>
+        <v>3.41677951812744</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11911,7 +11911,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.50267648696899</v>
+        <v>3.50267672538757</v>
       </c>
       <c r="H398" t="n">
         <v>1000</v>
@@ -11998,7 +11998,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857321739197</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H405" t="n">
         <v>5500</v>
@@ -12143,7 +12143,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12346,7 +12346,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G413" t="n">
-        <v>3.62674951553345</v>
+        <v>3.62674927711487</v>
       </c>
       <c r="H413" t="n">
         <v>500</v>
@@ -12665,7 +12665,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G425" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H425" t="n">
         <v>500</v>
@@ -12752,7 +12752,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H427" t="n">
         <v>2500</v>
@@ -12839,7 +12839,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H430" t="n">
         <v>4000</v>
@@ -12868,7 +12868,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H431" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G433" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H433" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H434" t="n">
         <v>2000</v>
@@ -12984,7 +12984,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692719459534</v>
+        <v>3.56692743301392</v>
       </c>
       <c r="H435" t="n">
         <v>3500</v>
@@ -13332,7 +13332,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H447" t="n">
         <v>51500</v>
@@ -13361,7 +13361,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H455" t="n">
         <v>2500</v>
@@ -13622,7 +13622,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692719459534</v>
+        <v>3.56692743301392</v>
       </c>
       <c r="H468" t="n">
         <v>2500</v>
@@ -13970,7 +13970,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G469" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H469" t="n">
         <v>2000</v>
@@ -14028,7 +14028,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H471" t="n">
         <v>8500</v>
@@ -14057,7 +14057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H472" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H474" t="n">
         <v>5500</v>
@@ -14144,7 +14144,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H475" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H476" t="n">
         <v>7500</v>
@@ -14202,7 +14202,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H477" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H482" t="n">
         <v>2500</v>
@@ -14521,7 +14521,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G488" t="n">
-        <v>3.45092964172363</v>
+        <v>3.45092940330505</v>
       </c>
       <c r="H488" t="n">
         <v>2500</v>
@@ -14579,7 +14579,7 @@
         <v>3.5</v>
       </c>
       <c r="G490" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H490" t="n">
         <v>4000</v>
@@ -14608,7 +14608,7 @@
         <v>3.5</v>
       </c>
       <c r="G491" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H491" t="n">
         <v>8500</v>
@@ -14840,7 +14840,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426497459412</v>
+        <v>3.35426473617554</v>
       </c>
       <c r="H499" t="n">
         <v>6500</v>
@@ -14869,7 +14869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H500" t="n">
         <v>5500</v>
@@ -14898,7 +14898,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G501" t="n">
-        <v>3.45092964172363</v>
+        <v>3.45092940330505</v>
       </c>
       <c r="H501" t="n">
         <v>6500</v>
@@ -14985,7 +14985,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>3.52826142311096</v>
+        <v>3.52826166152954</v>
       </c>
       <c r="H504" t="n">
         <v>4500</v>
@@ -15043,7 +15043,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H506" t="n">
         <v>2000</v>
@@ -15072,7 +15072,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G507" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15275,7 +15275,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H514" t="n">
         <v>3500</v>
@@ -15565,7 +15565,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G524" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H524" t="n">
         <v>13000</v>
@@ -15623,7 +15623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G526" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H526" t="n">
         <v>6000</v>
@@ -15681,7 +15681,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H528" t="n">
         <v>7500</v>
@@ -15710,7 +15710,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H529" t="n">
         <v>7500</v>
@@ -15739,7 +15739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G530" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H530" t="n">
         <v>8000</v>
@@ -15768,7 +15768,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H531" t="n">
         <v>500</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H532" t="n">
         <v>6000</v>
@@ -15913,7 +15913,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H536" t="n">
         <v>500</v>
@@ -16000,7 +16000,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.75059032440186</v>
+        <v>3.75059056282043</v>
       </c>
       <c r="H539" t="n">
         <v>12000</v>
@@ -16261,7 +16261,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H548" t="n">
         <v>2500</v>
@@ -16290,7 +16290,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H549" t="n">
         <v>2500</v>
@@ -16319,7 +16319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16493,7 +16493,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H556" t="n">
         <v>4500</v>
@@ -16522,7 +16522,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H557" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H559" t="n">
         <v>2500</v>
@@ -16609,7 +16609,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H560" t="n">
         <v>2500</v>
@@ -16725,7 +16725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H565" t="n">
         <v>7000</v>
@@ -16783,7 +16783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -16899,7 +16899,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G570" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H570" t="n">
         <v>1000</v>
@@ -16928,7 +16928,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G571" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G573" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H575" t="n">
         <v>13000</v>
@@ -17189,7 +17189,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H580" t="n">
         <v>8500</v>
@@ -17363,7 +17363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H586" t="n">
         <v>5500</v>
@@ -17479,7 +17479,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H590" t="n">
         <v>4000</v>
@@ -17508,7 +17508,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G592" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G593" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H599" t="n">
         <v>500</v>
@@ -17769,7 +17769,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17798,7 +17798,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17885,7 +17885,7 @@
         <v>3.5</v>
       </c>
       <c r="G604" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H604" t="n">
         <v>6500</v>
@@ -18001,7 +18001,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H608" t="n">
         <v>19500</v>
@@ -18030,7 +18030,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H609" t="n">
         <v>2000</v>
@@ -18059,7 +18059,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H610" t="n">
         <v>5000</v>
@@ -18088,7 +18088,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G611" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H611" t="n">
         <v>3000</v>
@@ -18117,7 +18117,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H612" t="n">
         <v>500</v>
@@ -18146,7 +18146,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H613" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H622" t="n">
         <v>4500</v>
@@ -18436,7 +18436,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H623" t="n">
         <v>1000</v>
@@ -18494,7 +18494,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H625" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H636" t="n">
         <v>7000</v>
@@ -18871,7 +18871,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -18900,7 +18900,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G639" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H639" t="n">
         <v>18000</v>
@@ -19074,7 +19074,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H645" t="n">
         <v>7500</v>
@@ -19132,7 +19132,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H647" t="n">
         <v>8500</v>
@@ -19161,7 +19161,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H650" t="n">
         <v>500</v>
@@ -19248,7 +19248,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H651" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19509,7 +19509,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H660" t="n">
         <v>10500</v>
@@ -19538,7 +19538,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H661" t="n">
         <v>10000</v>
@@ -19567,7 +19567,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H662" t="n">
         <v>1000</v>
@@ -19596,7 +19596,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H663" t="n">
         <v>8000</v>
@@ -19654,7 +19654,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H665" t="n">
         <v>12000</v>
@@ -19683,7 +19683,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H666" t="n">
         <v>10500</v>
@@ -19712,7 +19712,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H667" t="n">
         <v>13000</v>
@@ -19741,7 +19741,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H668" t="n">
         <v>4000</v>
@@ -19944,7 +19944,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H675" t="n">
         <v>2500</v>
@@ -20060,7 +20060,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932498931885</v>
+        <v>3.79932522773743</v>
       </c>
       <c r="H679" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H681" t="n">
         <v>94000</v>
@@ -20147,7 +20147,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932498931885</v>
+        <v>3.79932522773743</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20234,7 +20234,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H687" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20524,7 +20524,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H695" t="n">
         <v>10500</v>
@@ -21104,7 +21104,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H715" t="n">
         <v>12500</v>
@@ -21133,7 +21133,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H723" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H730" t="n">
         <v>500</v>
@@ -21713,7 +21713,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H736" t="n">
         <v>2000</v>
@@ -21974,7 +21974,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22003,7 +22003,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H746" t="n">
         <v>500</v>
@@ -22061,7 +22061,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H748" t="n">
         <v>8000</v>
@@ -22090,7 +22090,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H749" t="n">
         <v>500</v>
@@ -22235,7 +22235,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H754" t="n">
         <v>7000</v>
@@ -22351,7 +22351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H758" t="n">
         <v>16000</v>
@@ -22438,7 +22438,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H761" t="n">
         <v>500</v>
@@ -22467,7 +22467,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H766" t="n">
         <v>1000</v>
@@ -22612,7 +22612,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H770" t="n">
         <v>4000</v>
@@ -22786,7 +22786,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225555419922</v>
+        <v>4.13225507736206</v>
       </c>
       <c r="H773" t="n">
         <v>41000</v>
@@ -23018,7 +23018,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H781" t="n">
         <v>8500</v>
@@ -23076,7 +23076,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H783" t="n">
         <v>16500</v>
@@ -23105,7 +23105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183973312378</v>
+        <v>4.15183925628662</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H785" t="n">
         <v>26000</v>
@@ -23163,7 +23163,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H786" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H787" t="n">
         <v>3500</v>
@@ -23221,7 +23221,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H788" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809686660767</v>
+        <v>4.32809734344482</v>
       </c>
       <c r="H790" t="n">
         <v>7500</v>
@@ -23395,7 +23395,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H794" t="n">
         <v>1000</v>
@@ -23743,7 +23743,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.68061208724976</v>
+        <v>4.6806116104126</v>
       </c>
       <c r="H808" t="n">
         <v>7500</v>
@@ -23946,7 +23946,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71978044509888</v>
+        <v>4.71977996826172</v>
       </c>
       <c r="H818" t="n">
         <v>3500</v>
@@ -24207,7 +24207,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H822" t="n">
         <v>6500</v>
@@ -24236,7 +24236,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H827" t="n">
         <v>2000</v>
@@ -24381,7 +24381,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H831" t="n">
         <v>500</v>
@@ -24497,7 +24497,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -24816,7 +24816,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H843" t="n">
         <v>500</v>
@@ -25164,7 +25164,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H855" t="n">
         <v>2000</v>
@@ -25686,7 +25686,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H873" t="n">
         <v>500</v>
@@ -25715,7 +25715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -25889,7 +25889,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183973312378</v>
+        <v>4.15183925628662</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H881" t="n">
         <v>1500</v>
@@ -25947,7 +25947,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -25976,7 +25976,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26063,7 +26063,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H886" t="n">
         <v>2000</v>
@@ -26092,7 +26092,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H887" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H889" t="n">
         <v>2500</v>
@@ -26179,7 +26179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H892" t="n">
         <v>55000</v>
@@ -26266,7 +26266,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H893" t="n">
         <v>3000</v>
@@ -26295,7 +26295,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H895" t="n">
         <v>11500</v>
@@ -26469,7 +26469,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770038604736</v>
+        <v>4.81770086288452</v>
       </c>
       <c r="H900" t="n">
         <v>6500</v>
@@ -26556,7 +26556,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26730,7 +26730,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H909" t="n">
         <v>11000</v>
@@ -27020,7 +27020,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H919" t="n">
         <v>6500</v>
@@ -27107,7 +27107,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875999450684</v>
+        <v>5.23875951766968</v>
       </c>
       <c r="H922" t="n">
         <v>19000</v>
@@ -27194,7 +27194,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356151580811</v>
+        <v>5.48356199264526</v>
       </c>
       <c r="H925" t="n">
         <v>22000</v>
@@ -27339,7 +27339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772068023682</v>
+        <v>5.28772020339966</v>
       </c>
       <c r="H930" t="n">
         <v>16000</v>
@@ -27368,7 +27368,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772068023682</v>
+        <v>5.28772020339966</v>
       </c>
       <c r="H931" t="n">
         <v>3000</v>
@@ -41555,6 +41555,35 @@
         <v>750</v>
       </c>
       <c r="I1420" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1421" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1421" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>5.55000019073486</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>5.55000019073486</v>
+      </c>
+      <c r="H1421" t="n">
+        <v>500</v>
+      </c>
+      <c r="I1421" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0541045665741</v>
+        <v>3.05410480499268</v>
       </c>
       <c r="H4" t="n">
         <v>47000</v>
@@ -543,7 +543,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G6" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H6" t="n">
         <v>552500</v>
@@ -630,7 +630,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246367454529</v>
+        <v>3.40246391296387</v>
       </c>
       <c r="H9" t="n">
         <v>56500</v>
@@ -717,7 +717,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H12" t="n">
         <v>32000</v>
@@ -746,7 +746,7 @@
         <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H13" t="n">
         <v>26500</v>
@@ -775,7 +775,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H14" t="n">
         <v>78500</v>
@@ -833,7 +833,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H16" t="n">
         <v>34500</v>
@@ -862,7 +862,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.29747843742371</v>
+        <v>3.29747891426086</v>
       </c>
       <c r="H17" t="n">
         <v>15000</v>
@@ -978,7 +978,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>3.38337564468384</v>
+        <v>3.38337540626526</v>
       </c>
       <c r="H21" t="n">
         <v>32000</v>
@@ -1007,7 +1007,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H22" t="n">
         <v>32500</v>
@@ -1065,7 +1065,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H24" t="n">
         <v>48500</v>
@@ -1094,7 +1094,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G25" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H25" t="n">
         <v>13500</v>
@@ -1152,7 +1152,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611083984375</v>
+        <v>3.32611107826233</v>
       </c>
       <c r="H27" t="n">
         <v>10000</v>
@@ -1181,7 +1181,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H28" t="n">
         <v>14000</v>
@@ -1297,7 +1297,7 @@
         <v>3.5</v>
       </c>
       <c r="G32" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H32" t="n">
         <v>20500</v>
@@ -1413,7 +1413,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G36" t="n">
-        <v>3.33565497398376</v>
+        <v>3.33565473556519</v>
       </c>
       <c r="H36" t="n">
         <v>3500</v>
@@ -1442,7 +1442,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H37" t="n">
         <v>59500</v>
@@ -1529,7 +1529,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G40" t="n">
-        <v>3.75559449195862</v>
+        <v>3.75559425354004</v>
       </c>
       <c r="H40" t="n">
         <v>132500</v>
@@ -1732,7 +1732,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H47" t="n">
         <v>18000</v>
@@ -1761,7 +1761,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1790,7 +1790,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.55039668083191</v>
+        <v>3.55039691925049</v>
       </c>
       <c r="H49" t="n">
         <v>26000</v>
@@ -1819,7 +1819,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197732925415</v>
+        <v>3.62197756767273</v>
       </c>
       <c r="H50" t="n">
         <v>6500</v>
@@ -1848,7 +1848,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.60766100883484</v>
+        <v>3.607661485672</v>
       </c>
       <c r="H51" t="n">
         <v>24500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H54" t="n">
         <v>19000</v>
@@ -1964,7 +1964,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H55" t="n">
         <v>8000</v>
@@ -1993,7 +1993,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H56" t="n">
         <v>9000</v>
@@ -2022,7 +2022,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G57" t="n">
-        <v>3.55039668083191</v>
+        <v>3.55039691925049</v>
       </c>
       <c r="H57" t="n">
         <v>7000</v>
@@ -2109,7 +2109,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H60" t="n">
         <v>16000</v>
@@ -2167,7 +2167,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>3.54085254669189</v>
+        <v>3.54085278511047</v>
       </c>
       <c r="H62" t="n">
         <v>9000</v>
@@ -2196,7 +2196,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G63" t="n">
-        <v>3.54562449455261</v>
+        <v>3.54562473297119</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2254,7 +2254,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836040496826</v>
+        <v>3.48836016654968</v>
       </c>
       <c r="H65" t="n">
         <v>22000</v>
@@ -2283,7 +2283,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H66" t="n">
         <v>9500</v>
@@ -2312,7 +2312,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H67" t="n">
         <v>6000</v>
@@ -2341,7 +2341,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.4120078086853</v>
+        <v>3.41200757026672</v>
       </c>
       <c r="H68" t="n">
         <v>16500</v>
@@ -2428,7 +2428,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H71" t="n">
         <v>28500</v>
@@ -2457,7 +2457,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H72" t="n">
         <v>22500</v>
@@ -2515,7 +2515,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G74" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H75" t="n">
         <v>6000</v>
@@ -2573,7 +2573,7 @@
         <v>3.5</v>
       </c>
       <c r="G76" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H76" t="n">
         <v>118500</v>
@@ -2689,7 +2689,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H80" t="n">
         <v>4000</v>
@@ -2718,7 +2718,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H83" t="n">
         <v>4500</v>
@@ -2834,7 +2834,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H85" t="n">
         <v>43000</v>
@@ -2892,7 +2892,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H87" t="n">
         <v>8000</v>
@@ -2950,7 +2950,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G89" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H89" t="n">
         <v>4500</v>
@@ -2979,7 +2979,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G90" t="n">
-        <v>3.27839064598083</v>
+        <v>3.27839040756226</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3008,7 +3008,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H91" t="n">
         <v>9000</v>
@@ -3211,7 +3211,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G98" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H98" t="n">
         <v>31500</v>
@@ -3269,7 +3269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063997268677</v>
+        <v>3.44063973426819</v>
       </c>
       <c r="H100" t="n">
         <v>29000</v>
@@ -3327,7 +3327,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.4549560546875</v>
+        <v>3.45495581626892</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3530,7 +3530,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H109" t="n">
         <v>8500</v>
@@ -3617,7 +3617,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H112" t="n">
         <v>29000</v>
@@ -3646,7 +3646,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H113" t="n">
         <v>30500</v>
@@ -3675,7 +3675,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H114" t="n">
         <v>28000</v>
@@ -3704,7 +3704,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H115" t="n">
         <v>19500</v>
@@ -3907,7 +3907,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G122" t="n">
-        <v>4.11349725723267</v>
+        <v>4.11349678039551</v>
       </c>
       <c r="H122" t="n">
         <v>20500</v>
@@ -3936,7 +3936,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G123" t="n">
-        <v>4.09918165206909</v>
+        <v>4.09918117523193</v>
       </c>
       <c r="H123" t="n">
         <v>15000</v>
@@ -3965,7 +3965,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.97033619880676</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H124" t="n">
         <v>38000</v>
@@ -3994,7 +3994,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896883964539</v>
+        <v>3.99896860122681</v>
       </c>
       <c r="H125" t="n">
         <v>57500</v>
@@ -4110,7 +4110,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.97033619880676</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H129" t="n">
         <v>213000</v>
@@ -4168,7 +4168,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.97033619880676</v>
+        <v>3.97033596038818</v>
       </c>
       <c r="H131" t="n">
         <v>31000</v>
@@ -4197,7 +4197,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079254150391</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.96556448936462</v>
+        <v>3.96556401252747</v>
       </c>
       <c r="H133" t="n">
         <v>15500</v>
@@ -4255,7 +4255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H134" t="n">
         <v>2000</v>
@@ -4313,7 +4313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079254150391</v>
       </c>
       <c r="H136" t="n">
         <v>6500</v>
@@ -4458,7 +4458,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.94170427322388</v>
+        <v>3.9417040348053</v>
       </c>
       <c r="H141" t="n">
         <v>4000</v>
@@ -4487,7 +4487,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>3.95602035522461</v>
+        <v>3.95601987838745</v>
       </c>
       <c r="H142" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896883964539</v>
+        <v>3.99896860122681</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124816894531</v>
+        <v>3.95124793052673</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4574,7 +4574,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124816894531</v>
+        <v>3.95124793052673</v>
       </c>
       <c r="H145" t="n">
         <v>2000</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079206466675</v>
+        <v>3.96079254150391</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4632,7 +4632,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H147" t="n">
         <v>6500</v>
@@ -4661,7 +4661,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760028839111</v>
+        <v>4.02760076522827</v>
       </c>
       <c r="H148" t="n">
         <v>15500</v>
@@ -4690,7 +4690,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>4.01805639266968</v>
+        <v>4.01805686950684</v>
       </c>
       <c r="H149" t="n">
         <v>10000</v>
@@ -4719,7 +4719,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>4.00851249694824</v>
+        <v>4.0085129737854</v>
       </c>
       <c r="H150" t="n">
         <v>5000</v>
@@ -4748,7 +4748,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942399024963</v>
+        <v>3.98942422866821</v>
       </c>
       <c r="H151" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.94170427322388</v>
+        <v>3.9417040348053</v>
       </c>
       <c r="H152" t="n">
         <v>9500</v>
@@ -4835,7 +4835,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.87489533424377</v>
+        <v>3.87489557266235</v>
       </c>
       <c r="H154" t="n">
         <v>3000</v>
@@ -4893,7 +4893,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G156" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H156" t="n">
         <v>29500</v>
@@ -4980,7 +4980,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>3.87489533424377</v>
+        <v>3.87489557266235</v>
       </c>
       <c r="H159" t="n">
         <v>6000</v>
@@ -5125,7 +5125,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.82240319252014</v>
+        <v>3.82240295410156</v>
       </c>
       <c r="H164" t="n">
         <v>3500</v>
@@ -5154,7 +5154,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G165" t="n">
-        <v>3.82240319252014</v>
+        <v>3.82240295410156</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5386,7 +5386,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.60766100883484</v>
+        <v>3.607661485672</v>
       </c>
       <c r="H173" t="n">
         <v>6000</v>
@@ -5415,7 +5415,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H174" t="n">
         <v>5000</v>
@@ -5444,7 +5444,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G175" t="n">
-        <v>3.61243343353271</v>
+        <v>3.61243319511414</v>
       </c>
       <c r="H175" t="n">
         <v>9000</v>
@@ -5589,7 +5589,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G180" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H180" t="n">
         <v>8000</v>
@@ -5647,7 +5647,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063997268677</v>
+        <v>3.44063973426819</v>
       </c>
       <c r="H182" t="n">
         <v>12500</v>
@@ -5705,7 +5705,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H184" t="n">
         <v>17000</v>
@@ -5734,7 +5734,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383127212524</v>
+        <v>3.37383151054382</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5792,7 +5792,7 @@
         <v>3.5</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H187" t="n">
         <v>125000</v>
@@ -5821,7 +5821,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H188" t="n">
         <v>10500</v>
@@ -5850,7 +5850,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G189" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H189" t="n">
         <v>3000</v>
@@ -5908,7 +5908,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H191" t="n">
         <v>6000</v>
@@ -5937,7 +5937,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H192" t="n">
         <v>1500</v>
@@ -5995,7 +5995,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H194" t="n">
         <v>1500</v>
@@ -6053,7 +6053,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6082,7 +6082,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G197" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H198" t="n">
         <v>41000</v>
@@ -6140,7 +6140,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G199" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>3.5360803604126</v>
+        <v>3.53608059883118</v>
       </c>
       <c r="H200" t="n">
         <v>3500</v>
@@ -6198,7 +6198,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>3.54085254669189</v>
+        <v>3.54085278511047</v>
       </c>
       <c r="H201" t="n">
         <v>500</v>
@@ -6227,7 +6227,7 @@
         <v>3.5</v>
       </c>
       <c r="G202" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H202" t="n">
         <v>20500</v>
@@ -6256,7 +6256,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H203" t="n">
         <v>45000</v>
@@ -6343,7 +6343,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H206" t="n">
         <v>2000</v>
@@ -6372,7 +6372,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G207" t="n">
-        <v>3.45018410682678</v>
+        <v>3.4501838684082</v>
       </c>
       <c r="H207" t="n">
         <v>5000</v>
@@ -6430,7 +6430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H209" t="n">
         <v>5000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6546,7 +6546,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H213" t="n">
         <v>4000</v>
@@ -6575,7 +6575,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G215" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G216" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H216" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G222" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H222" t="n">
         <v>1000</v>
@@ -6836,7 +6836,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G223" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H223" t="n">
         <v>7500</v>
@@ -6952,7 +6952,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H227" t="n">
         <v>40000</v>
@@ -7068,7 +7068,7 @@
         <v>3.5</v>
       </c>
       <c r="G231" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H231" t="n">
         <v>6500</v>
@@ -7155,7 +7155,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H234" t="n">
         <v>3000</v>
@@ -7184,7 +7184,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>3.46450042724609</v>
+        <v>3.46450018882751</v>
       </c>
       <c r="H235" t="n">
         <v>46000</v>
@@ -7242,7 +7242,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G237" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H237" t="n">
         <v>3500</v>
@@ -7300,7 +7300,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G239" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H239" t="n">
         <v>2500</v>
@@ -7329,7 +7329,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>3.5</v>
       </c>
       <c r="G244" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H244" t="n">
         <v>5000</v>
@@ -7532,7 +7532,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635413169861</v>
+        <v>3.21635389328003</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>3.5</v>
       </c>
       <c r="G249" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H249" t="n">
         <v>5000</v>
@@ -7648,7 +7648,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>3.29747843742371</v>
+        <v>3.29747891426086</v>
       </c>
       <c r="H251" t="n">
         <v>4500</v>
@@ -7706,7 +7706,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>3.39291977882385</v>
+        <v>3.39291954040527</v>
       </c>
       <c r="H253" t="n">
         <v>2500</v>
@@ -7735,7 +7735,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H254" t="n">
         <v>500</v>
@@ -7764,7 +7764,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7822,7 +7822,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.4549560546875</v>
+        <v>3.45495581626892</v>
       </c>
       <c r="H257" t="n">
         <v>9000</v>
@@ -7851,7 +7851,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G258" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H258" t="n">
         <v>11500</v>
@@ -7880,7 +7880,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>3.60288906097412</v>
+        <v>3.6028892993927</v>
       </c>
       <c r="H259" t="n">
         <v>2500</v>
@@ -7909,7 +7909,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>3.60288906097412</v>
+        <v>3.6028892993927</v>
       </c>
       <c r="H260" t="n">
         <v>10500</v>
@@ -7967,7 +7967,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H262" t="n">
         <v>18500</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.59811687469482</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H265" t="n">
         <v>6000</v>
@@ -8170,7 +8170,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G269" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H269" t="n">
         <v>8000</v>
@@ -8199,7 +8199,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G270" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8257,7 +8257,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G272" t="n">
-        <v>3.39769172668457</v>
+        <v>3.39769148826599</v>
       </c>
       <c r="H272" t="n">
         <v>5000</v>
@@ -8431,7 +8431,7 @@
         <v>3.5</v>
       </c>
       <c r="G278" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8576,7 +8576,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>3.5</v>
       </c>
       <c r="G284" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8721,7 +8721,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>3.18772172927856</v>
+        <v>3.18772149085999</v>
       </c>
       <c r="H288" t="n">
         <v>500</v>
@@ -8779,7 +8779,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>3.51222062110901</v>
+        <v>3.51222038269043</v>
       </c>
       <c r="H290" t="n">
         <v>10500</v>
@@ -8808,7 +8808,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.59811687469482</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H292" t="n">
         <v>46500</v>
@@ -8895,7 +8895,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H294" t="n">
         <v>2000</v>
@@ -8953,7 +8953,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H296" t="n">
         <v>14500</v>
@@ -8982,7 +8982,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H297" t="n">
         <v>30500</v>
@@ -9069,7 +9069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H300" t="n">
         <v>26000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535143852234</v>
+        <v>3.86535167694092</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9301,7 +9301,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>3.80808687210083</v>
+        <v>3.80808663368225</v>
       </c>
       <c r="H308" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H309" t="n">
         <v>13500</v>
@@ -9446,7 +9446,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H313" t="n">
         <v>6000</v>
@@ -9504,7 +9504,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>3.75082230567932</v>
+        <v>3.75082206726074</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H316" t="n">
         <v>7000</v>
@@ -9562,7 +9562,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9591,7 +9591,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H318" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H319" t="n">
         <v>3500</v>
@@ -9649,7 +9649,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9823,7 +9823,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H326" t="n">
         <v>2000</v>
@@ -9881,7 +9881,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H328" t="n">
         <v>7000</v>
@@ -9910,7 +9910,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H338" t="n">
         <v>500</v>
@@ -10200,7 +10200,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>3.55039668083191</v>
+        <v>3.55039691925049</v>
       </c>
       <c r="H339" t="n">
         <v>500</v>
@@ -10229,7 +10229,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G340" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H340" t="n">
         <v>2500</v>
@@ -10374,7 +10374,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10403,7 +10403,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H347" t="n">
         <v>1500</v>
@@ -10461,7 +10461,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H348" t="n">
         <v>3000</v>
@@ -10780,7 +10780,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>3.72219014167786</v>
+        <v>3.72219038009644</v>
       </c>
       <c r="H359" t="n">
         <v>2500</v>
@@ -10809,7 +10809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H360" t="n">
         <v>9500</v>
@@ -10838,7 +10838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036667823792</v>
+        <v>3.76036643981934</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G370" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H370" t="n">
         <v>2000</v>
@@ -11128,7 +11128,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G371" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G377" t="n">
-        <v>3.55039668083191</v>
+        <v>3.55039691925049</v>
       </c>
       <c r="H377" t="n">
         <v>3500</v>
@@ -11331,7 +11331,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55039668083191</v>
+        <v>3.55039691925049</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.59811687469482</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H380" t="n">
         <v>4000</v>
@@ -11418,7 +11418,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.59811687469482</v>
+        <v>3.59811735153198</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G385" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H385" t="n">
         <v>7000</v>
@@ -11563,7 +11563,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H387" t="n">
         <v>43000</v>
@@ -11621,7 +11621,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G388" t="n">
-        <v>3.36905932426453</v>
+        <v>3.36905908584595</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11766,7 +11766,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H393" t="n">
         <v>6500</v>
@@ -11795,7 +11795,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G394" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H396" t="n">
         <v>8000</v>
@@ -11911,7 +11911,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.50267672538757</v>
+        <v>3.50267648696899</v>
       </c>
       <c r="H398" t="n">
         <v>1000</v>
@@ -12056,7 +12056,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>3.54085254669189</v>
+        <v>3.54085278511047</v>
       </c>
       <c r="H403" t="n">
         <v>2000</v>
@@ -12085,7 +12085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>3.53130841255188</v>
+        <v>3.53130865097046</v>
       </c>
       <c r="H404" t="n">
         <v>500</v>
@@ -12114,7 +12114,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H405" t="n">
         <v>5500</v>
@@ -12143,7 +12143,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>3.67446947097778</v>
+        <v>3.67446970939636</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12172,7 +12172,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G407" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H407" t="n">
         <v>2500</v>
@@ -12230,7 +12230,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G409" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H409" t="n">
         <v>1000</v>
@@ -12259,7 +12259,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H410" t="n">
         <v>1500</v>
@@ -12288,7 +12288,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G411" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H411" t="n">
         <v>6000</v>
@@ -12375,7 +12375,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G414" t="n">
-        <v>3.68401384353638</v>
+        <v>3.6840136051178</v>
       </c>
       <c r="H414" t="n">
         <v>500</v>
@@ -12404,7 +12404,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>3.65538144111633</v>
+        <v>3.65538167953491</v>
       </c>
       <c r="H415" t="n">
         <v>2500</v>
@@ -12433,7 +12433,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492557525635</v>
+        <v>3.66492581367493</v>
       </c>
       <c r="H416" t="n">
         <v>2500</v>
@@ -12665,7 +12665,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G425" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H425" t="n">
         <v>500</v>
@@ -12752,7 +12752,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H427" t="n">
         <v>2500</v>
@@ -12839,7 +12839,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H430" t="n">
         <v>4000</v>
@@ -12868,7 +12868,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H431" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G433" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H433" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H434" t="n">
         <v>2000</v>
@@ -12984,7 +12984,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H435" t="n">
         <v>3500</v>
@@ -13332,7 +13332,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H447" t="n">
         <v>51500</v>
@@ -13361,7 +13361,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H455" t="n">
         <v>2500</v>
@@ -13622,7 +13622,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H468" t="n">
         <v>2500</v>
@@ -13970,7 +13970,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G469" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H469" t="n">
         <v>2000</v>
@@ -14028,7 +14028,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H471" t="n">
         <v>8500</v>
@@ -14057,7 +14057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H472" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H474" t="n">
         <v>5500</v>
@@ -14144,7 +14144,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425921440125</v>
       </c>
       <c r="H475" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H476" t="n">
         <v>7500</v>
@@ -14202,7 +14202,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H477" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H482" t="n">
         <v>2500</v>
@@ -14521,7 +14521,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G488" t="n">
-        <v>3.45092940330505</v>
+        <v>3.45092964172363</v>
       </c>
       <c r="H488" t="n">
         <v>2500</v>
@@ -14579,7 +14579,7 @@
         <v>3.5</v>
       </c>
       <c r="G490" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H490" t="n">
         <v>4000</v>
@@ -14608,7 +14608,7 @@
         <v>3.5</v>
       </c>
       <c r="G491" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H491" t="n">
         <v>8500</v>
@@ -14840,7 +14840,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426473617554</v>
+        <v>3.35426497459412</v>
       </c>
       <c r="H499" t="n">
         <v>6500</v>
@@ -14869,7 +14869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H500" t="n">
         <v>5500</v>
@@ -14898,7 +14898,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G501" t="n">
-        <v>3.45092940330505</v>
+        <v>3.45092964172363</v>
       </c>
       <c r="H501" t="n">
         <v>6500</v>
@@ -14985,7 +14985,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>3.52826166152954</v>
+        <v>3.52826142311096</v>
       </c>
       <c r="H504" t="n">
         <v>4500</v>
@@ -15043,7 +15043,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H506" t="n">
         <v>2000</v>
@@ -15072,7 +15072,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G507" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15275,7 +15275,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H514" t="n">
         <v>3500</v>
@@ -15565,7 +15565,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G524" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H524" t="n">
         <v>13000</v>
@@ -15623,7 +15623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G526" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H526" t="n">
         <v>6000</v>
@@ -15681,7 +15681,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H528" t="n">
         <v>7500</v>
@@ -15710,7 +15710,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H529" t="n">
         <v>7500</v>
@@ -15739,7 +15739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G530" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H530" t="n">
         <v>8000</v>
@@ -15768,7 +15768,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H531" t="n">
         <v>500</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H532" t="n">
         <v>6000</v>
@@ -15913,7 +15913,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H536" t="n">
         <v>500</v>
@@ -16000,7 +16000,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.75059056282043</v>
+        <v>3.75059032440186</v>
       </c>
       <c r="H539" t="n">
         <v>12000</v>
@@ -16261,7 +16261,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H548" t="n">
         <v>2500</v>
@@ -16290,7 +16290,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H549" t="n">
         <v>2500</v>
@@ -16319,7 +16319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16493,7 +16493,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H556" t="n">
         <v>4500</v>
@@ -16522,7 +16522,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H557" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H559" t="n">
         <v>2500</v>
@@ -16609,7 +16609,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H560" t="n">
         <v>2500</v>
@@ -16725,7 +16725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H565" t="n">
         <v>7000</v>
@@ -16783,7 +16783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -16899,7 +16899,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G570" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H570" t="n">
         <v>1000</v>
@@ -16928,7 +16928,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G571" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G573" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H575" t="n">
         <v>13000</v>
@@ -17189,7 +17189,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H580" t="n">
         <v>8500</v>
@@ -17363,7 +17363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H586" t="n">
         <v>5500</v>
@@ -17479,7 +17479,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H590" t="n">
         <v>4000</v>
@@ -17508,7 +17508,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G592" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G593" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H599" t="n">
         <v>500</v>
@@ -17769,7 +17769,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17798,7 +17798,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17885,7 +17885,7 @@
         <v>3.5</v>
       </c>
       <c r="G604" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H604" t="n">
         <v>6500</v>
@@ -18001,7 +18001,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H608" t="n">
         <v>19500</v>
@@ -18030,7 +18030,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H609" t="n">
         <v>2000</v>
@@ -18059,7 +18059,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H610" t="n">
         <v>5000</v>
@@ -18088,7 +18088,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G611" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H611" t="n">
         <v>3000</v>
@@ -18117,7 +18117,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H612" t="n">
         <v>500</v>
@@ -18146,7 +18146,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H613" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H622" t="n">
         <v>4500</v>
@@ -18436,7 +18436,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H623" t="n">
         <v>1000</v>
@@ -18494,7 +18494,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H625" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H636" t="n">
         <v>7000</v>
@@ -18871,7 +18871,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -18900,7 +18900,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G639" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H639" t="n">
         <v>18000</v>
@@ -19074,7 +19074,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>3.73125720024109</v>
+        <v>3.73125696182251</v>
       </c>
       <c r="H645" t="n">
         <v>7500</v>
@@ -19132,7 +19132,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H647" t="n">
         <v>8500</v>
@@ -19161,7 +19161,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H650" t="n">
         <v>500</v>
@@ -19248,7 +19248,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H651" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19509,7 +19509,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H660" t="n">
         <v>10500</v>
@@ -19538,7 +19538,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H661" t="n">
         <v>10000</v>
@@ -19567,7 +19567,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392565727234</v>
       </c>
       <c r="H662" t="n">
         <v>1000</v>
@@ -19596,7 +19596,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H663" t="n">
         <v>8000</v>
@@ -19654,7 +19654,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H665" t="n">
         <v>12000</v>
@@ -19683,7 +19683,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H666" t="n">
         <v>10500</v>
@@ -19712,7 +19712,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H667" t="n">
         <v>13000</v>
@@ -19741,7 +19741,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H668" t="n">
         <v>4000</v>
@@ -19944,7 +19944,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H675" t="n">
         <v>2500</v>
@@ -20060,7 +20060,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H679" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H681" t="n">
         <v>94000</v>
@@ -20147,7 +20147,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20234,7 +20234,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H687" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20524,7 +20524,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H695" t="n">
         <v>10500</v>
@@ -21104,7 +21104,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H715" t="n">
         <v>12500</v>
@@ -21133,7 +21133,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H723" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H730" t="n">
         <v>500</v>
@@ -21713,7 +21713,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H736" t="n">
         <v>2000</v>
@@ -21974,7 +21974,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22003,7 +22003,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H746" t="n">
         <v>500</v>
@@ -22061,7 +22061,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H748" t="n">
         <v>8000</v>
@@ -22090,7 +22090,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H749" t="n">
         <v>500</v>
@@ -22235,7 +22235,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H754" t="n">
         <v>7000</v>
@@ -22351,7 +22351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H758" t="n">
         <v>16000</v>
@@ -22438,7 +22438,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H761" t="n">
         <v>500</v>
@@ -22467,7 +22467,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H766" t="n">
         <v>1000</v>
@@ -22612,7 +22612,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H770" t="n">
         <v>4000</v>
@@ -22786,7 +22786,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225507736206</v>
+        <v>4.13225555419922</v>
       </c>
       <c r="H773" t="n">
         <v>41000</v>
@@ -23018,7 +23018,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H781" t="n">
         <v>8500</v>
@@ -23076,7 +23076,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H783" t="n">
         <v>16500</v>
@@ -23105,7 +23105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H785" t="n">
         <v>26000</v>
@@ -23163,7 +23163,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H786" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H787" t="n">
         <v>3500</v>
@@ -23221,7 +23221,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H788" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809734344482</v>
+        <v>4.32809686660767</v>
       </c>
       <c r="H790" t="n">
         <v>7500</v>
@@ -23395,7 +23395,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H794" t="n">
         <v>1000</v>
@@ -23743,7 +23743,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.6806116104126</v>
+        <v>4.68061208724976</v>
       </c>
       <c r="H808" t="n">
         <v>7500</v>
@@ -23946,7 +23946,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71977996826172</v>
+        <v>4.71978044509888</v>
       </c>
       <c r="H818" t="n">
         <v>3500</v>
@@ -24207,7 +24207,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H822" t="n">
         <v>6500</v>
@@ -24236,7 +24236,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H827" t="n">
         <v>2000</v>
@@ -24381,7 +24381,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H831" t="n">
         <v>500</v>
@@ -24497,7 +24497,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -24816,7 +24816,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H843" t="n">
         <v>500</v>
@@ -25164,7 +25164,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H855" t="n">
         <v>2000</v>
@@ -25686,7 +25686,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H873" t="n">
         <v>500</v>
@@ -25715,7 +25715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -25889,7 +25889,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H881" t="n">
         <v>1500</v>
@@ -25947,7 +25947,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -25976,7 +25976,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26063,7 +26063,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H886" t="n">
         <v>2000</v>
@@ -26092,7 +26092,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H887" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H889" t="n">
         <v>2500</v>
@@ -26179,7 +26179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H892" t="n">
         <v>55000</v>
@@ -26266,7 +26266,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H893" t="n">
         <v>3000</v>
@@ -26295,7 +26295,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H895" t="n">
         <v>11500</v>
@@ -26469,7 +26469,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770086288452</v>
+        <v>4.81770038604736</v>
       </c>
       <c r="H900" t="n">
         <v>6500</v>
@@ -26556,7 +26556,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26730,7 +26730,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H909" t="n">
         <v>11000</v>
@@ -27020,7 +27020,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H919" t="n">
         <v>6500</v>
@@ -27107,7 +27107,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875951766968</v>
+        <v>5.23875999450684</v>
       </c>
       <c r="H922" t="n">
         <v>19000</v>
@@ -27194,7 +27194,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356199264526</v>
+        <v>5.48356151580811</v>
       </c>
       <c r="H925" t="n">
         <v>22000</v>
@@ -27339,7 +27339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H930" t="n">
         <v>16000</v>
@@ -27368,7 +27368,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H931" t="n">
         <v>3000</v>
@@ -41566,13 +41566,13 @@
         <v>46322.3333333333</v>
       </c>
       <c r="C1421" t="n">
-        <v>5.69999980926514</v>
+        <v>5.55000019073486</v>
       </c>
       <c r="D1421" t="n">
-        <v>5.69999980926514</v>
+        <v>5.55000019073486</v>
       </c>
       <c r="E1421" t="n">
-        <v>5.59999990463257</v>
+        <v>5.55000019073486</v>
       </c>
       <c r="F1421" t="n">
         <v>5.55000019073486</v>
@@ -41584,6 +41584,35 @@
         <v>500</v>
       </c>
       <c r="I1421" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1422" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1422" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>5.55000019073486</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="H1422" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I1422" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -630,7 +630,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246391296387</v>
+        <v>3.40246367454529</v>
       </c>
       <c r="H9" t="n">
         <v>56500</v>
@@ -746,7 +746,7 @@
         <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H13" t="n">
         <v>26500</v>
@@ -775,7 +775,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H14" t="n">
         <v>78500</v>
@@ -833,7 +833,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H16" t="n">
         <v>34500</v>
@@ -862,7 +862,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.29747891426086</v>
+        <v>3.29747867584229</v>
       </c>
       <c r="H17" t="n">
         <v>15000</v>
@@ -1065,7 +1065,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H24" t="n">
         <v>48500</v>
@@ -1152,7 +1152,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611107826233</v>
+        <v>3.32611083984375</v>
       </c>
       <c r="H27" t="n">
         <v>10000</v>
@@ -1181,7 +1181,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H28" t="n">
         <v>14000</v>
@@ -1210,7 +1210,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G29" t="n">
-        <v>3.40723562240601</v>
+        <v>3.40723538398743</v>
       </c>
       <c r="H29" t="n">
         <v>12000</v>
@@ -1297,7 +1297,7 @@
         <v>3.5</v>
       </c>
       <c r="G32" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H32" t="n">
         <v>20500</v>
@@ -1442,7 +1442,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H37" t="n">
         <v>59500</v>
@@ -1529,7 +1529,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G40" t="n">
-        <v>3.75559425354004</v>
+        <v>3.75559449195862</v>
       </c>
       <c r="H40" t="n">
         <v>132500</v>
@@ -1732,7 +1732,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380126953125</v>
+        <v>3.58380103111267</v>
       </c>
       <c r="H47" t="n">
         <v>18000</v>
@@ -1848,7 +1848,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.607661485672</v>
+        <v>3.60766124725342</v>
       </c>
       <c r="H51" t="n">
         <v>24500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1906,7 +1906,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H53" t="n">
         <v>14000</v>
@@ -1964,7 +1964,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H55" t="n">
         <v>8000</v>
@@ -2109,7 +2109,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H60" t="n">
         <v>16000</v>
@@ -2138,7 +2138,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G61" t="n">
-        <v>3.40723562240601</v>
+        <v>3.40723538398743</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2254,7 +2254,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836016654968</v>
+        <v>3.48836040496826</v>
       </c>
       <c r="H65" t="n">
         <v>22000</v>
@@ -2283,7 +2283,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H66" t="n">
         <v>9500</v>
@@ -2312,7 +2312,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H67" t="n">
         <v>6000</v>
@@ -2341,7 +2341,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>3.41200757026672</v>
+        <v>3.4120078086853</v>
       </c>
       <c r="H68" t="n">
         <v>16500</v>
@@ -2428,7 +2428,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109583854675</v>
+        <v>3.43109607696533</v>
       </c>
       <c r="H71" t="n">
         <v>28500</v>
@@ -2486,7 +2486,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.40723562240601</v>
+        <v>3.40723538398743</v>
       </c>
       <c r="H73" t="n">
         <v>5000</v>
@@ -2544,7 +2544,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H75" t="n">
         <v>6000</v>
@@ -2573,7 +2573,7 @@
         <v>3.5</v>
       </c>
       <c r="G76" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H76" t="n">
         <v>118500</v>
@@ -2718,7 +2718,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H83" t="n">
         <v>4500</v>
@@ -2834,7 +2834,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.3117949962616</v>
+        <v>3.31179475784302</v>
       </c>
       <c r="H85" t="n">
         <v>43000</v>
@@ -2892,7 +2892,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H87" t="n">
         <v>8000</v>
@@ -3008,7 +3008,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H91" t="n">
         <v>9000</v>
@@ -3356,7 +3356,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G103" t="n">
-        <v>3.40723562240601</v>
+        <v>3.40723538398743</v>
       </c>
       <c r="H103" t="n">
         <v>17500</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3501,7 +3501,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H108" t="n">
         <v>18000</v>
@@ -3530,7 +3530,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380126953125</v>
+        <v>3.58380103111267</v>
       </c>
       <c r="H109" t="n">
         <v>8500</v>
@@ -3675,7 +3675,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H114" t="n">
         <v>28000</v>
@@ -3762,7 +3762,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.08486557006836</v>
+        <v>4.0848650932312</v>
       </c>
       <c r="H117" t="n">
         <v>47000</v>
@@ -3878,7 +3878,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G121" t="n">
-        <v>4.06577730178833</v>
+        <v>4.06577682495117</v>
       </c>
       <c r="H121" t="n">
         <v>29500</v>
@@ -3907,7 +3907,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G122" t="n">
-        <v>4.11349678039551</v>
+        <v>4.11349725723267</v>
       </c>
       <c r="H122" t="n">
         <v>20500</v>
@@ -4197,7 +4197,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>3.96079254150391</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H132" t="n">
         <v>5500</v>
@@ -4226,7 +4226,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G133" t="n">
-        <v>3.96556401252747</v>
+        <v>3.96556448936462</v>
       </c>
       <c r="H133" t="n">
         <v>15500</v>
@@ -4313,7 +4313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G136" t="n">
-        <v>3.96079254150391</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H136" t="n">
         <v>6500</v>
@@ -4603,7 +4603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>3.96079254150391</v>
+        <v>3.96079206466675</v>
       </c>
       <c r="H146" t="n">
         <v>2000</v>
@@ -4661,7 +4661,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G148" t="n">
-        <v>4.02760076522827</v>
+        <v>4.02760028839111</v>
       </c>
       <c r="H148" t="n">
         <v>15500</v>
@@ -4690,7 +4690,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>4.01805686950684</v>
+        <v>4.01805639266968</v>
       </c>
       <c r="H149" t="n">
         <v>10000</v>
@@ -4748,7 +4748,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942422866821</v>
+        <v>3.98942375183105</v>
       </c>
       <c r="H151" t="n">
         <v>2500</v>
@@ -4835,7 +4835,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.87489557266235</v>
+        <v>3.87489533424377</v>
       </c>
       <c r="H154" t="n">
         <v>3000</v>
@@ -4980,7 +4980,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>3.87489557266235</v>
+        <v>3.87489533424377</v>
       </c>
       <c r="H159" t="n">
         <v>6000</v>
@@ -5038,7 +5038,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.89398336410522</v>
+        <v>3.89398312568665</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5241,7 +5241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G168" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5386,7 +5386,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.607661485672</v>
+        <v>3.60766124725342</v>
       </c>
       <c r="H173" t="n">
         <v>6000</v>
@@ -5444,7 +5444,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G175" t="n">
-        <v>3.61243319511414</v>
+        <v>3.61243343353271</v>
       </c>
       <c r="H175" t="n">
         <v>9000</v>
@@ -5734,7 +5734,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383151054382</v>
+        <v>3.37383127212524</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5792,7 +5792,7 @@
         <v>3.5</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H187" t="n">
         <v>125000</v>
@@ -5821,7 +5821,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H188" t="n">
         <v>10500</v>
@@ -5908,7 +5908,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H191" t="n">
         <v>6000</v>
@@ -5995,7 +5995,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H194" t="n">
         <v>1500</v>
@@ -6053,7 +6053,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6082,7 +6082,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G197" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H198" t="n">
         <v>41000</v>
@@ -6227,7 +6227,7 @@
         <v>3.5</v>
       </c>
       <c r="G202" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H202" t="n">
         <v>20500</v>
@@ -6256,7 +6256,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H203" t="n">
         <v>45000</v>
@@ -6430,7 +6430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H209" t="n">
         <v>5000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6575,7 +6575,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G215" t="n">
-        <v>3.52176451683044</v>
+        <v>3.52176475524902</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G216" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H216" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948494911194</v>
+        <v>3.56948471069336</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G222" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H222" t="n">
         <v>1000</v>
@@ -6952,7 +6952,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H227" t="n">
         <v>40000</v>
@@ -7068,7 +7068,7 @@
         <v>3.5</v>
       </c>
       <c r="G231" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H231" t="n">
         <v>6500</v>
@@ -7155,7 +7155,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H234" t="n">
         <v>3000</v>
@@ -7445,7 +7445,7 @@
         <v>3.5</v>
       </c>
       <c r="G244" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H244" t="n">
         <v>5000</v>
@@ -7532,7 +7532,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>3.21635389328003</v>
+        <v>3.21635413169861</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>3.5</v>
       </c>
       <c r="G249" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H249" t="n">
         <v>5000</v>
@@ -7648,7 +7648,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>3.29747891426086</v>
+        <v>3.29747867584229</v>
       </c>
       <c r="H251" t="n">
         <v>4500</v>
@@ -7764,7 +7764,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7880,7 +7880,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>3.6028892993927</v>
+        <v>3.60288906097412</v>
       </c>
       <c r="H259" t="n">
         <v>2500</v>
@@ -7909,7 +7909,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>3.6028892993927</v>
+        <v>3.60288906097412</v>
       </c>
       <c r="H260" t="n">
         <v>10500</v>
@@ -7938,7 +7938,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H261" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.59811735153198</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H265" t="n">
         <v>6000</v>
@@ -8170,7 +8170,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G269" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H269" t="n">
         <v>8000</v>
@@ -8199,7 +8199,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G270" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8431,7 +8431,7 @@
         <v>3.5</v>
       </c>
       <c r="G278" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8576,7 +8576,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316283226013</v>
+        <v>3.28316259384155</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>3.5</v>
       </c>
       <c r="G284" t="n">
-        <v>3.34042716026306</v>
+        <v>3.34042739868164</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8721,7 +8721,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>3.18772149085999</v>
+        <v>3.18772172927856</v>
       </c>
       <c r="H288" t="n">
         <v>500</v>
@@ -8808,7 +8808,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.59811735153198</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H292" t="n">
         <v>46500</v>
@@ -8982,7 +8982,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G297" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H297" t="n">
         <v>30500</v>
@@ -9069,7 +9069,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G300" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H300" t="n">
         <v>26000</v>
@@ -9127,7 +9127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G302" t="n">
-        <v>3.86535167694092</v>
+        <v>3.86535143852234</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9359,7 +9359,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H310" t="n">
         <v>8000</v>
@@ -9446,7 +9446,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H313" t="n">
         <v>6000</v>
@@ -9533,7 +9533,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H316" t="n">
         <v>7000</v>
@@ -9562,7 +9562,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9591,7 +9591,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H318" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H319" t="n">
         <v>3500</v>
@@ -9649,7 +9649,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945446968079</v>
+        <v>3.77945470809937</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9881,7 +9881,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H328" t="n">
         <v>7000</v>
@@ -9910,7 +9910,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G329" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G330" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G332" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H338" t="n">
         <v>500</v>
@@ -10229,7 +10229,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G340" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H340" t="n">
         <v>2500</v>
@@ -10403,7 +10403,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H348" t="n">
         <v>3000</v>
@@ -10809,7 +10809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H360" t="n">
         <v>9500</v>
@@ -10838,7 +10838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H366" t="n">
         <v>1500</v>
@@ -11012,7 +11012,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>3.76036643981934</v>
+        <v>3.76036667823792</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G370" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H370" t="n">
         <v>2000</v>
@@ -11128,7 +11128,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G371" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.59811735153198</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H380" t="n">
         <v>4000</v>
@@ -11418,7 +11418,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.59811735153198</v>
+        <v>3.5981171131134</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.48358821868896</v>
+        <v>3.48358845710754</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H387" t="n">
         <v>43000</v>
@@ -11766,7 +11766,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H393" t="n">
         <v>6500</v>
@@ -11795,7 +11795,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G394" t="n">
-        <v>3.47404408454895</v>
+        <v>3.47404432296753</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11853,7 +11853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814759254456</v>
+        <v>3.38814735412598</v>
       </c>
       <c r="H396" t="n">
         <v>8000</v>
@@ -11911,7 +11911,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.50267648696899</v>
+        <v>3.50267672538757</v>
       </c>
       <c r="H398" t="n">
         <v>1000</v>
@@ -11998,7 +11998,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857297897339</v>
+        <v>3.58857274055481</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310211181641</v>
+        <v>3.70310235023499</v>
       </c>
       <c r="H405" t="n">
         <v>5500</v>
@@ -12143,7 +12143,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>3.67446970939636</v>
+        <v>3.67446947097778</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12230,7 +12230,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G409" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H409" t="n">
         <v>1000</v>
@@ -12288,7 +12288,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G411" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H411" t="n">
         <v>6000</v>
@@ -12375,7 +12375,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G414" t="n">
-        <v>3.6840136051178</v>
+        <v>3.68401384353638</v>
       </c>
       <c r="H414" t="n">
         <v>500</v>
@@ -12665,7 +12665,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G425" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H425" t="n">
         <v>500</v>
@@ -12752,7 +12752,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H427" t="n">
         <v>2500</v>
@@ -12839,7 +12839,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H430" t="n">
         <v>4000</v>
@@ -12868,7 +12868,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H431" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G433" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H433" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H434" t="n">
         <v>2000</v>
@@ -12984,7 +12984,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692719459534</v>
+        <v>3.56692743301392</v>
       </c>
       <c r="H435" t="n">
         <v>3500</v>
@@ -13332,7 +13332,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H447" t="n">
         <v>51500</v>
@@ -13361,7 +13361,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H455" t="n">
         <v>2500</v>
@@ -13622,7 +13622,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692719459534</v>
+        <v>3.56692743301392</v>
       </c>
       <c r="H468" t="n">
         <v>2500</v>
@@ -13970,7 +13970,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G469" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H469" t="n">
         <v>2000</v>
@@ -14028,7 +14028,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H471" t="n">
         <v>8500</v>
@@ -14057,7 +14057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H472" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H474" t="n">
         <v>5500</v>
@@ -14144,7 +14144,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425921440125</v>
+        <v>3.64425897598267</v>
       </c>
       <c r="H475" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H476" t="n">
         <v>7500</v>
@@ -14202,7 +14202,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H477" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H482" t="n">
         <v>2500</v>
@@ -14521,7 +14521,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G488" t="n">
-        <v>3.45092964172363</v>
+        <v>3.45092940330505</v>
       </c>
       <c r="H488" t="n">
         <v>2500</v>
@@ -14579,7 +14579,7 @@
         <v>3.5</v>
       </c>
       <c r="G490" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H490" t="n">
         <v>4000</v>
@@ -14608,7 +14608,7 @@
         <v>3.5</v>
       </c>
       <c r="G491" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H491" t="n">
         <v>8500</v>
@@ -14840,7 +14840,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426497459412</v>
+        <v>3.35426473617554</v>
       </c>
       <c r="H499" t="n">
         <v>6500</v>
@@ -14869,7 +14869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H500" t="n">
         <v>5500</v>
@@ -14898,7 +14898,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G501" t="n">
-        <v>3.45092964172363</v>
+        <v>3.45092940330505</v>
       </c>
       <c r="H501" t="n">
         <v>6500</v>
@@ -14985,7 +14985,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>3.52826142311096</v>
+        <v>3.52826166152954</v>
       </c>
       <c r="H504" t="n">
         <v>4500</v>
@@ -15043,7 +15043,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H506" t="n">
         <v>2000</v>
@@ -15072,7 +15072,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G507" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15275,7 +15275,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>3.54759430885315</v>
+        <v>3.54759454727173</v>
       </c>
       <c r="H514" t="n">
         <v>3500</v>
@@ -15565,7 +15565,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G524" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H524" t="n">
         <v>13000</v>
@@ -15623,7 +15623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G526" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H526" t="n">
         <v>6000</v>
@@ -15681,7 +15681,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H528" t="n">
         <v>7500</v>
@@ -15710,7 +15710,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H529" t="n">
         <v>7500</v>
@@ -15739,7 +15739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G530" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H530" t="n">
         <v>8000</v>
@@ -15768,7 +15768,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H531" t="n">
         <v>500</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H532" t="n">
         <v>6000</v>
@@ -15913,7 +15913,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H536" t="n">
         <v>500</v>
@@ -16000,7 +16000,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.75059032440186</v>
+        <v>3.75059056282043</v>
       </c>
       <c r="H539" t="n">
         <v>12000</v>
@@ -16261,7 +16261,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H548" t="n">
         <v>2500</v>
@@ -16290,7 +16290,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H549" t="n">
         <v>2500</v>
@@ -16319,7 +16319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16493,7 +16493,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H556" t="n">
         <v>4500</v>
@@ -16522,7 +16522,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H557" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H559" t="n">
         <v>2500</v>
@@ -16609,7 +16609,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H560" t="n">
         <v>2500</v>
@@ -16725,7 +16725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H565" t="n">
         <v>7000</v>
@@ -16783,7 +16783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -16899,7 +16899,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G570" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H570" t="n">
         <v>1000</v>
@@ -16928,7 +16928,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G571" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G573" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H575" t="n">
         <v>13000</v>
@@ -17189,7 +17189,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H580" t="n">
         <v>8500</v>
@@ -17363,7 +17363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H586" t="n">
         <v>5500</v>
@@ -17479,7 +17479,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H590" t="n">
         <v>4000</v>
@@ -17508,7 +17508,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G592" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G593" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H599" t="n">
         <v>500</v>
@@ -17769,7 +17769,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17798,7 +17798,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17885,7 +17885,7 @@
         <v>3.5</v>
       </c>
       <c r="G604" t="n">
-        <v>3.3832643032074</v>
+        <v>3.38326454162598</v>
       </c>
       <c r="H604" t="n">
         <v>6500</v>
@@ -18001,7 +18001,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H608" t="n">
         <v>19500</v>
@@ -18030,7 +18030,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H609" t="n">
         <v>2000</v>
@@ -18059,7 +18059,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H610" t="n">
         <v>5000</v>
@@ -18088,7 +18088,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G611" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H611" t="n">
         <v>3000</v>
@@ -18117,7 +18117,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H612" t="n">
         <v>500</v>
@@ -18146,7 +18146,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H613" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H622" t="n">
         <v>4500</v>
@@ -18436,7 +18436,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H623" t="n">
         <v>1000</v>
@@ -18494,7 +18494,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H625" t="n">
         <v>2000</v>
@@ -18813,7 +18813,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H636" t="n">
         <v>7000</v>
@@ -18871,7 +18871,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -18900,7 +18900,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G639" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H639" t="n">
         <v>18000</v>
@@ -19074,7 +19074,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>3.73125696182251</v>
+        <v>3.73125720024109</v>
       </c>
       <c r="H645" t="n">
         <v>7500</v>
@@ -19132,7 +19132,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H647" t="n">
         <v>8500</v>
@@ -19161,7 +19161,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H650" t="n">
         <v>500</v>
@@ -19248,7 +19248,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525964736938</v>
+        <v>3.61525940895081</v>
       </c>
       <c r="H651" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859474182129</v>
+        <v>3.51859498023987</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19509,7 +19509,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H660" t="n">
         <v>10500</v>
@@ -19538,7 +19538,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H661" t="n">
         <v>10000</v>
@@ -19567,7 +19567,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392565727234</v>
+        <v>3.65392541885376</v>
       </c>
       <c r="H662" t="n">
         <v>1000</v>
@@ -19596,7 +19596,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H663" t="n">
         <v>8000</v>
@@ -19654,7 +19654,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H665" t="n">
         <v>12000</v>
@@ -19683,7 +19683,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H666" t="n">
         <v>10500</v>
@@ -19712,7 +19712,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H667" t="n">
         <v>13000</v>
@@ -19741,7 +19741,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>3.63459253311157</v>
+        <v>3.63459229469299</v>
       </c>
       <c r="H668" t="n">
         <v>4000</v>
@@ -19944,7 +19944,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H675" t="n">
         <v>2500</v>
@@ -20060,7 +20060,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932498931885</v>
+        <v>3.79932522773743</v>
       </c>
       <c r="H679" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H681" t="n">
         <v>94000</v>
@@ -20147,7 +20147,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932498931885</v>
+        <v>3.79932522773743</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20234,7 +20234,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H687" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974057197571</v>
+        <v>3.77974081039429</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20524,7 +20524,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H695" t="n">
         <v>10500</v>
@@ -21104,7 +21104,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H715" t="n">
         <v>12500</v>
@@ -21133,7 +21133,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H723" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H730" t="n">
         <v>500</v>
@@ -21713,7 +21713,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H736" t="n">
         <v>2000</v>
@@ -21974,7 +21974,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22003,7 +22003,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H746" t="n">
         <v>500</v>
@@ -22061,7 +22061,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516630172729</v>
+        <v>3.99516606330872</v>
       </c>
       <c r="H748" t="n">
         <v>8000</v>
@@ -22090,7 +22090,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H749" t="n">
         <v>500</v>
@@ -22235,7 +22235,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H754" t="n">
         <v>7000</v>
@@ -22351,7 +22351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H758" t="n">
         <v>16000</v>
@@ -22438,7 +22438,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H761" t="n">
         <v>500</v>
@@ -22467,7 +22467,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807728767395</v>
+        <v>3.85807752609253</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H766" t="n">
         <v>1000</v>
@@ -22612,7 +22612,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766146659851</v>
+        <v>3.87766170501709</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558236122131</v>
+        <v>3.97558212280273</v>
       </c>
       <c r="H770" t="n">
         <v>4000</v>
@@ -22786,7 +22786,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225555419922</v>
+        <v>4.13225507736206</v>
       </c>
       <c r="H773" t="n">
         <v>41000</v>
@@ -23018,7 +23018,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H781" t="n">
         <v>8500</v>
@@ -23076,7 +23076,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H783" t="n">
         <v>16500</v>
@@ -23105,7 +23105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183973312378</v>
+        <v>4.15183925628662</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H785" t="n">
         <v>26000</v>
@@ -23163,7 +23163,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H786" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H787" t="n">
         <v>3500</v>
@@ -23221,7 +23221,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H788" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809686660767</v>
+        <v>4.32809734344482</v>
       </c>
       <c r="H790" t="n">
         <v>7500</v>
@@ -23395,7 +23395,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H794" t="n">
         <v>1000</v>
@@ -23743,7 +23743,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.68061208724976</v>
+        <v>4.6806116104126</v>
       </c>
       <c r="H808" t="n">
         <v>7500</v>
@@ -23946,7 +23946,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71978044509888</v>
+        <v>4.71977996826172</v>
       </c>
       <c r="H818" t="n">
         <v>3500</v>
@@ -24207,7 +24207,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H822" t="n">
         <v>6500</v>
@@ -24236,7 +24236,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934432983398</v>
+        <v>4.26934480667114</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H827" t="n">
         <v>2000</v>
@@ -24381,7 +24381,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H831" t="n">
         <v>500</v>
@@ -24497,7 +24497,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -24816,7 +24816,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518611907959</v>
+        <v>4.46518564224243</v>
       </c>
       <c r="H843" t="n">
         <v>500</v>
@@ -25164,7 +25164,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H855" t="n">
         <v>2000</v>
@@ -25686,7 +25686,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H873" t="n">
         <v>500</v>
@@ -25715,7 +25715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017597198486</v>
+        <v>4.23017644882202</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -25889,7 +25889,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183973312378</v>
+        <v>4.15183925628662</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H881" t="n">
         <v>1500</v>
@@ -25947,7 +25947,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -25976,7 +25976,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.1714243888855</v>
+        <v>4.17142391204834</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26063,7 +26063,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H886" t="n">
         <v>2000</v>
@@ -26092,7 +26092,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H887" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H889" t="n">
         <v>2500</v>
@@ -26179,7 +26179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.19100856781006</v>
+        <v>4.1910080909729</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H892" t="n">
         <v>55000</v>
@@ -26266,7 +26266,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H893" t="n">
         <v>3000</v>
@@ -26295,7 +26295,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726522445679</v>
+        <v>4.36726570129395</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.28892850875854</v>
+        <v>4.2889289855957</v>
       </c>
       <c r="H895" t="n">
         <v>11500</v>
@@ -26469,7 +26469,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770038604736</v>
+        <v>4.81770086288452</v>
       </c>
       <c r="H900" t="n">
         <v>6500</v>
@@ -26556,7 +26556,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26730,7 +26730,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H909" t="n">
         <v>11000</v>
@@ -27020,7 +27020,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686874389648</v>
+        <v>4.85686922073364</v>
       </c>
       <c r="H919" t="n">
         <v>6500</v>
@@ -27107,7 +27107,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875999450684</v>
+        <v>5.23875951766968</v>
       </c>
       <c r="H922" t="n">
         <v>19000</v>
@@ -27194,7 +27194,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356151580811</v>
+        <v>5.48356199264526</v>
       </c>
       <c r="H925" t="n">
         <v>22000</v>
@@ -27339,7 +27339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772068023682</v>
+        <v>5.28772020339966</v>
       </c>
       <c r="H930" t="n">
         <v>16000</v>
@@ -27368,7 +27368,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772068023682</v>
+        <v>5.28772020339966</v>
       </c>
       <c r="H931" t="n">
         <v>3000</v>
@@ -41595,7 +41595,7 @@
         <v>46323.3333333333</v>
       </c>
       <c r="C1422" t="n">
-        <v>5.69999980926514</v>
+        <v>5.55000019073486</v>
       </c>
       <c r="D1422" t="n">
         <v>5.80000019073486</v>
@@ -41613,6 +41613,35 @@
         <v>28000</v>
       </c>
       <c r="I1422" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1423" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1423" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="H1423" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I1423" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABP.MI.xlsx
+++ b/data/ABP.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G5" t="n">
-        <v>3.19249367713928</v>
+        <v>3.19249391555786</v>
       </c>
       <c r="H5" t="n">
         <v>244500</v>
@@ -630,7 +630,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G9" t="n">
-        <v>3.40246367454529</v>
+        <v>3.40246391296387</v>
       </c>
       <c r="H9" t="n">
         <v>56500</v>
@@ -659,7 +659,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G10" t="n">
-        <v>3.42632365226746</v>
+        <v>3.42632389068604</v>
       </c>
       <c r="H10" t="n">
         <v>32500</v>
@@ -688,7 +688,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H11" t="n">
         <v>56500</v>
@@ -717,7 +717,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H12" t="n">
         <v>32000</v>
@@ -746,7 +746,7 @@
         <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H13" t="n">
         <v>26500</v>
@@ -804,7 +804,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H15" t="n">
         <v>53000</v>
@@ -833,7 +833,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H16" t="n">
         <v>34500</v>
@@ -891,7 +891,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.25930237770081</v>
+        <v>3.25930261611938</v>
       </c>
       <c r="H18" t="n">
         <v>31000</v>
@@ -978,7 +978,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>3.38337540626526</v>
+        <v>3.38337564468384</v>
       </c>
       <c r="H21" t="n">
         <v>32000</v>
@@ -1065,7 +1065,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H24" t="n">
         <v>48500</v>
@@ -1123,7 +1123,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951542854309</v>
       </c>
       <c r="H26" t="n">
         <v>19500</v>
@@ -1152,7 +1152,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32611083984375</v>
+        <v>3.32611107826233</v>
       </c>
       <c r="H27" t="n">
         <v>10000</v>
@@ -1181,7 +1181,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G28" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H28" t="n">
         <v>14000</v>
@@ -1210,7 +1210,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G29" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723562240601</v>
       </c>
       <c r="H29" t="n">
         <v>12000</v>
@@ -1297,7 +1297,7 @@
         <v>3.5</v>
       </c>
       <c r="G32" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H32" t="n">
         <v>20500</v>
@@ -1413,7 +1413,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G36" t="n">
-        <v>3.33565473556519</v>
+        <v>3.33565497398376</v>
       </c>
       <c r="H36" t="n">
         <v>3500</v>
@@ -1442,7 +1442,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H37" t="n">
         <v>59500</v>
@@ -1471,7 +1471,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H38" t="n">
         <v>12500</v>
@@ -1703,7 +1703,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G46" t="n">
-        <v>3.6458375453949</v>
+        <v>3.64583730697632</v>
       </c>
       <c r="H46" t="n">
         <v>12500</v>
@@ -1732,7 +1732,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H47" t="n">
         <v>18000</v>
@@ -1819,7 +1819,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>3.62197756767273</v>
+        <v>3.62197732925415</v>
       </c>
       <c r="H50" t="n">
         <v>6500</v>
@@ -1848,7 +1848,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>3.60766124725342</v>
+        <v>3.60766100883484</v>
       </c>
       <c r="H51" t="n">
         <v>24500</v>
@@ -1877,7 +1877,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G52" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H52" t="n">
         <v>5000</v>
@@ -1906,7 +1906,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G53" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H53" t="n">
         <v>14000</v>
@@ -1964,7 +1964,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H55" t="n">
         <v>8000</v>
@@ -2109,7 +2109,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G60" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H60" t="n">
         <v>16000</v>
@@ -2138,7 +2138,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G61" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723562240601</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2167,7 +2167,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H62" t="n">
         <v>9000</v>
@@ -2254,7 +2254,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>3.48836040496826</v>
+        <v>3.48836016654968</v>
       </c>
       <c r="H65" t="n">
         <v>22000</v>
@@ -2283,7 +2283,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H66" t="n">
         <v>9500</v>
@@ -2312,7 +2312,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H67" t="n">
         <v>6000</v>
@@ -2428,7 +2428,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G71" t="n">
-        <v>3.43109607696533</v>
+        <v>3.43109583854675</v>
       </c>
       <c r="H71" t="n">
         <v>28500</v>
@@ -2457,7 +2457,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H72" t="n">
         <v>22500</v>
@@ -2486,7 +2486,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723562240601</v>
       </c>
       <c r="H73" t="n">
         <v>5000</v>
@@ -2544,7 +2544,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H75" t="n">
         <v>6000</v>
@@ -2573,7 +2573,7 @@
         <v>3.5</v>
       </c>
       <c r="G76" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H76" t="n">
         <v>118500</v>
@@ -2602,7 +2602,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G77" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H77" t="n">
         <v>67000</v>
@@ -2631,7 +2631,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H78" t="n">
         <v>32000</v>
@@ -2689,7 +2689,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G80" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H80" t="n">
         <v>4000</v>
@@ -2718,7 +2718,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H81" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H83" t="n">
         <v>4500</v>
@@ -2805,7 +2805,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G84" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H84" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G85" t="n">
-        <v>3.31179475784302</v>
+        <v>3.3117949962616</v>
       </c>
       <c r="H85" t="n">
         <v>43000</v>
@@ -2863,7 +2863,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G86" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407432556152</v>
       </c>
       <c r="H86" t="n">
         <v>43000</v>
@@ -2892,7 +2892,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H87" t="n">
         <v>8000</v>
@@ -2921,7 +2921,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407432556152</v>
       </c>
       <c r="H88" t="n">
         <v>27500</v>
@@ -3008,7 +3008,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H91" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H95" t="n">
         <v>12000</v>
@@ -3153,7 +3153,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G96" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H96" t="n">
         <v>51000</v>
@@ -3182,7 +3182,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G97" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H97" t="n">
         <v>43000</v>
@@ -3269,7 +3269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063949584961</v>
       </c>
       <c r="H100" t="n">
         <v>29000</v>
@@ -3327,7 +3327,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G102" t="n">
-        <v>3.45495581626892</v>
+        <v>3.45495557785034</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3356,7 +3356,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G103" t="n">
-        <v>3.40723538398743</v>
+        <v>3.40723562240601</v>
       </c>
       <c r="H103" t="n">
         <v>17500</v>
@@ -3472,7 +3472,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G107" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H107" t="n">
         <v>54000</v>
@@ -3501,7 +3501,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H108" t="n">
         <v>18000</v>
@@ -3530,7 +3530,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.58380103111267</v>
+        <v>3.58380126953125</v>
       </c>
       <c r="H109" t="n">
         <v>8500</v>
@@ -3617,7 +3617,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>3.65538167953491</v>
+        <v>3.65538144111633</v>
       </c>
       <c r="H112" t="n">
         <v>29000</v>
@@ -3704,7 +3704,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>3.66492581367493</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H115" t="n">
         <v>19500</v>
@@ -3733,7 +3733,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G116" t="n">
-        <v>4.00374031066895</v>
+        <v>4.0037407875061</v>
       </c>
       <c r="H116" t="n">
         <v>224500</v>
@@ -3791,7 +3791,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>3.97988057136536</v>
+        <v>3.9798800945282</v>
       </c>
       <c r="H118" t="n">
         <v>63000</v>
@@ -3820,7 +3820,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H119" t="n">
         <v>38500</v>
@@ -3936,7 +3936,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G123" t="n">
-        <v>4.09918117523193</v>
+        <v>4.09918165206909</v>
       </c>
       <c r="H123" t="n">
         <v>15000</v>
@@ -3965,7 +3965,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G124" t="n">
-        <v>3.97033596038818</v>
+        <v>3.97033548355103</v>
       </c>
       <c r="H124" t="n">
         <v>38000</v>
@@ -3994,7 +3994,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G125" t="n">
-        <v>3.99896860122681</v>
+        <v>3.99896812438965</v>
       </c>
       <c r="H125" t="n">
         <v>57500</v>
@@ -4052,7 +4052,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G127" t="n">
-        <v>3.92261600494385</v>
+        <v>3.92261552810669</v>
       </c>
       <c r="H127" t="n">
         <v>7500</v>
@@ -4081,7 +4081,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.93215990066528</v>
+        <v>3.93215942382812</v>
       </c>
       <c r="H128" t="n">
         <v>15500</v>
@@ -4110,7 +4110,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>3.97033596038818</v>
+        <v>3.97033548355103</v>
       </c>
       <c r="H129" t="n">
         <v>213000</v>
@@ -4139,7 +4139,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G130" t="n">
-        <v>3.93215990066528</v>
+        <v>3.93215942382812</v>
       </c>
       <c r="H130" t="n">
         <v>15000</v>
@@ -4168,7 +4168,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G131" t="n">
-        <v>3.97033596038818</v>
+        <v>3.97033548355103</v>
       </c>
       <c r="H131" t="n">
         <v>31000</v>
@@ -4255,7 +4255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G134" t="n">
-        <v>4.0085129737854</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H134" t="n">
         <v>2000</v>
@@ -4284,7 +4284,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G135" t="n">
-        <v>3.92261600494385</v>
+        <v>3.92261552810669</v>
       </c>
       <c r="H135" t="n">
         <v>14500</v>
@@ -4342,7 +4342,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H137" t="n">
         <v>12000</v>
@@ -4371,7 +4371,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>3.91307163238525</v>
+        <v>3.91307139396667</v>
       </c>
       <c r="H138" t="n">
         <v>5500</v>
@@ -4400,7 +4400,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G139" t="n">
-        <v>4.00374031066895</v>
+        <v>4.0037407875061</v>
       </c>
       <c r="H139" t="n">
         <v>14000</v>
@@ -4429,7 +4429,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>3.93215990066528</v>
+        <v>3.93215942382812</v>
       </c>
       <c r="H140" t="n">
         <v>2500</v>
@@ -4458,7 +4458,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G141" t="n">
-        <v>3.9417040348053</v>
+        <v>3.94170355796814</v>
       </c>
       <c r="H141" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G143" t="n">
-        <v>3.99896860122681</v>
+        <v>3.99896812438965</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>3.95124793052673</v>
+        <v>3.95124745368958</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4574,7 +4574,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G145" t="n">
-        <v>3.95124793052673</v>
+        <v>3.95124745368958</v>
       </c>
       <c r="H145" t="n">
         <v>2000</v>
@@ -4632,7 +4632,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>4.0085129737854</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H147" t="n">
         <v>6500</v>
@@ -4719,7 +4719,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G150" t="n">
-        <v>4.0085129737854</v>
+        <v>4.00851249694824</v>
       </c>
       <c r="H150" t="n">
         <v>5000</v>
@@ -4748,7 +4748,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G151" t="n">
-        <v>3.98942375183105</v>
+        <v>3.98942422866821</v>
       </c>
       <c r="H151" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G152" t="n">
-        <v>3.9417040348053</v>
+        <v>3.94170355796814</v>
       </c>
       <c r="H152" t="n">
         <v>9500</v>
@@ -4835,7 +4835,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>3.87489533424377</v>
+        <v>3.8748950958252</v>
       </c>
       <c r="H154" t="n">
         <v>3000</v>
@@ -4864,7 +4864,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.88443994522095</v>
+        <v>3.88443970680237</v>
       </c>
       <c r="H155" t="n">
         <v>50000</v>
@@ -4980,7 +4980,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G159" t="n">
-        <v>3.87489533424377</v>
+        <v>3.8748950958252</v>
       </c>
       <c r="H159" t="n">
         <v>6000</v>
@@ -5038,7 +5038,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>3.89398312568665</v>
+        <v>3.89398336410522</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5299,7 +5299,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5357,7 +5357,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>3.64106559753418</v>
+        <v>3.6410653591156</v>
       </c>
       <c r="H172" t="n">
         <v>500</v>
@@ -5386,7 +5386,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G173" t="n">
-        <v>3.60766124725342</v>
+        <v>3.60766100883484</v>
       </c>
       <c r="H173" t="n">
         <v>6000</v>
@@ -5415,7 +5415,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G174" t="n">
-        <v>3.65538167953491</v>
+        <v>3.65538144111633</v>
       </c>
       <c r="H174" t="n">
         <v>5000</v>
@@ -5444,7 +5444,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G175" t="n">
-        <v>3.61243343353271</v>
+        <v>3.61243319511414</v>
       </c>
       <c r="H175" t="n">
         <v>9000</v>
@@ -5502,7 +5502,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H177" t="n">
         <v>500</v>
@@ -5531,7 +5531,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G178" t="n">
-        <v>3.57425689697266</v>
+        <v>3.57425665855408</v>
       </c>
       <c r="H178" t="n">
         <v>19000</v>
@@ -5647,7 +5647,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>3.44063973426819</v>
+        <v>3.44063949584961</v>
       </c>
       <c r="H182" t="n">
         <v>12500</v>
@@ -5734,7 +5734,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.37383127212524</v>
+        <v>3.37383151054382</v>
       </c>
       <c r="H185" t="n">
         <v>4000</v>
@@ -5792,7 +5792,7 @@
         <v>3.5</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H187" t="n">
         <v>125000</v>
@@ -5821,7 +5821,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H188" t="n">
         <v>10500</v>
@@ -5879,7 +5879,7 @@
         <v>3.625</v>
       </c>
       <c r="G190" t="n">
-        <v>3.4597282409668</v>
+        <v>3.45972800254822</v>
       </c>
       <c r="H190" t="n">
         <v>15000</v>
@@ -5908,7 +5908,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H191" t="n">
         <v>6000</v>
@@ -5995,7 +5995,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H194" t="n">
         <v>1500</v>
@@ -6053,7 +6053,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G196" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6082,7 +6082,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G197" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H198" t="n">
         <v>41000</v>
@@ -6198,7 +6198,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H201" t="n">
         <v>500</v>
@@ -6227,7 +6227,7 @@
         <v>3.5</v>
       </c>
       <c r="G202" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H202" t="n">
         <v>20500</v>
@@ -6256,7 +6256,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G203" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H203" t="n">
         <v>45000</v>
@@ -6314,7 +6314,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6343,7 +6343,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H206" t="n">
         <v>2000</v>
@@ -6401,7 +6401,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G208" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H208" t="n">
         <v>2000</v>
@@ -6430,7 +6430,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G209" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H209" t="n">
         <v>5000</v>
@@ -6459,7 +6459,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.50744843482971</v>
+        <v>3.50744819641113</v>
       </c>
       <c r="H210" t="n">
         <v>18000</v>
@@ -6488,7 +6488,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H211" t="n">
         <v>35500</v>
@@ -6575,7 +6575,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G215" t="n">
-        <v>3.52176475524902</v>
+        <v>3.52176451683044</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G216" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H216" t="n">
         <v>3000</v>
@@ -6662,7 +6662,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G217" t="n">
-        <v>3.57425689697266</v>
+        <v>3.57425665855408</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6720,7 +6720,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H219" t="n">
         <v>5000</v>
@@ -6749,7 +6749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>3.56948471069336</v>
+        <v>3.56948494911194</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G222" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H222" t="n">
         <v>1000</v>
@@ -6923,7 +6923,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>3.42155170440674</v>
+        <v>3.42155194282532</v>
       </c>
       <c r="H226" t="n">
         <v>21000</v>
@@ -6952,7 +6952,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H227" t="n">
         <v>40000</v>
@@ -7068,7 +7068,7 @@
         <v>3.5</v>
       </c>
       <c r="G231" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H231" t="n">
         <v>6500</v>
@@ -7126,7 +7126,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951542854309</v>
       </c>
       <c r="H233" t="n">
         <v>8500</v>
@@ -7155,7 +7155,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H234" t="n">
         <v>3000</v>
@@ -7184,7 +7184,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>3.46450018882751</v>
+        <v>3.46449995040894</v>
       </c>
       <c r="H235" t="n">
         <v>46000</v>
@@ -7213,7 +7213,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H236" t="n">
         <v>4000</v>
@@ -7271,7 +7271,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H238" t="n">
         <v>5000</v>
@@ -7300,7 +7300,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G239" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H239" t="n">
         <v>2500</v>
@@ -7329,7 +7329,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G240" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H241" t="n">
         <v>17500</v>
@@ -7387,7 +7387,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G242" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H242" t="n">
         <v>36500</v>
@@ -7416,7 +7416,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G243" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H243" t="n">
         <v>2500</v>
@@ -7445,7 +7445,7 @@
         <v>3.5</v>
       </c>
       <c r="G244" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H244" t="n">
         <v>5000</v>
@@ -7474,7 +7474,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H245" t="n">
         <v>9500</v>
@@ -7503,7 +7503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7590,7 +7590,7 @@
         <v>3.5</v>
       </c>
       <c r="G249" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H249" t="n">
         <v>5000</v>
@@ -7619,7 +7619,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G250" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H250" t="n">
         <v>2500</v>
@@ -7677,7 +7677,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>3.32133913040161</v>
+        <v>3.32133889198303</v>
       </c>
       <c r="H252" t="n">
         <v>4000</v>
@@ -7706,7 +7706,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>3.39291954040527</v>
+        <v>3.39291977882385</v>
       </c>
       <c r="H253" t="n">
         <v>2500</v>
@@ -7735,7 +7735,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G254" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H254" t="n">
         <v>500</v>
@@ -7764,7 +7764,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G255" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H255" t="n">
         <v>3500</v>
@@ -7822,7 +7822,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>3.45495581626892</v>
+        <v>3.45495557785034</v>
       </c>
       <c r="H257" t="n">
         <v>9000</v>
@@ -7938,7 +7938,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G261" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H261" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H265" t="n">
         <v>6000</v>
@@ -8141,7 +8141,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44541192054749</v>
+        <v>3.44541168212891</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8170,7 +8170,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G269" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H269" t="n">
         <v>8000</v>
@@ -8199,7 +8199,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G270" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G271" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H271" t="n">
         <v>9000</v>
@@ -8315,7 +8315,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>3.35951519012451</v>
+        <v>3.35951542854309</v>
       </c>
       <c r="H274" t="n">
         <v>1500</v>
@@ -8431,7 +8431,7 @@
         <v>3.5</v>
       </c>
       <c r="G278" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H278" t="n">
         <v>7500</v>
@@ -8460,7 +8460,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H279" t="n">
         <v>9500</v>
@@ -8489,7 +8489,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407432556152</v>
       </c>
       <c r="H281" t="n">
         <v>1000</v>
@@ -8547,7 +8547,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.2640745639801</v>
+        <v>3.26407432556152</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G283" t="n">
-        <v>3.28316259384155</v>
+        <v>3.28316283226013</v>
       </c>
       <c r="H283" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>3.5</v>
       </c>
       <c r="G284" t="n">
-        <v>3.34042739868164</v>
+        <v>3.34042716026306</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8634,7 +8634,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H285" t="n">
         <v>1000</v>
@@ -8663,7 +8663,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G286" t="n">
-        <v>3.23544216156006</v>
+        <v>3.23544239997864</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G287" t="n">
-        <v>3.24498629570007</v>
+        <v>3.24498653411865</v>
       </c>
       <c r="H287" t="n">
         <v>2000</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H289" t="n">
         <v>7000</v>
@@ -8837,7 +8837,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H292" t="n">
         <v>46500</v>
@@ -9359,7 +9359,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G310" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H310" t="n">
         <v>8000</v>
@@ -9446,7 +9446,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G313" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H313" t="n">
         <v>6000</v>
@@ -9504,7 +9504,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G315" t="n">
-        <v>3.75082206726074</v>
+        <v>3.7508225440979</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H316" t="n">
         <v>7000</v>
@@ -9591,7 +9591,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H318" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H319" t="n">
         <v>3500</v>
@@ -9649,7 +9649,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G320" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>3.77945470809937</v>
+        <v>3.77945446968079</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G324" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H324" t="n">
         <v>1000</v>
@@ -9794,7 +9794,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G325" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H325" t="n">
         <v>1500</v>
@@ -10432,7 +10432,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>3.66492581367493</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H347" t="n">
         <v>1500</v>
@@ -10548,7 +10548,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G351" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H351" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G353" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H353" t="n">
         <v>4000</v>
@@ -10635,7 +10635,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G354" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H355" t="n">
         <v>2500</v>
@@ -10693,7 +10693,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G356" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H356" t="n">
         <v>1000</v>
@@ -10751,7 +10751,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G358" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H358" t="n">
         <v>2500</v>
@@ -10809,7 +10809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G360" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H360" t="n">
         <v>9500</v>
@@ -10838,7 +10838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G361" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>3.6458375453949</v>
+        <v>3.64583730697632</v>
       </c>
       <c r="H369" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H380" t="n">
         <v>4000</v>
@@ -11418,7 +11418,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>3.5981171131134</v>
+        <v>3.59811687469482</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.48358845710754</v>
+        <v>3.48358821868896</v>
       </c>
       <c r="H386" t="n">
         <v>13000</v>
@@ -11592,7 +11592,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G387" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H387" t="n">
         <v>43000</v>
@@ -11621,7 +11621,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G388" t="n">
-        <v>3.36905908584595</v>
+        <v>3.36905932426453</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11679,7 +11679,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G390" t="n">
-        <v>3.25453042984009</v>
+        <v>3.25453066825867</v>
       </c>
       <c r="H390" t="n">
         <v>1000</v>
@@ -11708,7 +11708,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G391" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H391" t="n">
         <v>32000</v>
@@ -11766,7 +11766,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H393" t="n">
         <v>6500</v>
@@ -11795,7 +11795,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G394" t="n">
-        <v>3.47404432296753</v>
+        <v>3.47404408454895</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G395" t="n">
-        <v>3.3499710559845</v>
+        <v>3.34997129440308</v>
       </c>
       <c r="H395" t="n">
         <v>8500</v>
@@ -11853,7 +11853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>3.38814735412598</v>
+        <v>3.38814759254456</v>
       </c>
       <c r="H396" t="n">
         <v>8000</v>
@@ -11882,7 +11882,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>3.41677951812744</v>
+        <v>3.4167799949646</v>
       </c>
       <c r="H397" t="n">
         <v>7000</v>
@@ -11911,7 +11911,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>3.50267672538757</v>
+        <v>3.50267648696899</v>
       </c>
       <c r="H398" t="n">
         <v>1000</v>
@@ -11998,7 +11998,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58857274055481</v>
+        <v>3.58857297897339</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12056,7 +12056,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>3.54085278511047</v>
+        <v>3.54085254669189</v>
       </c>
       <c r="H403" t="n">
         <v>2000</v>
@@ -12114,7 +12114,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.70310235023499</v>
+        <v>3.70310211181641</v>
       </c>
       <c r="H405" t="n">
         <v>5500</v>
@@ -12172,7 +12172,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G407" t="n">
-        <v>3.65538167953491</v>
+        <v>3.65538144111633</v>
       </c>
       <c r="H407" t="n">
         <v>2500</v>
@@ -12259,7 +12259,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G410" t="n">
-        <v>3.66492581367493</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H410" t="n">
         <v>1500</v>
@@ -12404,7 +12404,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>3.65538167953491</v>
+        <v>3.65538144111633</v>
       </c>
       <c r="H415" t="n">
         <v>2500</v>
@@ -12433,7 +12433,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G416" t="n">
-        <v>3.66492581367493</v>
+        <v>3.66492557525635</v>
       </c>
       <c r="H416" t="n">
         <v>2500</v>
@@ -12491,7 +12491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G418" t="n">
-        <v>3.69355773925781</v>
+        <v>3.69355797767639</v>
       </c>
       <c r="H418" t="n">
         <v>5000</v>
@@ -12520,7 +12520,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>3.7409234046936</v>
+        <v>3.74092364311218</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H424" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G425" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H425" t="n">
         <v>500</v>
@@ -12723,7 +12723,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G426" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H426" t="n">
         <v>1000</v>
@@ -12752,7 +12752,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G427" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H427" t="n">
         <v>2500</v>
@@ -12781,7 +12781,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G428" t="n">
-        <v>3.7409234046936</v>
+        <v>3.74092364311218</v>
       </c>
       <c r="H428" t="n">
         <v>1500</v>
@@ -12839,7 +12839,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H430" t="n">
         <v>4000</v>
@@ -12868,7 +12868,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G431" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H431" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G433" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H433" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G434" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H434" t="n">
         <v>2000</v>
@@ -12984,7 +12984,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H435" t="n">
         <v>3500</v>
@@ -13332,7 +13332,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G447" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H447" t="n">
         <v>51500</v>
@@ -13361,7 +13361,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G450" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G451" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G453" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H454" t="n">
         <v>1000</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H455" t="n">
         <v>2500</v>
@@ -13622,7 +13622,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G468" t="n">
-        <v>3.56692743301392</v>
+        <v>3.56692719459534</v>
       </c>
       <c r="H468" t="n">
         <v>2500</v>
@@ -13970,7 +13970,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G469" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H469" t="n">
         <v>2000</v>
@@ -14028,7 +14028,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G471" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H471" t="n">
         <v>8500</v>
@@ -14057,7 +14057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G472" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H472" t="n">
         <v>5000</v>
@@ -14115,7 +14115,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H474" t="n">
         <v>5500</v>
@@ -14144,7 +14144,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G475" t="n">
-        <v>3.64425897598267</v>
+        <v>3.64425873756409</v>
       </c>
       <c r="H475" t="n">
         <v>1000</v>
@@ -14173,7 +14173,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H476" t="n">
         <v>7500</v>
@@ -14202,7 +14202,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G477" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H477" t="n">
         <v>500</v>
@@ -14260,7 +14260,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H479" t="n">
         <v>500</v>
@@ -14289,7 +14289,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G480" t="n">
-        <v>3.5862603187561</v>
+        <v>3.58626008033752</v>
       </c>
       <c r="H480" t="n">
         <v>10000</v>
@@ -14347,7 +14347,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G482" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H482" t="n">
         <v>2500</v>
@@ -14405,7 +14405,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G484" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H484" t="n">
         <v>14500</v>
@@ -14434,7 +14434,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G485" t="n">
-        <v>3.47026252746582</v>
+        <v>3.4702627658844</v>
       </c>
       <c r="H485" t="n">
         <v>6500</v>
@@ -14463,7 +14463,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H486" t="n">
         <v>4000</v>
@@ -14521,7 +14521,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G488" t="n">
-        <v>3.45092940330505</v>
+        <v>3.45092964172363</v>
       </c>
       <c r="H488" t="n">
         <v>2500</v>
@@ -14550,7 +14550,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G489" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H489" t="n">
         <v>1000</v>
@@ -14579,7 +14579,7 @@
         <v>3.5</v>
       </c>
       <c r="G490" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H490" t="n">
         <v>4000</v>
@@ -14608,7 +14608,7 @@
         <v>3.5</v>
       </c>
       <c r="G491" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H491" t="n">
         <v>8500</v>
@@ -14637,7 +14637,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>3.31559920310974</v>
+        <v>3.31559896469116</v>
       </c>
       <c r="H492" t="n">
         <v>8500</v>
@@ -14782,7 +14782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G497" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H497" t="n">
         <v>3000</v>
@@ -14811,7 +14811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G498" t="n">
-        <v>3.36393165588379</v>
+        <v>3.36393141746521</v>
       </c>
       <c r="H498" t="n">
         <v>1500</v>
@@ -14840,7 +14840,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>3.35426473617554</v>
+        <v>3.35426497459412</v>
       </c>
       <c r="H499" t="n">
         <v>6500</v>
@@ -14869,7 +14869,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G500" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H500" t="n">
         <v>5500</v>
@@ -14898,7 +14898,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G501" t="n">
-        <v>3.45092940330505</v>
+        <v>3.45092964172363</v>
       </c>
       <c r="H501" t="n">
         <v>6500</v>
@@ -14927,7 +14927,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H502" t="n">
         <v>4000</v>
@@ -14956,7 +14956,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H503" t="n">
         <v>3000</v>
@@ -14985,7 +14985,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>3.52826166152954</v>
+        <v>3.52826142311096</v>
       </c>
       <c r="H504" t="n">
         <v>4500</v>
@@ -15014,7 +15014,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G505" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H505" t="n">
         <v>1500</v>
@@ -15043,7 +15043,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G506" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H506" t="n">
         <v>2000</v>
@@ -15072,7 +15072,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G507" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>3.50892853736877</v>
+        <v>3.5089282989502</v>
       </c>
       <c r="H509" t="n">
         <v>1000</v>
@@ -15275,7 +15275,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>3.54759454727173</v>
+        <v>3.54759430885315</v>
       </c>
       <c r="H514" t="n">
         <v>3500</v>
@@ -15362,7 +15362,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H517" t="n">
         <v>6500</v>
@@ -15391,7 +15391,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H518" t="n">
         <v>25000</v>
@@ -15478,7 +15478,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G521" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H521" t="n">
         <v>5500</v>
@@ -15507,7 +15507,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G522" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H522" t="n">
         <v>6000</v>
@@ -15536,7 +15536,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G523" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H523" t="n">
         <v>8500</v>
@@ -15594,7 +15594,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G525" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H525" t="n">
         <v>4000</v>
@@ -15710,7 +15710,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G529" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H529" t="n">
         <v>7500</v>
@@ -15739,7 +15739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G530" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H530" t="n">
         <v>8000</v>
@@ -15768,7 +15768,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G531" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H531" t="n">
         <v>500</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H532" t="n">
         <v>6000</v>
@@ -15826,7 +15826,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H533" t="n">
         <v>5000</v>
@@ -15855,7 +15855,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H534" t="n">
         <v>2500</v>
@@ -15913,7 +15913,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H536" t="n">
         <v>500</v>
@@ -15942,7 +15942,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G537" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H537" t="n">
         <v>6500</v>
@@ -15971,7 +15971,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G538" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G539" t="n">
-        <v>3.75059056282043</v>
+        <v>3.75059032440186</v>
       </c>
       <c r="H539" t="n">
         <v>12000</v>
@@ -16058,7 +16058,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>3.46059584617615</v>
+        <v>3.46059632301331</v>
       </c>
       <c r="H541" t="n">
         <v>16500</v>
@@ -16261,7 +16261,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G548" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H548" t="n">
         <v>2500</v>
@@ -16290,7 +16290,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G549" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H549" t="n">
         <v>2500</v>
@@ -16319,7 +16319,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G550" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16493,7 +16493,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G556" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H556" t="n">
         <v>4500</v>
@@ -16522,7 +16522,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H557" t="n">
         <v>1500</v>
@@ -16580,7 +16580,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G559" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H559" t="n">
         <v>2500</v>
@@ -16609,7 +16609,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G560" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H560" t="n">
         <v>2500</v>
@@ -16725,7 +16725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G564" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H564" t="n">
         <v>1000</v>
@@ -16754,7 +16754,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H565" t="n">
         <v>7000</v>
@@ -16783,7 +16783,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G566" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G568" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G569" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -16899,7 +16899,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G570" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H570" t="n">
         <v>1000</v>
@@ -16928,7 +16928,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G571" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G573" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G575" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H575" t="n">
         <v>13000</v>
@@ -17102,7 +17102,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G577" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H577" t="n">
         <v>19000</v>
@@ -17189,7 +17189,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H580" t="n">
         <v>8500</v>
@@ -17334,7 +17334,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H585" t="n">
         <v>9500</v>
@@ -17363,7 +17363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G586" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H586" t="n">
         <v>5500</v>
@@ -17421,7 +17421,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H588" t="n">
         <v>5000</v>
@@ -17450,7 +17450,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G589" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H590" t="n">
         <v>4000</v>
@@ -17508,7 +17508,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G592" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G593" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G595" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H595" t="n">
         <v>7000</v>
@@ -17740,7 +17740,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H599" t="n">
         <v>500</v>
@@ -17769,7 +17769,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17798,7 +17798,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G601" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17856,7 +17856,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H603" t="n">
         <v>7000</v>
@@ -17885,7 +17885,7 @@
         <v>3.5</v>
       </c>
       <c r="G604" t="n">
-        <v>3.38326454162598</v>
+        <v>3.3832643032074</v>
       </c>
       <c r="H604" t="n">
         <v>6500</v>
@@ -17943,7 +17943,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H606" t="n">
         <v>1000</v>
@@ -18001,7 +18001,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H608" t="n">
         <v>19500</v>
@@ -18030,7 +18030,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G609" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H609" t="n">
         <v>2000</v>
@@ -18059,7 +18059,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H610" t="n">
         <v>5000</v>
@@ -18088,7 +18088,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G611" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H611" t="n">
         <v>3000</v>
@@ -18117,7 +18117,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G612" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H612" t="n">
         <v>500</v>
@@ -18146,7 +18146,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G613" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H613" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G617" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H617" t="n">
         <v>1000</v>
@@ -18291,7 +18291,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G622" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H622" t="n">
         <v>4500</v>
@@ -18436,7 +18436,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H623" t="n">
         <v>1000</v>
@@ -18494,7 +18494,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G625" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H625" t="n">
         <v>2000</v>
@@ -18697,7 +18697,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>3.40259718894958</v>
+        <v>3.40259742736816</v>
       </c>
       <c r="H632" t="n">
         <v>19000</v>
@@ -18726,7 +18726,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>3.36393165588379</v>
+        <v>3.36393141746521</v>
       </c>
       <c r="H633" t="n">
         <v>18000</v>
@@ -18755,7 +18755,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G634" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H634" t="n">
         <v>19000</v>
@@ -18784,7 +18784,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G635" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H635" t="n">
         <v>6000</v>
@@ -18813,7 +18813,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H636" t="n">
         <v>7000</v>
@@ -18871,7 +18871,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G638" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H638" t="n">
         <v>500</v>
@@ -18900,7 +18900,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G639" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H639" t="n">
         <v>18000</v>
@@ -19016,7 +19016,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G643" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H643" t="n">
         <v>7500</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H646" t="n">
         <v>9000</v>
@@ -19132,7 +19132,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H647" t="n">
         <v>8500</v>
@@ -19161,7 +19161,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H650" t="n">
         <v>500</v>
@@ -19248,7 +19248,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G651" t="n">
-        <v>3.61525940895081</v>
+        <v>3.61525964736938</v>
       </c>
       <c r="H651" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G656" t="n">
-        <v>3.51859498023987</v>
+        <v>3.51859474182129</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G657" t="n">
-        <v>3.4992618560791</v>
+        <v>3.49926161766052</v>
       </c>
       <c r="H657" t="n">
         <v>500</v>
@@ -19509,7 +19509,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H660" t="n">
         <v>10500</v>
@@ -19538,7 +19538,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H661" t="n">
         <v>10000</v>
@@ -19567,7 +19567,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>3.65392541885376</v>
+        <v>3.65392518043518</v>
       </c>
       <c r="H662" t="n">
         <v>1000</v>
@@ -19596,7 +19596,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H663" t="n">
         <v>8000</v>
@@ -19654,7 +19654,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G665" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H665" t="n">
         <v>12000</v>
@@ -19683,7 +19683,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G666" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H666" t="n">
         <v>10500</v>
@@ -19712,7 +19712,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H667" t="n">
         <v>13000</v>
@@ -19741,7 +19741,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>3.63459229469299</v>
+        <v>3.63459253311157</v>
       </c>
       <c r="H668" t="n">
         <v>4000</v>
@@ -19770,7 +19770,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G669" t="n">
-        <v>3.7119243144989</v>
+        <v>3.71192407608032</v>
       </c>
       <c r="H669" t="n">
         <v>3500</v>
@@ -19828,7 +19828,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H671" t="n">
         <v>500</v>
@@ -19857,7 +19857,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>3.69259142875671</v>
+        <v>3.69259119033813</v>
       </c>
       <c r="H673" t="n">
         <v>1500</v>
@@ -19944,7 +19944,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G675" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H675" t="n">
         <v>2500</v>
@@ -20060,7 +20060,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H679" t="n">
         <v>3000</v>
@@ -20118,7 +20118,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H681" t="n">
         <v>94000</v>
@@ -20147,7 +20147,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G682" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G683" t="n">
-        <v>3.79932522773743</v>
+        <v>3.79932498931885</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20234,7 +20234,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G685" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H685" t="n">
         <v>3000</v>
@@ -20292,7 +20292,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H687" t="n">
         <v>4000</v>
@@ -20379,7 +20379,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>3.77974081039429</v>
+        <v>3.77974057197571</v>
       </c>
       <c r="H690" t="n">
         <v>2000</v>
@@ -20524,7 +20524,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H695" t="n">
         <v>10500</v>
@@ -21104,7 +21104,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G715" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H715" t="n">
         <v>12500</v>
@@ -21133,7 +21133,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G722" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H723" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G730" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H730" t="n">
         <v>500</v>
@@ -21713,7 +21713,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H736" t="n">
         <v>2000</v>
@@ -21974,7 +21974,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G745" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22003,7 +22003,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H746" t="n">
         <v>500</v>
@@ -22061,7 +22061,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99516606330872</v>
+        <v>3.99516630172729</v>
       </c>
       <c r="H748" t="n">
         <v>8000</v>
@@ -22090,7 +22090,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G749" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H749" t="n">
         <v>500</v>
@@ -22235,7 +22235,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G754" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H754" t="n">
         <v>7000</v>
@@ -22351,7 +22351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H758" t="n">
         <v>16000</v>
@@ -22438,7 +22438,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G761" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H761" t="n">
         <v>500</v>
@@ -22467,7 +22467,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.85807752609253</v>
+        <v>3.85807728767395</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H766" t="n">
         <v>1000</v>
@@ -22612,7 +22612,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>3.87766170501709</v>
+        <v>3.87766146659851</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22699,7 +22699,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G770" t="n">
-        <v>3.97558212280273</v>
+        <v>3.97558236122131</v>
       </c>
       <c r="H770" t="n">
         <v>4000</v>
@@ -22786,7 +22786,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>4.13225507736206</v>
+        <v>4.13225555419922</v>
       </c>
       <c r="H773" t="n">
         <v>41000</v>
@@ -23018,7 +23018,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G781" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H781" t="n">
         <v>8500</v>
@@ -23076,7 +23076,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H783" t="n">
         <v>16500</v>
@@ -23105,7 +23105,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G785" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H785" t="n">
         <v>26000</v>
@@ -23163,7 +23163,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G786" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H786" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G787" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H787" t="n">
         <v>3500</v>
@@ -23221,7 +23221,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H788" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>4.32809734344482</v>
+        <v>4.32809686660767</v>
       </c>
       <c r="H790" t="n">
         <v>7500</v>
@@ -23395,7 +23395,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H794" t="n">
         <v>1000</v>
@@ -23743,7 +23743,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G806" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G808" t="n">
-        <v>4.6806116104126</v>
+        <v>4.68061208724976</v>
       </c>
       <c r="H808" t="n">
         <v>7500</v>
@@ -23946,7 +23946,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G818" t="n">
-        <v>4.71977996826172</v>
+        <v>4.71978044509888</v>
       </c>
       <c r="H818" t="n">
         <v>3500</v>
@@ -24207,7 +24207,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H822" t="n">
         <v>6500</v>
@@ -24236,7 +24236,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26934480667114</v>
+        <v>4.26934432983398</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H827" t="n">
         <v>2000</v>
@@ -24381,7 +24381,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H831" t="n">
         <v>500</v>
@@ -24497,7 +24497,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -24816,7 +24816,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>4.46518564224243</v>
+        <v>4.46518611907959</v>
       </c>
       <c r="H843" t="n">
         <v>500</v>
@@ -25164,7 +25164,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H855" t="n">
         <v>2000</v>
@@ -25686,7 +25686,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H873" t="n">
         <v>500</v>
@@ -25715,7 +25715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G874" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G875" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G877" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G878" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G879" t="n">
-        <v>4.23017644882202</v>
+        <v>4.23017597198486</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -25889,7 +25889,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G880" t="n">
-        <v>4.15183925628662</v>
+        <v>4.15183973312378</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H881" t="n">
         <v>1500</v>
@@ -25947,7 +25947,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -25976,7 +25976,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G884" t="n">
-        <v>4.17142391204834</v>
+        <v>4.1714243888855</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26063,7 +26063,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G886" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H886" t="n">
         <v>2000</v>
@@ -26092,7 +26092,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G887" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H887" t="n">
         <v>1500</v>
@@ -26150,7 +26150,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G889" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H889" t="n">
         <v>2500</v>
@@ -26179,7 +26179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G890" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G891" t="n">
-        <v>4.1910080909729</v>
+        <v>4.19100856781006</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H892" t="n">
         <v>55000</v>
@@ -26266,7 +26266,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H893" t="n">
         <v>3000</v>
@@ -26295,7 +26295,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>4.36726570129395</v>
+        <v>4.36726522445679</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.2889289855957</v>
+        <v>4.28892850875854</v>
       </c>
       <c r="H895" t="n">
         <v>11500</v>
@@ -26469,7 +26469,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>4.81770086288452</v>
+        <v>4.81770038604736</v>
       </c>
       <c r="H900" t="n">
         <v>6500</v>
@@ -26556,7 +26556,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H903" t="n">
         <v>2000</v>
@@ -26730,7 +26730,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H909" t="n">
         <v>11000</v>
@@ -27020,7 +27020,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>4.85686922073364</v>
+        <v>4.85686874389648</v>
       </c>
       <c r="H919" t="n">
         <v>6500</v>
@@ -27107,7 +27107,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G922" t="n">
-        <v>5.23875951766968</v>
+        <v>5.23875999450684</v>
       </c>
       <c r="H922" t="n">
         <v>19000</v>
@@ -27194,7 +27194,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G925" t="n">
-        <v>5.48356199264526</v>
+        <v>5.48356151580811</v>
       </c>
       <c r="H925" t="n">
         <v>22000</v>
@@ -27339,7 +27339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G930" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H930" t="n">
         <v>16000</v>
@@ -27368,7 +27368,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>5.28772020339966</v>
+        <v>5.28772068023682</v>
       </c>
       <c r="H931" t="n">
         <v>3000</v>
